--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,738 +394,722 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46269</v>
+        <v>46278</v>
       </c>
       <c r="B2">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46269.01041666666</v>
+        <v>46278.01041666666</v>
       </c>
       <c r="B3">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46269.02083333334</v>
+        <v>46278.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46269.03125</v>
+        <v>46278.03125</v>
       </c>
       <c r="B5">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46269.04166666666</v>
+        <v>46278.04166666666</v>
       </c>
       <c r="B6">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46269.05208333334</v>
+        <v>46278.05208333334</v>
       </c>
       <c r="B7">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46269.0625</v>
+        <v>46278.0625</v>
       </c>
       <c r="B8">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46269.07291666666</v>
+        <v>46278.07291666666</v>
       </c>
       <c r="B9">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46269.08333333334</v>
+        <v>46278.08333333334</v>
       </c>
       <c r="B10">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46269.09375</v>
+        <v>46278.09375</v>
       </c>
       <c r="B11">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46269.10416666666</v>
+        <v>46278.10416666666</v>
       </c>
       <c r="B12">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46269.11458333334</v>
+        <v>46278.11458333334</v>
       </c>
       <c r="B13">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46269.125</v>
+        <v>46278.125</v>
       </c>
       <c r="B14">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46269.13541666666</v>
+        <v>46278.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46269.14583333334</v>
+        <v>46278.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46269.15625</v>
+        <v>46278.15625</v>
       </c>
       <c r="B17">
-        <v>0.96</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46269.16666666666</v>
+        <v>46278.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.96</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46269.17708333334</v>
+        <v>46278.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.96</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46269.1875</v>
+        <v>46278.1875</v>
       </c>
       <c r="B20">
-        <v>0.964</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46269.19791666666</v>
+        <v>46278.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.984</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46269.20833333334</v>
+        <v>46278.20833333334</v>
       </c>
       <c r="B22">
-        <v>7.867</v>
+        <v>1.225</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46269.21875</v>
+        <v>46278.21875</v>
       </c>
       <c r="B23">
-        <v>7.947</v>
+        <v>1.313</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46269.22916666666</v>
+        <v>46278.22916666666</v>
       </c>
       <c r="B24">
-        <v>8.1</v>
+        <v>1.396</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46269.23958333334</v>
+        <v>46278.23958333334</v>
       </c>
       <c r="B25">
-        <v>13.333</v>
+        <v>1.559</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46269.25</v>
+        <v>46278.25</v>
       </c>
       <c r="B26">
-        <v>78.624</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46269.26041666666</v>
+        <v>46278.26041666666</v>
       </c>
       <c r="B27">
-        <v>137.374</v>
+        <v>34.896</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46269.27083333334</v>
+        <v>46278.27083333334</v>
       </c>
       <c r="B28">
-        <v>226.764</v>
+        <v>69.55</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46269.28125</v>
+        <v>46278.28125</v>
       </c>
       <c r="B29">
-        <v>338.594</v>
+        <v>116.631</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46269.29166666666</v>
+        <v>46278.29166666666</v>
       </c>
       <c r="B30">
-        <v>623.2670000000001</v>
+        <v>273.304</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46269.30208333334</v>
+        <v>46278.30208333334</v>
       </c>
       <c r="B31">
-        <v>783.881</v>
+        <v>365.571</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46269.3125</v>
+        <v>46278.3125</v>
       </c>
       <c r="B32">
-        <v>985.016</v>
+        <v>477.805</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46269.32291666666</v>
+        <v>46278.32291666666</v>
       </c>
       <c r="B33">
-        <v>1194.456</v>
+        <v>582.08</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46269.33333333334</v>
+        <v>46278.33333333334</v>
       </c>
       <c r="B34">
-        <v>1519.277</v>
+        <v>812.4450000000001</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46269.34375</v>
+        <v>46278.34375</v>
       </c>
       <c r="B35">
-        <v>1722.747</v>
+        <v>932.312</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46269.35416666666</v>
+        <v>46278.35416666666</v>
       </c>
       <c r="B36">
-        <v>1956.876</v>
+        <v>1041.12</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46269.36458333334</v>
+        <v>46278.36458333334</v>
       </c>
       <c r="B37">
-        <v>2149.137</v>
+        <v>1155.093</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46269.375</v>
+        <v>46278.375</v>
       </c>
       <c r="B38">
-        <v>2405.773</v>
+        <v>1364.381</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46269.38541666666</v>
+        <v>46278.38541666666</v>
       </c>
       <c r="B39">
-        <v>2581.082</v>
+        <v>1469.349</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46269.39583333334</v>
+        <v>46278.39583333334</v>
       </c>
       <c r="B40">
-        <v>2723.984</v>
+        <v>1554.535</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46269.40625</v>
+        <v>46278.40625</v>
       </c>
       <c r="B41">
-        <v>2824.998</v>
+        <v>1635.145</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46269.41666666666</v>
+        <v>46278.41666666666</v>
       </c>
       <c r="B42">
-        <v>2978.614</v>
+        <v>1760.41</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46269.42708333334</v>
+        <v>46278.42708333334</v>
       </c>
       <c r="B43">
-        <v>3058.722</v>
+        <v>1825.05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46269.4375</v>
+        <v>46278.4375</v>
       </c>
       <c r="B44">
-        <v>3127.65</v>
+        <v>1871.979</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46269.44791666666</v>
+        <v>46278.44791666666</v>
       </c>
       <c r="B45">
-        <v>3177.935</v>
+        <v>1937.056</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46269.45833333334</v>
+        <v>46278.45833333334</v>
       </c>
       <c r="B46">
-        <v>3230.302</v>
+        <v>1990.404</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46269.46875</v>
+        <v>46278.46875</v>
       </c>
       <c r="B47">
-        <v>3251.786</v>
+        <v>2014.873</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46269.47916666666</v>
+        <v>46278.47916666666</v>
       </c>
       <c r="B48">
-        <v>3249.906</v>
+        <v>2032.412</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46269.48958333334</v>
+        <v>46278.48958333334</v>
       </c>
       <c r="B49">
-        <v>3247.066</v>
+        <v>2037.188</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46269.5</v>
+        <v>46278.5</v>
       </c>
       <c r="B50">
-        <v>3237.43</v>
+        <v>2033.264</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46269.51041666666</v>
+        <v>46278.51041666666</v>
       </c>
       <c r="B51">
-        <v>3203.665</v>
+        <v>2022.174</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46269.52083333334</v>
+        <v>46278.52083333334</v>
       </c>
       <c r="B52">
-        <v>3176.111</v>
+        <v>2007.055</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46269.53125</v>
+        <v>46278.53125</v>
       </c>
       <c r="B53">
-        <v>3136.263</v>
+        <v>1983.457</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46269.54166666666</v>
+        <v>46278.54166666666</v>
       </c>
       <c r="B54">
-        <v>3133.775</v>
+        <v>1929.889</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46269.55208333334</v>
+        <v>46278.55208333334</v>
       </c>
       <c r="B55">
-        <v>3091.335</v>
+        <v>1904.428</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46269.5625</v>
+        <v>46278.5625</v>
       </c>
       <c r="B56">
-        <v>3014.359</v>
+        <v>1866.915</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46269.57291666666</v>
+        <v>46278.57291666666</v>
       </c>
       <c r="B57">
-        <v>2965.181</v>
+        <v>1826.348</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46269.58333333334</v>
+        <v>46278.58333333334</v>
       </c>
       <c r="B58">
-        <v>2869.885</v>
+        <v>1743.549</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46269.59375</v>
+        <v>46278.59375</v>
       </c>
       <c r="B59">
-        <v>2804.189</v>
+        <v>1693.287</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46269.60416666666</v>
+        <v>46278.60416666666</v>
       </c>
       <c r="B60">
-        <v>2721.527</v>
+        <v>1631.824</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46269.61458333334</v>
+        <v>46278.61458333334</v>
       </c>
       <c r="B61">
-        <v>2621.95</v>
+        <v>1566.041</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46269.625</v>
+        <v>46278.625</v>
       </c>
       <c r="B62">
-        <v>2424.243</v>
+        <v>1439.453</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46269.63541666666</v>
+        <v>46278.63541666666</v>
       </c>
       <c r="B63">
-        <v>2289.566</v>
+        <v>1357.551</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46269.64583333334</v>
+        <v>46278.64583333334</v>
       </c>
       <c r="B64">
-        <v>2168.407</v>
+        <v>1275.93</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46269.65625</v>
+        <v>46278.65625</v>
       </c>
       <c r="B65">
-        <v>2031.409</v>
+        <v>1176.989</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46269.66666666666</v>
+        <v>46278.66666666666</v>
       </c>
       <c r="B66">
-        <v>1772.637</v>
+        <v>1001.109</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46269.67708333334</v>
+        <v>46278.67708333334</v>
       </c>
       <c r="B67">
-        <v>1571.049</v>
+        <v>884.253</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46269.6875</v>
+        <v>46278.6875</v>
       </c>
       <c r="B68">
-        <v>1366.472</v>
+        <v>763.891</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46269.69791666666</v>
+        <v>46278.69791666666</v>
       </c>
       <c r="B69">
-        <v>1169.687</v>
+        <v>633.197</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46269.70833333334</v>
+        <v>46278.70833333334</v>
       </c>
       <c r="B70">
-        <v>876.314</v>
+        <v>453.52</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46269.71875</v>
+        <v>46278.71875</v>
       </c>
       <c r="B71">
-        <v>679.837</v>
+        <v>355.202</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46269.72916666666</v>
+        <v>46278.72916666666</v>
       </c>
       <c r="B72">
-        <v>515.554</v>
+        <v>243.305</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46269.73958333334</v>
+        <v>46278.73958333334</v>
       </c>
       <c r="B73">
-        <v>361.048</v>
+        <v>149.217</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46269.75</v>
+        <v>46278.75</v>
       </c>
       <c r="B74">
-        <v>183.025</v>
+        <v>62.391</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46269.76041666666</v>
+        <v>46278.76041666666</v>
       </c>
       <c r="B75">
-        <v>106.734</v>
+        <v>29.939</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46269.77083333334</v>
+        <v>46278.77083333334</v>
       </c>
       <c r="B76">
-        <v>48.326</v>
+        <v>14.857</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46269.78125</v>
+        <v>46278.78125</v>
       </c>
       <c r="B77">
-        <v>27.438</v>
+        <v>12.117</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46269.79166666666</v>
+        <v>46278.79166666666</v>
       </c>
       <c r="B78">
-        <v>41.587</v>
+        <v>43.436</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46269.80208333334</v>
+        <v>46278.80208333334</v>
       </c>
       <c r="B79">
-        <v>48.233</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46269.8125</v>
+        <v>46278.8125</v>
       </c>
       <c r="B80">
-        <v>47.544</v>
+        <v>42.69</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46269.82291666666</v>
+        <v>46278.82291666666</v>
       </c>
       <c r="B81">
-        <v>47.5</v>
+        <v>42.882</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46269.83333333334</v>
+        <v>46278.83333333334</v>
       </c>
       <c r="B82">
-        <v>60.286</v>
+        <v>41.062</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46269.84375</v>
+        <v>46278.84375</v>
       </c>
       <c r="B83">
-        <v>53.874</v>
+        <v>40.062</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46269.85416666666</v>
+        <v>46278.85416666666</v>
       </c>
       <c r="B84">
-        <v>55.77</v>
+        <v>38.062</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46269.86458333334</v>
+        <v>46278.86458333334</v>
       </c>
       <c r="B85">
-        <v>59.47</v>
+        <v>35.562</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46269.875</v>
+        <v>46278.875</v>
       </c>
       <c r="B86">
-        <v>42.96</v>
+        <v>35.16</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46269.88541666666</v>
+        <v>46278.88541666666</v>
       </c>
       <c r="B87">
-        <v>34.96</v>
+        <v>35.16</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46269.89583333334</v>
+        <v>46278.89583333334</v>
       </c>
       <c r="B88">
-        <v>40.96</v>
+        <v>33.16</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46269.90625</v>
+        <v>46278.90625</v>
       </c>
       <c r="B89">
-        <v>39.06</v>
+        <v>31.36</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46269.91666666666</v>
+        <v>46278.91666666666</v>
       </c>
       <c r="B90">
-        <v>38.56</v>
+        <v>30.762</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46269.92708333334</v>
+        <v>46278.92708333334</v>
       </c>
       <c r="B91">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" s="2">
-        <v>46269.9375</v>
-      </c>
-      <c r="B92">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="2">
-        <v>46269.94791666666</v>
-      </c>
-      <c r="B93">
-        <v>8.960000000000001</v>
+        <v>1.162</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B91"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,722 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="B2">
-        <v>1.16</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46278.01041666666</v>
+        <v>46283.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.16</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46278.02083333334</v>
+        <v>46283.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46278.03125</v>
+        <v>46283.03125</v>
       </c>
       <c r="B5">
-        <v>1.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46278.04166666666</v>
+        <v>46283.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.16</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46278.05208333334</v>
+        <v>46283.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46278.0625</v>
+        <v>46283.0625</v>
       </c>
       <c r="B8">
-        <v>1.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46278.07291666666</v>
+        <v>46283.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46278.08333333334</v>
+        <v>46283.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.16</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46278.09375</v>
+        <v>46283.09375</v>
       </c>
       <c r="B11">
-        <v>1.16</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46278.10416666666</v>
+        <v>46283.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.16</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46278.11458333334</v>
+        <v>46283.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.16</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46278.125</v>
+        <v>46283.125</v>
       </c>
       <c r="B14">
-        <v>1.16</v>
+        <v>4.66</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46278.13541666666</v>
+        <v>46283.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46278.14583333334</v>
+        <v>46283.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.16</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46278.15625</v>
+        <v>46283.15625</v>
       </c>
       <c r="B17">
-        <v>1.16</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46278.16666666666</v>
+        <v>46283.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.162</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46278.17708333334</v>
+        <v>46283.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.162</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46278.1875</v>
+        <v>46283.1875</v>
       </c>
       <c r="B20">
-        <v>1.162</v>
+        <v>5.064</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46278.19791666666</v>
+        <v>46283.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.162</v>
+        <v>13.576</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46278.20833333334</v>
+        <v>46283.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.225</v>
+        <v>14.092</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46278.21875</v>
+        <v>46283.21875</v>
       </c>
       <c r="B23">
-        <v>1.313</v>
+        <v>14.252</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46278.22916666666</v>
+        <v>46283.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.396</v>
+        <v>16.14</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46278.23958333334</v>
+        <v>46283.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.559</v>
+        <v>5.538</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46278.25</v>
+        <v>46283.25</v>
       </c>
       <c r="B26">
-        <v>17.99</v>
+        <v>31.097</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46278.26041666666</v>
+        <v>46283.26041666666</v>
       </c>
       <c r="B27">
-        <v>34.896</v>
+        <v>59.086</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46278.27083333334</v>
+        <v>46283.27083333334</v>
       </c>
       <c r="B28">
-        <v>69.55</v>
+        <v>132.979</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46278.28125</v>
+        <v>46283.28125</v>
       </c>
       <c r="B29">
-        <v>116.631</v>
+        <v>228.031</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46278.29166666666</v>
+        <v>46283.29166666666</v>
       </c>
       <c r="B30">
-        <v>273.304</v>
+        <v>511.306</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46278.30208333334</v>
+        <v>46283.30208333334</v>
       </c>
       <c r="B31">
-        <v>365.571</v>
+        <v>670.47</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46278.3125</v>
+        <v>46283.3125</v>
       </c>
       <c r="B32">
-        <v>477.805</v>
+        <v>870.21</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46278.32291666666</v>
+        <v>46283.32291666666</v>
       </c>
       <c r="B33">
-        <v>582.08</v>
+        <v>1063.431</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46278.33333333334</v>
+        <v>46283.33333333334</v>
       </c>
       <c r="B34">
-        <v>812.4450000000001</v>
+        <v>1393.274</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46278.34375</v>
+        <v>46283.34375</v>
       </c>
       <c r="B35">
-        <v>932.312</v>
+        <v>1590.06</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46278.35416666666</v>
+        <v>46283.35416666666</v>
       </c>
       <c r="B36">
-        <v>1041.12</v>
+        <v>1811.688</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46278.36458333334</v>
+        <v>46283.36458333334</v>
       </c>
       <c r="B37">
-        <v>1155.093</v>
+        <v>1977.532</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46278.375</v>
+        <v>46283.375</v>
       </c>
       <c r="B38">
-        <v>1364.381</v>
+        <v>2222.037</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46278.38541666666</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="B39">
-        <v>1469.349</v>
+        <v>2363.881</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46278.39583333334</v>
+        <v>46283.39583333334</v>
       </c>
       <c r="B40">
-        <v>1554.535</v>
+        <v>2502.008</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46278.40625</v>
+        <v>46283.40625</v>
       </c>
       <c r="B41">
-        <v>1635.145</v>
+        <v>2611.342</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46278.41666666666</v>
+        <v>46283.41666666666</v>
       </c>
       <c r="B42">
-        <v>1760.41</v>
+        <v>2715.648</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46278.42708333334</v>
+        <v>46283.42708333334</v>
       </c>
       <c r="B43">
-        <v>1825.05</v>
+        <v>2798.179</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46278.4375</v>
+        <v>46283.4375</v>
       </c>
       <c r="B44">
-        <v>1871.979</v>
+        <v>2866.483</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46278.44791666666</v>
+        <v>46283.44791666666</v>
       </c>
       <c r="B45">
-        <v>1937.056</v>
+        <v>2912.851</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46278.45833333334</v>
+        <v>46283.45833333334</v>
       </c>
       <c r="B46">
-        <v>1990.404</v>
+        <v>2981.872</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46278.46875</v>
+        <v>46283.46875</v>
       </c>
       <c r="B47">
-        <v>2014.873</v>
+        <v>2999.996</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46278.47916666666</v>
+        <v>46283.47916666666</v>
       </c>
       <c r="B48">
-        <v>2032.412</v>
+        <v>3023.408</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46278.48958333334</v>
+        <v>46283.48958333334</v>
       </c>
       <c r="B49">
-        <v>2037.188</v>
+        <v>3035.697</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46278.5</v>
+        <v>46283.5</v>
       </c>
       <c r="B50">
-        <v>2033.264</v>
+        <v>3028.508</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46278.51041666666</v>
+        <v>46283.51041666666</v>
       </c>
       <c r="B51">
-        <v>2022.174</v>
+        <v>3022.42</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46278.52083333334</v>
+        <v>46283.52083333334</v>
       </c>
       <c r="B52">
-        <v>2007.055</v>
+        <v>3008.501</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46278.53125</v>
+        <v>46283.53125</v>
       </c>
       <c r="B53">
-        <v>1983.457</v>
+        <v>2991.305</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46278.54166666666</v>
+        <v>46283.54166666666</v>
       </c>
       <c r="B54">
-        <v>1929.889</v>
+        <v>2932.644</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46278.55208333334</v>
+        <v>46283.55208333334</v>
       </c>
       <c r="B55">
-        <v>1904.428</v>
+        <v>2895.814</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46278.5625</v>
+        <v>46283.5625</v>
       </c>
       <c r="B56">
-        <v>1866.915</v>
+        <v>2838.808</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46278.57291666666</v>
+        <v>46283.57291666666</v>
       </c>
       <c r="B57">
-        <v>1826.348</v>
+        <v>2776.972</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46278.58333333334</v>
+        <v>46283.58333333334</v>
       </c>
       <c r="B58">
-        <v>1743.549</v>
+        <v>2641.75</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46278.59375</v>
+        <v>46283.59375</v>
       </c>
       <c r="B59">
-        <v>1693.287</v>
+        <v>2550.745</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46278.60416666666</v>
+        <v>46283.60416666666</v>
       </c>
       <c r="B60">
-        <v>1631.824</v>
+        <v>2450.406</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46278.61458333334</v>
+        <v>46283.61458333334</v>
       </c>
       <c r="B61">
-        <v>1566.041</v>
+        <v>2341.953</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46278.625</v>
+        <v>46283.625</v>
       </c>
       <c r="B62">
-        <v>1439.453</v>
+        <v>2184.411</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46278.63541666666</v>
+        <v>46283.63541666666</v>
       </c>
       <c r="B63">
-        <v>1357.551</v>
+        <v>2028.368</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46278.64583333334</v>
+        <v>46283.64583333334</v>
       </c>
       <c r="B64">
-        <v>1275.93</v>
+        <v>1884.445</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46278.65625</v>
+        <v>46283.65625</v>
       </c>
       <c r="B65">
-        <v>1176.989</v>
+        <v>1726.577</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46278.66666666666</v>
+        <v>46283.66666666666</v>
       </c>
       <c r="B66">
-        <v>1001.109</v>
+        <v>1419.466</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46278.67708333334</v>
+        <v>46283.67708333334</v>
       </c>
       <c r="B67">
-        <v>884.253</v>
+        <v>1228.01</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46278.6875</v>
+        <v>46283.6875</v>
       </c>
       <c r="B68">
-        <v>763.891</v>
+        <v>1025.833</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46278.69791666666</v>
+        <v>46283.69791666666</v>
       </c>
       <c r="B69">
-        <v>633.197</v>
+        <v>825.982</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46278.70833333334</v>
+        <v>46283.70833333334</v>
       </c>
       <c r="B70">
-        <v>453.52</v>
+        <v>557.951</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46278.71875</v>
+        <v>46283.71875</v>
       </c>
       <c r="B71">
-        <v>355.202</v>
+        <v>400.59</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46278.72916666666</v>
+        <v>46283.72916666666</v>
       </c>
       <c r="B72">
-        <v>243.305</v>
+        <v>251.042</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46278.73958333334</v>
+        <v>46283.73958333334</v>
       </c>
       <c r="B73">
-        <v>149.217</v>
+        <v>155.945</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46278.75</v>
+        <v>46283.75</v>
       </c>
       <c r="B74">
-        <v>62.391</v>
+        <v>89.795</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46278.76041666666</v>
+        <v>46283.76041666666</v>
       </c>
       <c r="B75">
-        <v>29.939</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46278.77083333334</v>
+        <v>46283.77083333334</v>
       </c>
       <c r="B76">
-        <v>14.857</v>
+        <v>52.816</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46278.78125</v>
+        <v>46283.78125</v>
       </c>
       <c r="B77">
-        <v>12.117</v>
+        <v>59.671</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46278.79166666666</v>
+        <v>46283.79166666666</v>
       </c>
       <c r="B78">
-        <v>43.436</v>
+        <v>64.63800000000001</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46278.80208333334</v>
+        <v>46283.80208333334</v>
       </c>
       <c r="B79">
-        <v>43.53</v>
+        <v>64.322</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46278.8125</v>
+        <v>46283.8125</v>
       </c>
       <c r="B80">
-        <v>42.69</v>
+        <v>64.602</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46278.82291666666</v>
+        <v>46283.82291666666</v>
       </c>
       <c r="B81">
-        <v>42.882</v>
+        <v>65.77800000000001</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46278.83333333334</v>
+        <v>46283.83333333334</v>
       </c>
       <c r="B82">
-        <v>41.062</v>
+        <v>60.868</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46278.84375</v>
+        <v>46283.84375</v>
       </c>
       <c r="B83">
-        <v>40.062</v>
+        <v>61.06</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46278.85416666666</v>
+        <v>46283.85416666666</v>
       </c>
       <c r="B84">
-        <v>38.062</v>
+        <v>60.06</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46278.86458333334</v>
+        <v>46283.86458333334</v>
       </c>
       <c r="B85">
-        <v>35.562</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46278.875</v>
+        <v>46283.875</v>
       </c>
       <c r="B86">
-        <v>35.16</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46278.88541666666</v>
+        <v>46283.88541666666</v>
       </c>
       <c r="B87">
-        <v>35.16</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46278.89583333334</v>
+        <v>46283.89583333334</v>
       </c>
       <c r="B88">
-        <v>33.16</v>
+        <v>14.66</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46278.90625</v>
+        <v>46283.90625</v>
       </c>
       <c r="B89">
-        <v>31.36</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46278.91666666666</v>
+        <v>46283.91666666666</v>
       </c>
       <c r="B90">
-        <v>30.762</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46278.92708333334</v>
+        <v>46283.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.162</v>
+        <v>9.460000000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="2">
+        <v>46283.9375</v>
+      </c>
+      <c r="B92">
+        <v>9.359999999999999</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
+        <v>46283.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>9.16</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46283</v>
+        <v>46285</v>
       </c>
       <c r="B2">
-        <v>13.56</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46283.01041666666</v>
+        <v>46285.01041666666</v>
       </c>
       <c r="B3">
-        <v>13.56</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46283.02083333334</v>
+        <v>46285.02083333334</v>
       </c>
       <c r="B4">
-        <v>5.06</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46283.03125</v>
+        <v>46285.03125</v>
       </c>
       <c r="B5">
-        <v>5.06</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46283.04166666666</v>
+        <v>46285.04166666666</v>
       </c>
       <c r="B6">
-        <v>3.14</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46283.05208333334</v>
+        <v>46285.05208333334</v>
       </c>
       <c r="B7">
-        <v>5.14</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46283.0625</v>
+        <v>46285.0625</v>
       </c>
       <c r="B8">
-        <v>5.14</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46283.07291666666</v>
+        <v>46285.07291666666</v>
       </c>
       <c r="B9">
-        <v>5.14</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46283.08333333334</v>
+        <v>46285.08333333334</v>
       </c>
       <c r="B10">
-        <v>5.14</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46283.09375</v>
+        <v>46285.09375</v>
       </c>
       <c r="B11">
-        <v>3.14</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46283.10416666666</v>
+        <v>46285.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.74</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46283.11458333334</v>
+        <v>46285.11458333334</v>
       </c>
       <c r="B13">
-        <v>2.34</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46283.125</v>
+        <v>46285.125</v>
       </c>
       <c r="B14">
-        <v>4.66</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46283.13541666666</v>
+        <v>46285.13541666666</v>
       </c>
       <c r="B15">
-        <v>5.06</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46283.14583333334</v>
+        <v>46285.14583333334</v>
       </c>
       <c r="B16">
-        <v>5.06</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46283.15625</v>
+        <v>46285.15625</v>
       </c>
       <c r="B17">
-        <v>3.06</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46283.16666666666</v>
+        <v>46285.16666666666</v>
       </c>
       <c r="B18">
-        <v>3.06</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46283.17708333334</v>
+        <v>46285.17708333334</v>
       </c>
       <c r="B19">
-        <v>3.06</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46283.1875</v>
+        <v>46285.1875</v>
       </c>
       <c r="B20">
-        <v>5.064</v>
+        <v>1.162</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46283.19791666666</v>
+        <v>46285.19791666666</v>
       </c>
       <c r="B21">
-        <v>13.576</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46283.20833333334</v>
+        <v>46285.20833333334</v>
       </c>
       <c r="B22">
-        <v>14.092</v>
+        <v>1.361</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46283.21875</v>
+        <v>46285.21875</v>
       </c>
       <c r="B23">
-        <v>14.252</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46283.22916666666</v>
+        <v>46285.22916666666</v>
       </c>
       <c r="B24">
-        <v>16.14</v>
+        <v>5.114</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46283.23958333334</v>
+        <v>46285.23958333334</v>
       </c>
       <c r="B25">
-        <v>5.538</v>
+        <v>5.343</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46283.25</v>
+        <v>46285.25</v>
       </c>
       <c r="B26">
-        <v>31.097</v>
+        <v>25.325</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46283.26041666666</v>
+        <v>46285.26041666666</v>
       </c>
       <c r="B27">
-        <v>59.086</v>
+        <v>48.448</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46283.27083333334</v>
+        <v>46285.27083333334</v>
       </c>
       <c r="B28">
-        <v>132.979</v>
+        <v>116.911</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46283.28125</v>
+        <v>46285.28125</v>
       </c>
       <c r="B29">
-        <v>228.031</v>
+        <v>207.832</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46283.29166666666</v>
+        <v>46285.29166666666</v>
       </c>
       <c r="B30">
-        <v>511.306</v>
+        <v>476.289</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46283.30208333334</v>
+        <v>46285.30208333334</v>
       </c>
       <c r="B31">
-        <v>670.47</v>
+        <v>641.2</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46283.3125</v>
+        <v>46285.3125</v>
       </c>
       <c r="B32">
-        <v>870.21</v>
+        <v>839.292</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46283.32291666666</v>
+        <v>46285.32291666666</v>
       </c>
       <c r="B33">
-        <v>1063.431</v>
+        <v>1059.265</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46283.33333333334</v>
+        <v>46285.33333333334</v>
       </c>
       <c r="B34">
-        <v>1393.274</v>
+        <v>1415.803</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46283.34375</v>
+        <v>46285.34375</v>
       </c>
       <c r="B35">
-        <v>1590.06</v>
+        <v>1618.376</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46283.35416666666</v>
+        <v>46285.35416666666</v>
       </c>
       <c r="B36">
-        <v>1811.688</v>
+        <v>1832.221</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46283.36458333334</v>
+        <v>46285.36458333334</v>
       </c>
       <c r="B37">
-        <v>1977.532</v>
+        <v>2029.992</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46283.375</v>
+        <v>46285.375</v>
       </c>
       <c r="B38">
-        <v>2222.037</v>
+        <v>2330.164</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46283.38541666666</v>
+        <v>46285.38541666666</v>
       </c>
       <c r="B39">
-        <v>2363.881</v>
+        <v>2492.244</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46283.39583333334</v>
+        <v>46285.39583333334</v>
       </c>
       <c r="B40">
-        <v>2502.008</v>
+        <v>2644.105</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46283.40625</v>
+        <v>46285.40625</v>
       </c>
       <c r="B41">
-        <v>2611.342</v>
+        <v>2507.971</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46283.41666666666</v>
+        <v>46285.41666666666</v>
       </c>
       <c r="B42">
-        <v>2715.648</v>
+        <v>2645.455</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46283.42708333334</v>
+        <v>46285.42708333334</v>
       </c>
       <c r="B43">
-        <v>2798.179</v>
+        <v>2626.607</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46283.4375</v>
+        <v>46285.4375</v>
       </c>
       <c r="B44">
-        <v>2866.483</v>
+        <v>2726.665</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46283.44791666666</v>
+        <v>46285.44791666666</v>
       </c>
       <c r="B45">
-        <v>2912.851</v>
+        <v>2618.21</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46283.45833333334</v>
+        <v>46285.45833333334</v>
       </c>
       <c r="B46">
-        <v>2981.872</v>
+        <v>2444.298</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46283.46875</v>
+        <v>46285.46875</v>
       </c>
       <c r="B47">
-        <v>2999.996</v>
+        <v>2470.978</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46283.47916666666</v>
+        <v>46285.47916666666</v>
       </c>
       <c r="B48">
-        <v>3023.408</v>
+        <v>2489.029</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46283.48958333334</v>
+        <v>46285.48958333334</v>
       </c>
       <c r="B49">
-        <v>3035.697</v>
+        <v>2502.717</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46283.5</v>
+        <v>46285.5</v>
       </c>
       <c r="B50">
-        <v>3028.508</v>
+        <v>2528.601</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46283.51041666666</v>
+        <v>46285.51041666666</v>
       </c>
       <c r="B51">
-        <v>3022.42</v>
+        <v>2510.899</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46283.52083333334</v>
+        <v>46285.52083333334</v>
       </c>
       <c r="B52">
-        <v>3008.501</v>
+        <v>2493.466</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46283.53125</v>
+        <v>46285.53125</v>
       </c>
       <c r="B53">
-        <v>2991.305</v>
+        <v>2468.98</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46283.54166666666</v>
+        <v>46285.54166666666</v>
       </c>
       <c r="B54">
-        <v>2932.644</v>
+        <v>2304.99</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46283.55208333334</v>
+        <v>46285.55208333334</v>
       </c>
       <c r="B55">
-        <v>2895.814</v>
+        <v>2267.393</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46283.5625</v>
+        <v>46285.5625</v>
       </c>
       <c r="B56">
-        <v>2838.808</v>
+        <v>2222.629</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46283.57291666666</v>
+        <v>46285.57291666666</v>
       </c>
       <c r="B57">
-        <v>2776.972</v>
+        <v>2219.169</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46283.58333333334</v>
+        <v>46285.58333333334</v>
       </c>
       <c r="B58">
-        <v>2641.75</v>
+        <v>2177.488</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46283.59375</v>
+        <v>46285.59375</v>
       </c>
       <c r="B59">
-        <v>2550.745</v>
+        <v>2100.828</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46283.60416666666</v>
+        <v>46285.60416666666</v>
       </c>
       <c r="B60">
-        <v>2450.406</v>
+        <v>2014.696</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46283.61458333334</v>
+        <v>46285.61458333334</v>
       </c>
       <c r="B61">
-        <v>2341.953</v>
+        <v>1921.585</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46283.625</v>
+        <v>46285.625</v>
       </c>
       <c r="B62">
-        <v>2184.411</v>
+        <v>2057.194</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46283.63541666666</v>
+        <v>46285.63541666666</v>
       </c>
       <c r="B63">
-        <v>2028.368</v>
+        <v>1926.647</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46283.64583333334</v>
+        <v>46285.64583333334</v>
       </c>
       <c r="B64">
-        <v>1884.445</v>
+        <v>1813.899</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46283.65625</v>
+        <v>46285.65625</v>
       </c>
       <c r="B65">
-        <v>1726.577</v>
+        <v>1701.357</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46283.66666666666</v>
+        <v>46285.66666666666</v>
       </c>
       <c r="B66">
-        <v>1419.466</v>
+        <v>1489.15</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46283.67708333334</v>
+        <v>46285.67708333334</v>
       </c>
       <c r="B67">
-        <v>1228.01</v>
+        <v>1292.313</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46283.6875</v>
+        <v>46285.6875</v>
       </c>
       <c r="B68">
-        <v>1025.833</v>
+        <v>1085.41</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46283.69791666666</v>
+        <v>46285.69791666666</v>
       </c>
       <c r="B69">
-        <v>825.982</v>
+        <v>868.647</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46283.70833333334</v>
+        <v>46285.70833333334</v>
       </c>
       <c r="B70">
-        <v>557.951</v>
+        <v>571.021</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46283.71875</v>
+        <v>46285.71875</v>
       </c>
       <c r="B71">
-        <v>400.59</v>
+        <v>412.783</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46283.72916666666</v>
+        <v>46285.72916666666</v>
       </c>
       <c r="B72">
-        <v>251.042</v>
+        <v>267.756</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46283.73958333334</v>
+        <v>46285.73958333334</v>
       </c>
       <c r="B73">
-        <v>155.945</v>
+        <v>151.396</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46283.75</v>
+        <v>46285.75</v>
       </c>
       <c r="B74">
-        <v>89.795</v>
+        <v>50.095</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46283.76041666666</v>
+        <v>46285.76041666666</v>
       </c>
       <c r="B75">
-        <v>60.68</v>
+        <v>19.752</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46283.77083333334</v>
+        <v>46285.77083333334</v>
       </c>
       <c r="B76">
-        <v>52.816</v>
+        <v>47.119</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46283.78125</v>
+        <v>46285.78125</v>
       </c>
       <c r="B77">
-        <v>59.671</v>
+        <v>50.412</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46283.79166666666</v>
+        <v>46285.79166666666</v>
       </c>
       <c r="B78">
-        <v>64.63800000000001</v>
+        <v>54.779</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46283.80208333334</v>
+        <v>46285.80208333334</v>
       </c>
       <c r="B79">
-        <v>64.322</v>
+        <v>53.692</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46283.8125</v>
+        <v>46285.8125</v>
       </c>
       <c r="B80">
-        <v>64.602</v>
+        <v>53.582</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46283.82291666666</v>
+        <v>46285.82291666666</v>
       </c>
       <c r="B81">
-        <v>65.77800000000001</v>
+        <v>54.036</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46283.83333333334</v>
+        <v>46285.83333333334</v>
       </c>
       <c r="B82">
-        <v>60.868</v>
+        <v>51.076</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46283.84375</v>
+        <v>46285.84375</v>
       </c>
       <c r="B83">
-        <v>61.06</v>
+        <v>52.66</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46283.85416666666</v>
+        <v>46285.85416666666</v>
       </c>
       <c r="B84">
-        <v>60.06</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46283.86458333334</v>
+        <v>46285.86458333334</v>
       </c>
       <c r="B85">
-        <v>51.86</v>
+        <v>47.76</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46283.875</v>
+        <v>46285.875</v>
       </c>
       <c r="B86">
-        <v>16.56</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46283.88541666666</v>
+        <v>46285.88541666666</v>
       </c>
       <c r="B87">
-        <v>6.56</v>
+        <v>44.66</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46283.89583333334</v>
+        <v>46285.89583333334</v>
       </c>
       <c r="B88">
-        <v>14.66</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46283.90625</v>
+        <v>46285.90625</v>
       </c>
       <c r="B89">
-        <v>12.76</v>
+        <v>8.26</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46283.91666666666</v>
+        <v>46285.91666666666</v>
       </c>
       <c r="B90">
-        <v>10.36</v>
+        <v>3.662</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46283.92708333334</v>
+        <v>46285.92708333334</v>
       </c>
       <c r="B91">
-        <v>9.460000000000001</v>
+        <v>2.062</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46283.9375</v>
+        <v>46285.9375</v>
       </c>
       <c r="B92">
-        <v>9.359999999999999</v>
+        <v>1.962</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46283.94791666666</v>
+        <v>46285.94791666666</v>
       </c>
       <c r="B93">
-        <v>9.16</v>
+        <v>1.662</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,738 +394,738 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46285</v>
+        <v>46295</v>
       </c>
       <c r="B2">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46285.01041666666</v>
+        <v>46295.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46285.02083333334</v>
+        <v>46295.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46285.03125</v>
+        <v>46295.03125</v>
       </c>
       <c r="B5">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46285.04166666666</v>
+        <v>46295.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46285.05208333334</v>
+        <v>46295.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46285.0625</v>
+        <v>46295.0625</v>
       </c>
       <c r="B8">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46285.07291666666</v>
+        <v>46295.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46285.08333333334</v>
+        <v>46295.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46285.09375</v>
+        <v>46295.09375</v>
       </c>
       <c r="B11">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46285.10416666666</v>
+        <v>46295.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46285.11458333334</v>
+        <v>46295.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46285.125</v>
+        <v>46295.125</v>
       </c>
       <c r="B14">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46285.13541666666</v>
+        <v>46295.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46285.14583333334</v>
+        <v>46295.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.16</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46285.15625</v>
+        <v>46295.15625</v>
       </c>
       <c r="B17">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46285.16666666666</v>
+        <v>46295.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.162</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46285.17708333334</v>
+        <v>46295.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.162</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46285.1875</v>
+        <v>46295.1875</v>
       </c>
       <c r="B20">
-        <v>1.162</v>
+        <v>1.088</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46285.19791666666</v>
+        <v>46295.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.17</v>
+        <v>1.104</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46285.20833333334</v>
+        <v>46295.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.361</v>
+        <v>1.222</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46285.21875</v>
+        <v>46295.21875</v>
       </c>
       <c r="B23">
-        <v>4.96</v>
+        <v>1.342</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46285.22916666666</v>
+        <v>46295.22916666666</v>
       </c>
       <c r="B24">
-        <v>5.114</v>
+        <v>1.454</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46285.23958333334</v>
+        <v>46295.23958333334</v>
       </c>
       <c r="B25">
-        <v>5.343</v>
+        <v>1.607</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46285.25</v>
+        <v>46295.25</v>
       </c>
       <c r="B26">
-        <v>25.325</v>
+        <v>13.429</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46285.26041666666</v>
+        <v>46295.26041666666</v>
       </c>
       <c r="B27">
-        <v>48.448</v>
+        <v>19.176</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46285.27083333334</v>
+        <v>46295.27083333334</v>
       </c>
       <c r="B28">
-        <v>116.911</v>
+        <v>57.782</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46285.28125</v>
+        <v>46295.28125</v>
       </c>
       <c r="B29">
-        <v>207.832</v>
+        <v>146.852</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46285.29166666666</v>
+        <v>46295.29166666666</v>
       </c>
       <c r="B30">
-        <v>476.289</v>
+        <v>456.106</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46285.30208333334</v>
+        <v>46295.30208333334</v>
       </c>
       <c r="B31">
-        <v>641.2</v>
+        <v>630.788</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46285.3125</v>
+        <v>46295.3125</v>
       </c>
       <c r="B32">
-        <v>839.292</v>
+        <v>895.01</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46285.32291666666</v>
+        <v>46295.32291666666</v>
       </c>
       <c r="B33">
-        <v>1059.265</v>
+        <v>1151.509</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46285.33333333334</v>
+        <v>46295.33333333334</v>
       </c>
       <c r="B34">
-        <v>1415.803</v>
+        <v>1585.826</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46285.34375</v>
+        <v>46295.34375</v>
       </c>
       <c r="B35">
-        <v>1618.376</v>
+        <v>1813.448</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46285.35416666666</v>
+        <v>46295.35416666666</v>
       </c>
       <c r="B36">
-        <v>1832.221</v>
+        <v>2063.628</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46285.36458333334</v>
+        <v>46295.36458333334</v>
       </c>
       <c r="B37">
-        <v>2029.992</v>
+        <v>2289.755</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46285.375</v>
+        <v>46295.375</v>
       </c>
       <c r="B38">
-        <v>2330.164</v>
+        <v>2687.266</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46285.38541666666</v>
+        <v>46295.38541666666</v>
       </c>
       <c r="B39">
-        <v>2492.244</v>
+        <v>2830.778</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46285.39583333334</v>
+        <v>46295.39583333334</v>
       </c>
       <c r="B40">
-        <v>2644.105</v>
+        <v>2977.207</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46285.40625</v>
+        <v>46295.40625</v>
       </c>
       <c r="B41">
-        <v>2507.971</v>
+        <v>3103.374</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46285.41666666666</v>
+        <v>46295.41666666666</v>
       </c>
       <c r="B42">
-        <v>2645.455</v>
+        <v>3262.909</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46285.42708333334</v>
+        <v>46295.42708333334</v>
       </c>
       <c r="B43">
-        <v>2626.607</v>
+        <v>3349.309</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46285.4375</v>
+        <v>46295.4375</v>
       </c>
       <c r="B44">
-        <v>2726.665</v>
+        <v>3413.734</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46285.44791666666</v>
+        <v>46295.44791666666</v>
       </c>
       <c r="B45">
-        <v>2618.21</v>
+        <v>3471.937</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46285.45833333334</v>
+        <v>46295.45833333334</v>
       </c>
       <c r="B46">
-        <v>2444.298</v>
+        <v>3509.55</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46285.46875</v>
+        <v>46295.46875</v>
       </c>
       <c r="B47">
-        <v>2470.978</v>
+        <v>3539.383</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46285.47916666666</v>
+        <v>46295.47916666666</v>
       </c>
       <c r="B48">
-        <v>2489.029</v>
+        <v>3560.622</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46285.48958333334</v>
+        <v>46295.48958333334</v>
       </c>
       <c r="B49">
-        <v>2502.717</v>
+        <v>3574.442</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46285.5</v>
+        <v>46295.5</v>
       </c>
       <c r="B50">
-        <v>2528.601</v>
+        <v>3568.444</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46285.51041666666</v>
+        <v>46295.51041666666</v>
       </c>
       <c r="B51">
-        <v>2510.899</v>
+        <v>3564.931</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46285.52083333334</v>
+        <v>46295.52083333334</v>
       </c>
       <c r="B52">
-        <v>2493.466</v>
+        <v>3553.282</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46285.53125</v>
+        <v>46295.53125</v>
       </c>
       <c r="B53">
-        <v>2468.98</v>
+        <v>3535.308</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46285.54166666666</v>
+        <v>46295.54166666666</v>
       </c>
       <c r="B54">
-        <v>2304.99</v>
+        <v>3494.304</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46285.55208333334</v>
+        <v>46295.55208333334</v>
       </c>
       <c r="B55">
-        <v>2267.393</v>
+        <v>3462.053</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46285.5625</v>
+        <v>46295.5625</v>
       </c>
       <c r="B56">
-        <v>2222.629</v>
+        <v>3409.963</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46285.57291666666</v>
+        <v>46295.57291666666</v>
       </c>
       <c r="B57">
-        <v>2219.169</v>
+        <v>3353.559</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46285.58333333334</v>
+        <v>46295.58333333334</v>
       </c>
       <c r="B58">
-        <v>2177.488</v>
+        <v>3224.779</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46285.59375</v>
+        <v>46295.59375</v>
       </c>
       <c r="B59">
-        <v>2100.828</v>
+        <v>3136.936</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46285.60416666666</v>
+        <v>46295.60416666666</v>
       </c>
       <c r="B60">
-        <v>2014.696</v>
+        <v>3035.398</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46285.61458333334</v>
+        <v>46295.61458333334</v>
       </c>
       <c r="B61">
-        <v>1921.585</v>
+        <v>2893.48</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46285.625</v>
+        <v>46295.625</v>
       </c>
       <c r="B62">
-        <v>2057.194</v>
+        <v>2621.13</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46285.63541666666</v>
+        <v>46295.63541666666</v>
       </c>
       <c r="B63">
-        <v>1926.647</v>
+        <v>2430.702</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46285.64583333334</v>
+        <v>46295.64583333334</v>
       </c>
       <c r="B64">
-        <v>1813.899</v>
+        <v>2225.928</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46285.65625</v>
+        <v>46295.65625</v>
       </c>
       <c r="B65">
-        <v>1701.357</v>
+        <v>2006.891</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46285.66666666666</v>
+        <v>46295.66666666666</v>
       </c>
       <c r="B66">
-        <v>1489.15</v>
+        <v>1617.702</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46285.67708333334</v>
+        <v>46295.67708333334</v>
       </c>
       <c r="B67">
-        <v>1292.313</v>
+        <v>1365.998</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46285.6875</v>
+        <v>46295.6875</v>
       </c>
       <c r="B68">
-        <v>1085.41</v>
+        <v>1092.291</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46285.69791666666</v>
+        <v>46295.69791666666</v>
       </c>
       <c r="B69">
-        <v>868.647</v>
+        <v>838.862</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46285.70833333334</v>
+        <v>46295.70833333334</v>
       </c>
       <c r="B70">
-        <v>571.021</v>
+        <v>481.849</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46285.71875</v>
+        <v>46295.71875</v>
       </c>
       <c r="B71">
-        <v>412.783</v>
+        <v>307.929</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46285.72916666666</v>
+        <v>46295.72916666666</v>
       </c>
       <c r="B72">
-        <v>267.756</v>
+        <v>170.101</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46285.73958333334</v>
+        <v>46295.73958333334</v>
       </c>
       <c r="B73">
-        <v>151.396</v>
+        <v>92.40000000000001</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46285.75</v>
+        <v>46295.75</v>
       </c>
       <c r="B74">
-        <v>50.095</v>
+        <v>22.545</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46285.76041666666</v>
+        <v>46295.76041666666</v>
       </c>
       <c r="B75">
-        <v>19.752</v>
+        <v>19.845</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46285.77083333334</v>
+        <v>46295.77083333334</v>
       </c>
       <c r="B76">
-        <v>47.119</v>
+        <v>19.387</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46285.78125</v>
+        <v>46295.78125</v>
       </c>
       <c r="B77">
-        <v>50.412</v>
+        <v>18.661</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46285.79166666666</v>
+        <v>46295.79166666666</v>
       </c>
       <c r="B78">
-        <v>54.779</v>
+        <v>17.924</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46285.80208333334</v>
+        <v>46295.80208333334</v>
       </c>
       <c r="B79">
-        <v>53.692</v>
+        <v>17.76</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46285.8125</v>
+        <v>46295.8125</v>
       </c>
       <c r="B80">
-        <v>53.582</v>
+        <v>15.708</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46285.82291666666</v>
+        <v>46295.82291666666</v>
       </c>
       <c r="B81">
-        <v>54.036</v>
+        <v>13.844</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46285.83333333334</v>
+        <v>46295.83333333334</v>
       </c>
       <c r="B82">
-        <v>51.076</v>
+        <v>12.708</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46285.84375</v>
+        <v>46295.84375</v>
       </c>
       <c r="B83">
-        <v>52.66</v>
+        <v>11.788</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46285.85416666666</v>
+        <v>46295.85416666666</v>
       </c>
       <c r="B84">
-        <v>50.66</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46285.86458333334</v>
+        <v>46295.86458333334</v>
       </c>
       <c r="B85">
-        <v>47.76</v>
+        <v>7.98</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46285.875</v>
+        <v>46295.875</v>
       </c>
       <c r="B86">
-        <v>45.26</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46285.88541666666</v>
+        <v>46295.88541666666</v>
       </c>
       <c r="B87">
-        <v>44.66</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46285.89583333334</v>
+        <v>46295.89583333334</v>
       </c>
       <c r="B88">
-        <v>9.76</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46285.90625</v>
+        <v>46295.90625</v>
       </c>
       <c r="B89">
-        <v>8.26</v>
+        <v>2.98</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46285.91666666666</v>
+        <v>46295.91666666666</v>
       </c>
       <c r="B90">
-        <v>3.662</v>
+        <v>5.482</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46285.92708333334</v>
+        <v>46295.92708333334</v>
       </c>
       <c r="B91">
-        <v>2.062</v>
+        <v>3.482</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46285.9375</v>
+        <v>46295.9375</v>
       </c>
       <c r="B92">
-        <v>1.962</v>
+        <v>2.582</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46285.94791666666</v>
+        <v>46295.94791666666</v>
       </c>
       <c r="B93">
-        <v>1.662</v>
+        <v>1.482</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,103 +394,103 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46295</v>
+        <v>46298</v>
       </c>
       <c r="B2">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46295.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B3">
-        <v>2.08</v>
+        <v>1.884</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46295.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B4">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46295.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B5">
-        <v>2.08</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46295.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B6">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46295.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B7">
-        <v>2.16</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46295.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B8">
-        <v>2.16</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46295.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B9">
-        <v>2.16</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46295.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B10">
-        <v>2.16</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46295.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B11">
-        <v>2.16</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46295.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.16</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46295.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B13">
-        <v>2.16</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46295.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B14">
         <v>1.08</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46295.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B15">
         <v>1.08</v>
@@ -506,15 +506,15 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46295.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B16">
-        <v>2.08</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46295.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B17">
         <v>1.08</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46295.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B18">
         <v>1.08</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46295.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B19">
         <v>1.08</v>
@@ -538,594 +538,594 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46295.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B20">
-        <v>1.088</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46295.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.104</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46295.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.222</v>
+        <v>3.683</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46295.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B23">
-        <v>1.342</v>
+        <v>3.759</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46295.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.454</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46295.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.607</v>
+        <v>3.952</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46295.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B26">
-        <v>13.429</v>
+        <v>12.494</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46295.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B27">
-        <v>19.176</v>
+        <v>15.905</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46295.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B28">
-        <v>57.782</v>
+        <v>52.686</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46295.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B29">
-        <v>146.852</v>
+        <v>142.407</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46295.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B30">
-        <v>456.106</v>
+        <v>405.441</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46295.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B31">
-        <v>630.788</v>
+        <v>607.095</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46295.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B32">
-        <v>895.01</v>
+        <v>818.942</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46295.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B33">
-        <v>1151.509</v>
+        <v>1093.388</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46295.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B34">
-        <v>1585.826</v>
+        <v>1464.961</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46295.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B35">
-        <v>1813.448</v>
+        <v>1709.586</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46295.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B36">
-        <v>2063.628</v>
+        <v>1983.527</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46295.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B37">
-        <v>2289.755</v>
+        <v>2201.657</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46295.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B38">
-        <v>2687.266</v>
+        <v>2551.623</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46295.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B39">
-        <v>2830.778</v>
+        <v>2715.187</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46295.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B40">
-        <v>2977.207</v>
+        <v>2861.44</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46295.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B41">
-        <v>3103.374</v>
+        <v>2987.487</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46295.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B42">
-        <v>3262.909</v>
+        <v>3151.942</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46295.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B43">
-        <v>3349.309</v>
+        <v>3240.309</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46295.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B44">
-        <v>3413.734</v>
+        <v>3310.706</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46295.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B45">
-        <v>3471.937</v>
+        <v>3366.296</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46295.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B46">
-        <v>3509.55</v>
+        <v>3374.007</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46295.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B47">
-        <v>3539.383</v>
+        <v>3393.886</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46295.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B48">
-        <v>3560.622</v>
+        <v>3411.223</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46295.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B49">
-        <v>3574.442</v>
+        <v>3416.168</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46295.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B50">
-        <v>3568.444</v>
+        <v>3451.039</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46295.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B51">
-        <v>3564.931</v>
+        <v>3433.668</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46295.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B52">
-        <v>3553.282</v>
+        <v>3420.693</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46295.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B53">
-        <v>3535.308</v>
+        <v>3399.492</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46295.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B54">
-        <v>3494.304</v>
+        <v>3355.819</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46295.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B55">
-        <v>3462.053</v>
+        <v>3310.072</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46295.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B56">
-        <v>3409.963</v>
+        <v>3251.246</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46295.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B57">
-        <v>3353.559</v>
+        <v>3193.931</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46295.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B58">
-        <v>3224.779</v>
+        <v>3082.772</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46295.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B59">
-        <v>3136.936</v>
+        <v>2987.186</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46295.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B60">
-        <v>3035.398</v>
+        <v>2864.465</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46295.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B61">
-        <v>2893.48</v>
+        <v>2736.522</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46295.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B62">
-        <v>2621.13</v>
+        <v>2494.313</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46295.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B63">
-        <v>2430.702</v>
+        <v>2308.932</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46295.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B64">
-        <v>2225.928</v>
+        <v>2082.994</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46295.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B65">
-        <v>2006.891</v>
+        <v>1867.71</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46295.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B66">
-        <v>1617.702</v>
+        <v>1460.85</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46295.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B67">
-        <v>1365.998</v>
+        <v>1211.642</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46295.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B68">
-        <v>1092.291</v>
+        <v>941.423</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46295.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B69">
-        <v>838.862</v>
+        <v>711.698</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46295.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B70">
-        <v>481.849</v>
+        <v>409.568</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46295.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B71">
-        <v>307.929</v>
+        <v>249.426</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46295.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B72">
-        <v>170.101</v>
+        <v>134.19</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46295.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B73">
-        <v>92.40000000000001</v>
+        <v>65.28100000000001</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46295.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B74">
-        <v>22.545</v>
+        <v>17.138</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46295.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B75">
-        <v>19.845</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46295.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B76">
-        <v>19.387</v>
+        <v>70.249</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46295.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B77">
-        <v>18.661</v>
+        <v>73.105</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46295.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B78">
-        <v>17.924</v>
+        <v>69.982</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46295.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B79">
-        <v>17.76</v>
+        <v>70.88200000000001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46295.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B80">
-        <v>15.708</v>
+        <v>68.268</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46295.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B81">
-        <v>13.844</v>
+        <v>67.724</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46295.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B82">
-        <v>12.708</v>
+        <v>60.584</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46295.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B83">
-        <v>11.788</v>
+        <v>60.084</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46295.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B84">
-        <v>10.78</v>
+        <v>12.484</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46295.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B85">
-        <v>7.98</v>
+        <v>8.984</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46295.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B86">
-        <v>6.78</v>
+        <v>5.884</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46295.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B87">
-        <v>6.08</v>
+        <v>5.584</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46295.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B88">
-        <v>5.08</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46295.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B89">
-        <v>2.98</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46295.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B90">
-        <v>5.482</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46295.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B91">
-        <v>3.482</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46295.9375</v>
+        <v>46298.9375</v>
       </c>
       <c r="B92">
-        <v>2.582</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46295.94791666666</v>
+        <v>46298.94791666666</v>
       </c>
       <c r="B93">
-        <v>1.482</v>
+        <v>3.48</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B93"/>
+  <dimension ref="A1:B92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,47 +394,47 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="B2">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46298.01041666666</v>
+        <v>46299.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.884</v>
+        <v>1.084</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46298.02083333334</v>
+        <v>46299.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.88</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46298.03125</v>
+        <v>46299.03125</v>
       </c>
       <c r="B5">
-        <v>1.88</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46298.04166666666</v>
+        <v>46299.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.66</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46298.05208333334</v>
+        <v>46299.05208333334</v>
       </c>
       <c r="B7">
         <v>1.16</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46298.0625</v>
+        <v>46299.0625</v>
       </c>
       <c r="B8">
         <v>1.16</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46298.07291666666</v>
+        <v>46299.07291666666</v>
       </c>
       <c r="B9">
         <v>1.16</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46298.08333333334</v>
+        <v>46299.08333333334</v>
       </c>
       <c r="B10">
         <v>1.16</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46298.09375</v>
+        <v>46299.09375</v>
       </c>
       <c r="B11">
         <v>1.16</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46298.10416666666</v>
+        <v>46299.10416666666</v>
       </c>
       <c r="B12">
         <v>1.16</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46298.11458333334</v>
+        <v>46299.11458333334</v>
       </c>
       <c r="B13">
         <v>1.16</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46298.125</v>
+        <v>46299.125</v>
       </c>
       <c r="B14">
         <v>1.08</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46298.13541666666</v>
+        <v>46299.13541666666</v>
       </c>
       <c r="B15">
         <v>1.08</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46298.14583333334</v>
+        <v>46299.14583333334</v>
       </c>
       <c r="B16">
         <v>1.08</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46298.15625</v>
+        <v>46299.15625</v>
       </c>
       <c r="B17">
         <v>1.08</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46298.16666666666</v>
+        <v>46299.16666666666</v>
       </c>
       <c r="B18">
         <v>1.08</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46298.17708333334</v>
+        <v>46299.17708333334</v>
       </c>
       <c r="B19">
         <v>1.08</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46298.1875</v>
+        <v>46299.1875</v>
       </c>
       <c r="B20">
         <v>1.08</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46298.19791666666</v>
+        <v>46299.19791666666</v>
       </c>
       <c r="B21">
         <v>1.08</v>
@@ -554,578 +554,570 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46298.20833333334</v>
+        <v>46299.20833333334</v>
       </c>
       <c r="B22">
-        <v>3.683</v>
+        <v>2.679</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46298.21875</v>
+        <v>46299.21875</v>
       </c>
       <c r="B23">
-        <v>3.759</v>
+        <v>2.795</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46298.22916666666</v>
+        <v>46299.22916666666</v>
       </c>
       <c r="B24">
-        <v>3.85</v>
+        <v>2.898</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46298.23958333334</v>
+        <v>46299.23958333334</v>
       </c>
       <c r="B25">
-        <v>3.952</v>
+        <v>3.065</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46298.25</v>
+        <v>46299.25</v>
       </c>
       <c r="B26">
-        <v>12.494</v>
+        <v>12.095</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46298.26041666666</v>
+        <v>46299.26041666666</v>
       </c>
       <c r="B27">
-        <v>15.905</v>
+        <v>14.951</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46298.27083333334</v>
+        <v>46299.27083333334</v>
       </c>
       <c r="B28">
-        <v>52.686</v>
+        <v>41.999</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46298.28125</v>
+        <v>46299.28125</v>
       </c>
       <c r="B29">
-        <v>142.407</v>
+        <v>130.165</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46298.29166666666</v>
+        <v>46299.29166666666</v>
       </c>
       <c r="B30">
-        <v>405.441</v>
+        <v>415.901</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46298.30208333334</v>
+        <v>46299.30208333334</v>
       </c>
       <c r="B31">
-        <v>607.095</v>
+        <v>624.016</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46298.3125</v>
+        <v>46299.3125</v>
       </c>
       <c r="B32">
-        <v>818.942</v>
+        <v>838.8920000000001</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46298.32291666666</v>
+        <v>46299.32291666666</v>
       </c>
       <c r="B33">
-        <v>1093.388</v>
+        <v>1069.664</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46298.33333333334</v>
+        <v>46299.33333333334</v>
       </c>
       <c r="B34">
-        <v>1464.961</v>
+        <v>1504.16</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46298.34375</v>
+        <v>46299.34375</v>
       </c>
       <c r="B35">
-        <v>1709.586</v>
+        <v>1749.545</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46298.35416666666</v>
+        <v>46299.35416666666</v>
       </c>
       <c r="B36">
-        <v>1983.527</v>
+        <v>2000.739</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46298.36458333334</v>
+        <v>46299.36458333334</v>
       </c>
       <c r="B37">
-        <v>2201.657</v>
+        <v>2223.396</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46298.375</v>
+        <v>46299.375</v>
       </c>
       <c r="B38">
-        <v>2551.623</v>
+        <v>2576.91</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46298.38541666666</v>
+        <v>46299.38541666666</v>
       </c>
       <c r="B39">
-        <v>2715.187</v>
+        <v>2739.877</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46298.39583333334</v>
+        <v>46299.39583333334</v>
       </c>
       <c r="B40">
-        <v>2861.44</v>
+        <v>2890.956</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46298.40625</v>
+        <v>46299.40625</v>
       </c>
       <c r="B41">
-        <v>2987.487</v>
+        <v>2990.111</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46298.41666666666</v>
+        <v>46299.41666666666</v>
       </c>
       <c r="B42">
-        <v>3151.942</v>
+        <v>3170.235</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46298.42708333334</v>
+        <v>46299.42708333334</v>
       </c>
       <c r="B43">
-        <v>3240.309</v>
+        <v>3253.768</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46298.4375</v>
+        <v>46299.4375</v>
       </c>
       <c r="B44">
-        <v>3310.706</v>
+        <v>3318.067</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46298.44791666666</v>
+        <v>46299.44791666666</v>
       </c>
       <c r="B45">
-        <v>3366.296</v>
+        <v>3319.086</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46298.45833333334</v>
+        <v>46299.45833333334</v>
       </c>
       <c r="B46">
-        <v>3374.007</v>
+        <v>3376.091</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46298.46875</v>
+        <v>46299.46875</v>
       </c>
       <c r="B47">
-        <v>3393.886</v>
+        <v>3371.73</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46298.47916666666</v>
+        <v>46299.47916666666</v>
       </c>
       <c r="B48">
-        <v>3411.223</v>
+        <v>3395.102</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46298.48958333334</v>
+        <v>46299.48958333334</v>
       </c>
       <c r="B49">
-        <v>3416.168</v>
+        <v>3386.406</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46298.5</v>
+        <v>46299.5</v>
       </c>
       <c r="B50">
-        <v>3451.039</v>
+        <v>3387.84</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46298.51041666666</v>
+        <v>46299.51041666666</v>
       </c>
       <c r="B51">
-        <v>3433.668</v>
+        <v>3377.45</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46298.52083333334</v>
+        <v>46299.52083333334</v>
       </c>
       <c r="B52">
-        <v>3420.693</v>
+        <v>3360.19</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46298.53125</v>
+        <v>46299.53125</v>
       </c>
       <c r="B53">
-        <v>3399.492</v>
+        <v>3330.88</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46298.54166666666</v>
+        <v>46299.54166666666</v>
       </c>
       <c r="B54">
-        <v>3355.819</v>
+        <v>3297.269</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46298.55208333334</v>
+        <v>46299.55208333334</v>
       </c>
       <c r="B55">
-        <v>3310.072</v>
+        <v>3253.336</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46298.5625</v>
+        <v>46299.5625</v>
       </c>
       <c r="B56">
-        <v>3251.246</v>
+        <v>3200.916</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46298.57291666666</v>
+        <v>46299.57291666666</v>
       </c>
       <c r="B57">
-        <v>3193.931</v>
+        <v>3138.313</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46298.58333333334</v>
+        <v>46299.58333333334</v>
       </c>
       <c r="B58">
-        <v>3082.772</v>
+        <v>3018.6</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46298.59375</v>
+        <v>46299.59375</v>
       </c>
       <c r="B59">
-        <v>2987.186</v>
+        <v>2923.411</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46298.60416666666</v>
+        <v>46299.60416666666</v>
       </c>
       <c r="B60">
-        <v>2864.465</v>
+        <v>2826.209</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46298.61458333334</v>
+        <v>46299.61458333334</v>
       </c>
       <c r="B61">
-        <v>2736.522</v>
+        <v>2731.052</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46298.625</v>
+        <v>46299.625</v>
       </c>
       <c r="B62">
-        <v>2494.313</v>
+        <v>2461.736</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46298.63541666666</v>
+        <v>46299.63541666666</v>
       </c>
       <c r="B63">
-        <v>2308.932</v>
+        <v>2279.912</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46298.64583333334</v>
+        <v>46299.64583333334</v>
       </c>
       <c r="B64">
-        <v>2082.994</v>
+        <v>2071.161</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46298.65625</v>
+        <v>46299.65625</v>
       </c>
       <c r="B65">
-        <v>1867.71</v>
+        <v>1851.096</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46298.66666666666</v>
+        <v>46299.66666666666</v>
       </c>
       <c r="B66">
-        <v>1460.85</v>
+        <v>1457.302</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46298.67708333334</v>
+        <v>46299.67708333334</v>
       </c>
       <c r="B67">
-        <v>1211.642</v>
+        <v>1201.027</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46298.6875</v>
+        <v>46299.6875</v>
       </c>
       <c r="B68">
-        <v>941.423</v>
+        <v>932.765</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46298.69791666666</v>
+        <v>46299.69791666666</v>
       </c>
       <c r="B69">
-        <v>711.698</v>
+        <v>694.253</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46298.70833333334</v>
+        <v>46299.70833333334</v>
       </c>
       <c r="B70">
-        <v>409.568</v>
+        <v>378.203</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46298.71875</v>
+        <v>46299.71875</v>
       </c>
       <c r="B71">
-        <v>249.426</v>
+        <v>235.084</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46298.72916666666</v>
+        <v>46299.72916666666</v>
       </c>
       <c r="B72">
-        <v>134.19</v>
+        <v>113.12</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46298.73958333334</v>
+        <v>46299.73958333334</v>
       </c>
       <c r="B73">
-        <v>65.28100000000001</v>
+        <v>48.889</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46298.75</v>
+        <v>46299.75</v>
       </c>
       <c r="B74">
-        <v>17.138</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46298.76041666666</v>
+        <v>46299.76041666666</v>
       </c>
       <c r="B75">
-        <v>21.39</v>
+        <v>18.674</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46298.77083333334</v>
+        <v>46299.77083333334</v>
       </c>
       <c r="B76">
-        <v>70.249</v>
+        <v>17.586</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46298.78125</v>
+        <v>46299.78125</v>
       </c>
       <c r="B77">
-        <v>73.105</v>
+        <v>66.206</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46298.79166666666</v>
+        <v>46299.79166666666</v>
       </c>
       <c r="B78">
-        <v>69.982</v>
+        <v>65.068</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46298.80208333334</v>
+        <v>46299.80208333334</v>
       </c>
       <c r="B79">
-        <v>70.88200000000001</v>
+        <v>65.16800000000001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46298.8125</v>
+        <v>46299.8125</v>
       </c>
       <c r="B80">
-        <v>68.268</v>
+        <v>63.168</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46298.82291666666</v>
+        <v>46299.82291666666</v>
       </c>
       <c r="B81">
-        <v>67.724</v>
+        <v>61.624</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46298.83333333334</v>
+        <v>46299.83333333334</v>
       </c>
       <c r="B82">
-        <v>60.584</v>
+        <v>55.184</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46298.84375</v>
+        <v>46299.84375</v>
       </c>
       <c r="B83">
-        <v>60.084</v>
+        <v>54.084</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46298.85416666666</v>
+        <v>46299.85416666666</v>
       </c>
       <c r="B84">
-        <v>12.484</v>
+        <v>52.384</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46298.86458333334</v>
+        <v>46299.86458333334</v>
       </c>
       <c r="B85">
-        <v>8.984</v>
+        <v>3.384</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46298.875</v>
+        <v>46299.875</v>
       </c>
       <c r="B86">
-        <v>5.884</v>
+        <v>1.884</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46298.88541666666</v>
+        <v>46299.88541666666</v>
       </c>
       <c r="B87">
-        <v>5.584</v>
+        <v>1.884</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46298.89583333334</v>
+        <v>46299.89583333334</v>
       </c>
       <c r="B88">
-        <v>5.38</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46298.90625</v>
+        <v>46299.90625</v>
       </c>
       <c r="B89">
-        <v>5.08</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46298.91666666666</v>
+        <v>46299.91666666666</v>
       </c>
       <c r="B90">
-        <v>4.98</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46298.92708333334</v>
+        <v>46299.92708333334</v>
       </c>
       <c r="B91">
-        <v>4.18</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46298.9375</v>
+        <v>46299.9375</v>
       </c>
       <c r="B92">
-        <v>3.58</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" s="2">
-        <v>46298.94791666666</v>
-      </c>
-      <c r="B93">
-        <v>3.48</v>
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B92"/>
+  <dimension ref="A1:B471"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,47 +394,47 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46299</v>
+        <v>46298</v>
       </c>
       <c r="B2">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46299.01041666666</v>
+        <v>46298.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.084</v>
+        <v>1.884</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46299.02083333334</v>
+        <v>46298.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.08</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46299.03125</v>
+        <v>46298.03125</v>
       </c>
       <c r="B5">
-        <v>1.08</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46299.04166666666</v>
+        <v>46298.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.16</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46299.05208333334</v>
+        <v>46298.05208333334</v>
       </c>
       <c r="B7">
         <v>1.16</v>
@@ -442,7 +442,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46299.0625</v>
+        <v>46298.0625</v>
       </c>
       <c r="B8">
         <v>1.16</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46299.07291666666</v>
+        <v>46298.07291666666</v>
       </c>
       <c r="B9">
         <v>1.16</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46299.08333333334</v>
+        <v>46298.08333333334</v>
       </c>
       <c r="B10">
         <v>1.16</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46299.09375</v>
+        <v>46298.09375</v>
       </c>
       <c r="B11">
         <v>1.16</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46299.10416666666</v>
+        <v>46298.10416666666</v>
       </c>
       <c r="B12">
         <v>1.16</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46299.11458333334</v>
+        <v>46298.11458333334</v>
       </c>
       <c r="B13">
         <v>1.16</v>
@@ -490,7 +490,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46299.125</v>
+        <v>46298.125</v>
       </c>
       <c r="B14">
         <v>1.08</v>
@@ -498,7 +498,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46299.13541666666</v>
+        <v>46298.13541666666</v>
       </c>
       <c r="B15">
         <v>1.08</v>
@@ -506,7 +506,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46299.14583333334</v>
+        <v>46298.14583333334</v>
       </c>
       <c r="B16">
         <v>1.08</v>
@@ -514,7 +514,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46299.15625</v>
+        <v>46298.15625</v>
       </c>
       <c r="B17">
         <v>1.08</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46299.16666666666</v>
+        <v>46298.16666666666</v>
       </c>
       <c r="B18">
         <v>1.08</v>
@@ -530,7 +530,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46299.17708333334</v>
+        <v>46298.17708333334</v>
       </c>
       <c r="B19">
         <v>1.08</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46299.1875</v>
+        <v>46298.1875</v>
       </c>
       <c r="B20">
         <v>1.08</v>
@@ -546,7 +546,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46299.19791666666</v>
+        <v>46298.19791666666</v>
       </c>
       <c r="B21">
         <v>1.08</v>
@@ -554,569 +554,3601 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46299.20833333334</v>
+        <v>46298.20833333334</v>
       </c>
       <c r="B22">
-        <v>2.679</v>
+        <v>3.683</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46299.21875</v>
+        <v>46298.21875</v>
       </c>
       <c r="B23">
-        <v>2.795</v>
+        <v>3.759</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46299.22916666666</v>
+        <v>46298.22916666666</v>
       </c>
       <c r="B24">
-        <v>2.898</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46299.23958333334</v>
+        <v>46298.23958333334</v>
       </c>
       <c r="B25">
-        <v>3.065</v>
+        <v>3.952</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46299.25</v>
+        <v>46298.25</v>
       </c>
       <c r="B26">
-        <v>12.095</v>
+        <v>12.494</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46299.26041666666</v>
+        <v>46298.26041666666</v>
       </c>
       <c r="B27">
-        <v>14.951</v>
+        <v>15.905</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46299.27083333334</v>
+        <v>46298.27083333334</v>
       </c>
       <c r="B28">
-        <v>41.999</v>
+        <v>52.686</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46299.28125</v>
+        <v>46298.28125</v>
       </c>
       <c r="B29">
-        <v>130.165</v>
+        <v>142.407</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46299.29166666666</v>
+        <v>46298.29166666666</v>
       </c>
       <c r="B30">
-        <v>415.901</v>
+        <v>405.441</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46299.30208333334</v>
+        <v>46298.30208333334</v>
       </c>
       <c r="B31">
-        <v>624.016</v>
+        <v>607.095</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46299.3125</v>
+        <v>46298.3125</v>
       </c>
       <c r="B32">
-        <v>838.8920000000001</v>
+        <v>818.942</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46299.32291666666</v>
+        <v>46298.32291666666</v>
       </c>
       <c r="B33">
-        <v>1069.664</v>
+        <v>1093.388</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46299.33333333334</v>
+        <v>46298.33333333334</v>
       </c>
       <c r="B34">
-        <v>1504.16</v>
+        <v>1464.961</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46299.34375</v>
+        <v>46298.34375</v>
       </c>
       <c r="B35">
-        <v>1749.545</v>
+        <v>1709.586</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46299.35416666666</v>
+        <v>46298.35416666666</v>
       </c>
       <c r="B36">
-        <v>2000.739</v>
+        <v>1983.527</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46299.36458333334</v>
+        <v>46298.36458333334</v>
       </c>
       <c r="B37">
-        <v>2223.396</v>
+        <v>2201.657</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46299.375</v>
+        <v>46298.375</v>
       </c>
       <c r="B38">
-        <v>2576.91</v>
+        <v>2551.623</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46299.38541666666</v>
+        <v>46298.38541666666</v>
       </c>
       <c r="B39">
-        <v>2739.877</v>
+        <v>2715.187</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46299.39583333334</v>
+        <v>46298.39583333334</v>
       </c>
       <c r="B40">
-        <v>2890.956</v>
+        <v>2861.44</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46299.40625</v>
+        <v>46298.40625</v>
       </c>
       <c r="B41">
-        <v>2990.111</v>
+        <v>2987.487</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46299.41666666666</v>
+        <v>46298.41666666666</v>
       </c>
       <c r="B42">
-        <v>3170.235</v>
+        <v>3151.942</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46299.42708333334</v>
+        <v>46298.42708333334</v>
       </c>
       <c r="B43">
-        <v>3253.768</v>
+        <v>3240.309</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46299.4375</v>
+        <v>46298.4375</v>
       </c>
       <c r="B44">
-        <v>3318.067</v>
+        <v>3310.706</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46299.44791666666</v>
+        <v>46298.44791666666</v>
       </c>
       <c r="B45">
-        <v>3319.086</v>
+        <v>3366.296</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46299.45833333334</v>
+        <v>46298.45833333334</v>
       </c>
       <c r="B46">
-        <v>3376.091</v>
+        <v>3374.007</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46299.46875</v>
+        <v>46298.46875</v>
       </c>
       <c r="B47">
-        <v>3371.73</v>
+        <v>3393.886</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46299.47916666666</v>
+        <v>46298.47916666666</v>
       </c>
       <c r="B48">
-        <v>3395.102</v>
+        <v>3411.223</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46299.48958333334</v>
+        <v>46298.48958333334</v>
       </c>
       <c r="B49">
-        <v>3386.406</v>
+        <v>3416.168</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46299.5</v>
+        <v>46298.5</v>
       </c>
       <c r="B50">
-        <v>3387.84</v>
+        <v>3451.039</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46299.51041666666</v>
+        <v>46298.51041666666</v>
       </c>
       <c r="B51">
-        <v>3377.45</v>
+        <v>3433.668</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46299.52083333334</v>
+        <v>46298.52083333334</v>
       </c>
       <c r="B52">
-        <v>3360.19</v>
+        <v>3420.693</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46299.53125</v>
+        <v>46298.53125</v>
       </c>
       <c r="B53">
-        <v>3330.88</v>
+        <v>3399.492</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46299.54166666666</v>
+        <v>46298.54166666666</v>
       </c>
       <c r="B54">
-        <v>3297.269</v>
+        <v>3355.819</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46299.55208333334</v>
+        <v>46298.55208333334</v>
       </c>
       <c r="B55">
-        <v>3253.336</v>
+        <v>3310.072</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46299.5625</v>
+        <v>46298.5625</v>
       </c>
       <c r="B56">
-        <v>3200.916</v>
+        <v>3251.246</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46299.57291666666</v>
+        <v>46298.57291666666</v>
       </c>
       <c r="B57">
-        <v>3138.313</v>
+        <v>3193.931</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46299.58333333334</v>
+        <v>46298.58333333334</v>
       </c>
       <c r="B58">
-        <v>3018.6</v>
+        <v>3082.772</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46299.59375</v>
+        <v>46298.59375</v>
       </c>
       <c r="B59">
-        <v>2923.411</v>
+        <v>2987.186</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46299.60416666666</v>
+        <v>46298.60416666666</v>
       </c>
       <c r="B60">
-        <v>2826.209</v>
+        <v>2864.465</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46299.61458333334</v>
+        <v>46298.61458333334</v>
       </c>
       <c r="B61">
-        <v>2731.052</v>
+        <v>2736.522</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46299.625</v>
+        <v>46298.625</v>
       </c>
       <c r="B62">
-        <v>2461.736</v>
+        <v>2494.313</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46299.63541666666</v>
+        <v>46298.63541666666</v>
       </c>
       <c r="B63">
-        <v>2279.912</v>
+        <v>2308.932</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46299.64583333334</v>
+        <v>46298.64583333334</v>
       </c>
       <c r="B64">
-        <v>2071.161</v>
+        <v>2082.994</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46299.65625</v>
+        <v>46298.65625</v>
       </c>
       <c r="B65">
-        <v>1851.096</v>
+        <v>1867.71</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46299.66666666666</v>
+        <v>46298.66666666666</v>
       </c>
       <c r="B66">
-        <v>1457.302</v>
+        <v>1460.85</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46299.67708333334</v>
+        <v>46298.67708333334</v>
       </c>
       <c r="B67">
-        <v>1201.027</v>
+        <v>1211.642</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46299.6875</v>
+        <v>46298.6875</v>
       </c>
       <c r="B68">
-        <v>932.765</v>
+        <v>941.423</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46299.69791666666</v>
+        <v>46298.69791666666</v>
       </c>
       <c r="B69">
-        <v>694.253</v>
+        <v>711.698</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46299.70833333334</v>
+        <v>46298.70833333334</v>
       </c>
       <c r="B70">
-        <v>378.203</v>
+        <v>409.568</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46299.71875</v>
+        <v>46298.71875</v>
       </c>
       <c r="B71">
-        <v>235.084</v>
+        <v>249.426</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46299.72916666666</v>
+        <v>46298.72916666666</v>
       </c>
       <c r="B72">
-        <v>113.12</v>
+        <v>134.19</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46299.73958333334</v>
+        <v>46298.73958333334</v>
       </c>
       <c r="B73">
-        <v>48.889</v>
+        <v>65.28100000000001</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46299.75</v>
+        <v>46298.75</v>
       </c>
       <c r="B74">
-        <v>14.25</v>
+        <v>17.138</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46299.76041666666</v>
+        <v>46298.76041666666</v>
       </c>
       <c r="B75">
-        <v>18.674</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46299.77083333334</v>
+        <v>46298.77083333334</v>
       </c>
       <c r="B76">
-        <v>17.586</v>
+        <v>70.249</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46299.78125</v>
+        <v>46298.78125</v>
       </c>
       <c r="B77">
-        <v>66.206</v>
+        <v>73.105</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46299.79166666666</v>
+        <v>46298.79166666666</v>
       </c>
       <c r="B78">
-        <v>65.068</v>
+        <v>69.982</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46299.80208333334</v>
+        <v>46298.80208333334</v>
       </c>
       <c r="B79">
-        <v>65.16800000000001</v>
+        <v>70.88200000000001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46299.8125</v>
+        <v>46298.8125</v>
       </c>
       <c r="B80">
-        <v>63.168</v>
+        <v>68.268</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46299.82291666666</v>
+        <v>46298.82291666666</v>
       </c>
       <c r="B81">
-        <v>61.624</v>
+        <v>67.724</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46299.83333333334</v>
+        <v>46298.83333333334</v>
       </c>
       <c r="B82">
-        <v>55.184</v>
+        <v>60.584</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46299.84375</v>
+        <v>46298.84375</v>
       </c>
       <c r="B83">
-        <v>54.084</v>
+        <v>60.084</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46299.85416666666</v>
+        <v>46298.85416666666</v>
       </c>
       <c r="B84">
-        <v>52.384</v>
+        <v>12.484</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46299.86458333334</v>
+        <v>46298.86458333334</v>
       </c>
       <c r="B85">
-        <v>3.384</v>
+        <v>8.984</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46299.875</v>
+        <v>46298.875</v>
       </c>
       <c r="B86">
-        <v>1.884</v>
+        <v>5.884</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46299.88541666666</v>
+        <v>46298.88541666666</v>
       </c>
       <c r="B87">
-        <v>1.884</v>
+        <v>5.584</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46299.89583333334</v>
+        <v>46298.89583333334</v>
       </c>
       <c r="B88">
-        <v>1.88</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46299.90625</v>
+        <v>46298.90625</v>
       </c>
       <c r="B89">
-        <v>1.88</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46299.91666666666</v>
+        <v>46298.91666666666</v>
       </c>
       <c r="B90">
-        <v>1.88</v>
+        <v>4.98</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46299.92708333334</v>
+        <v>46298.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.88</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
+        <v>46298.9375</v>
+      </c>
+      <c r="B92">
+        <v>3.58</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
+        <v>46298.94791666666</v>
+      </c>
+      <c r="B93">
+        <v>3.48</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46298.95833333334</v>
+      </c>
+      <c r="B94">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2">
+        <v>46298.96875</v>
+      </c>
+      <c r="B95">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2">
+        <v>46298.97916666666</v>
+      </c>
+      <c r="B96">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="2">
+        <v>46298.98958333334</v>
+      </c>
+      <c r="B97">
+        <v>1.084</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B98">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="2">
+        <v>46299.01041666666</v>
+      </c>
+      <c r="B99">
+        <v>1.084</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="2">
+        <v>46299.02083333334</v>
+      </c>
+      <c r="B100">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="2">
+        <v>46299.03125</v>
+      </c>
+      <c r="B101">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="2">
+        <v>46299.04166666666</v>
+      </c>
+      <c r="B102">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="2">
+        <v>46299.05208333334</v>
+      </c>
+      <c r="B103">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="2">
+        <v>46299.0625</v>
+      </c>
+      <c r="B104">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="2">
+        <v>46299.07291666666</v>
+      </c>
+      <c r="B105">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="2">
+        <v>46299.08333333334</v>
+      </c>
+      <c r="B106">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="2">
+        <v>46299.09375</v>
+      </c>
+      <c r="B107">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="2">
+        <v>46299.10416666666</v>
+      </c>
+      <c r="B108">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="2">
+        <v>46299.11458333334</v>
+      </c>
+      <c r="B109">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="2">
+        <v>46299.125</v>
+      </c>
+      <c r="B110">
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="2">
+        <v>46299.13541666666</v>
+      </c>
+      <c r="B111">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="2">
+        <v>46299.14583333334</v>
+      </c>
+      <c r="B112">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="2">
+        <v>46299.15625</v>
+      </c>
+      <c r="B113">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="2">
+        <v>46299.16666666666</v>
+      </c>
+      <c r="B114">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="2">
+        <v>46299.17708333334</v>
+      </c>
+      <c r="B115">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="2">
+        <v>46299.1875</v>
+      </c>
+      <c r="B116">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="2">
+        <v>46299.19791666666</v>
+      </c>
+      <c r="B117">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="2">
+        <v>46299.20833333334</v>
+      </c>
+      <c r="B118">
+        <v>5.179</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="2">
+        <v>46299.21875</v>
+      </c>
+      <c r="B119">
+        <v>5.295</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="2">
+        <v>46299.22916666666</v>
+      </c>
+      <c r="B120">
+        <v>5.398</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="2">
+        <v>46299.23958333334</v>
+      </c>
+      <c r="B121">
+        <v>5.565</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" s="2">
+        <v>46299.25</v>
+      </c>
+      <c r="B122">
+        <v>15.895</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="2">
+        <v>46299.26041666666</v>
+      </c>
+      <c r="B123">
+        <v>18.851</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" s="2">
+        <v>46299.27083333334</v>
+      </c>
+      <c r="B124">
+        <v>54.017</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="2">
+        <v>46299.28125</v>
+      </c>
+      <c r="B125">
+        <v>146.109</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" s="2">
+        <v>46299.29166666666</v>
+      </c>
+      <c r="B126">
+        <v>426.098</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="2">
+        <v>46299.30208333334</v>
+      </c>
+      <c r="B127">
+        <v>633.59</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" s="2">
+        <v>46299.3125</v>
+      </c>
+      <c r="B128">
+        <v>857.647</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="2">
+        <v>46299.32291666666</v>
+      </c>
+      <c r="B129">
+        <v>1093.743</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" s="2">
+        <v>46299.33333333334</v>
+      </c>
+      <c r="B130">
+        <v>1542.282</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="2">
+        <v>46299.34375</v>
+      </c>
+      <c r="B131">
+        <v>1794.591</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="2">
+        <v>46299.35416666666</v>
+      </c>
+      <c r="B132">
+        <v>2051.985</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="2">
+        <v>46299.36458333334</v>
+      </c>
+      <c r="B133">
+        <v>2284.662</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="2">
+        <v>46299.375</v>
+      </c>
+      <c r="B134">
+        <v>2651.428</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="2">
+        <v>46299.38541666666</v>
+      </c>
+      <c r="B135">
+        <v>2825.262</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="2">
+        <v>46299.39583333334</v>
+      </c>
+      <c r="B136">
+        <v>3005.977</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="2">
+        <v>46299.40625</v>
+      </c>
+      <c r="B137">
+        <v>3116.493</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" s="2">
+        <v>46299.41666666666</v>
+      </c>
+      <c r="B138">
+        <v>3287.693</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="2">
+        <v>46299.42708333334</v>
+      </c>
+      <c r="B139">
+        <v>3366.795</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="2">
+        <v>46299.4375</v>
+      </c>
+      <c r="B140">
+        <v>3424.73</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="2">
+        <v>46299.44791666666</v>
+      </c>
+      <c r="B141">
+        <v>3438.371</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="2">
+        <v>46299.45833333334</v>
+      </c>
+      <c r="B142">
+        <v>3449.123</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="2">
+        <v>46299.46875</v>
+      </c>
+      <c r="B143">
+        <v>3474.524</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="2">
+        <v>46299.47916666666</v>
+      </c>
+      <c r="B144">
+        <v>3482.02</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="2">
+        <v>46299.48958333334</v>
+      </c>
+      <c r="B145">
+        <v>3479.513</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="2">
+        <v>46299.5</v>
+      </c>
+      <c r="B146">
+        <v>3467.627</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="2">
+        <v>46299.51041666666</v>
+      </c>
+      <c r="B147">
+        <v>3462.126</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="2">
+        <v>46299.52083333334</v>
+      </c>
+      <c r="B148">
+        <v>3455.392</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="2">
+        <v>46299.53125</v>
+      </c>
+      <c r="B149">
+        <v>3423.806</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="2">
+        <v>46299.54166666666</v>
+      </c>
+      <c r="B150">
+        <v>3408.338</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="2">
+        <v>46299.55208333334</v>
+      </c>
+      <c r="B151">
+        <v>3360.871</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="2">
+        <v>46299.5625</v>
+      </c>
+      <c r="B152">
+        <v>3301.957</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="2">
+        <v>46299.57291666666</v>
+      </c>
+      <c r="B153">
+        <v>3238.946</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="2">
+        <v>46299.58333333334</v>
+      </c>
+      <c r="B154">
+        <v>3144.104</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="2">
+        <v>46299.59375</v>
+      </c>
+      <c r="B155">
+        <v>3031.715</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="2">
+        <v>46299.60416666666</v>
+      </c>
+      <c r="B156">
+        <v>2912.475</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="2">
+        <v>46299.61458333334</v>
+      </c>
+      <c r="B157">
+        <v>2802.887</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="2">
+        <v>46299.625</v>
+      </c>
+      <c r="B158">
+        <v>2546.279</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="2">
+        <v>46299.63541666666</v>
+      </c>
+      <c r="B159">
+        <v>2357.005</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="2">
+        <v>46299.64583333334</v>
+      </c>
+      <c r="B160">
+        <v>2141.6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="2">
+        <v>46299.65625</v>
+      </c>
+      <c r="B161">
+        <v>1923.587</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="2">
+        <v>46299.66666666666</v>
+      </c>
+      <c r="B162">
+        <v>1538.392</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="2">
+        <v>46299.67708333334</v>
+      </c>
+      <c r="B163">
+        <v>1281.551</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="2">
+        <v>46299.6875</v>
+      </c>
+      <c r="B164">
+        <v>987.958</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="2">
+        <v>46299.69791666666</v>
+      </c>
+      <c r="B165">
+        <v>747.318</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="2">
+        <v>46299.70833333334</v>
+      </c>
+      <c r="B166">
+        <v>452.429</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="2">
+        <v>46299.71875</v>
+      </c>
+      <c r="B167">
+        <v>286.726</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="2">
+        <v>46299.72916666666</v>
+      </c>
+      <c r="B168">
+        <v>128.174</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="2">
+        <v>46299.73958333334</v>
+      </c>
+      <c r="B169">
+        <v>58.757</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="2">
+        <v>46299.75</v>
+      </c>
+      <c r="B170">
+        <v>57.35</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="2">
+        <v>46299.76041666666</v>
+      </c>
+      <c r="B171">
+        <v>27.774</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="2">
+        <v>46299.77083333334</v>
+      </c>
+      <c r="B172">
+        <v>26.686</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="2">
+        <v>46299.78125</v>
+      </c>
+      <c r="B173">
+        <v>27.806</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="2">
+        <v>46299.79166666666</v>
+      </c>
+      <c r="B174">
+        <v>24.378</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="2">
+        <v>46299.80208333334</v>
+      </c>
+      <c r="B175">
+        <v>24.478</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="2">
+        <v>46299.8125</v>
+      </c>
+      <c r="B176">
+        <v>22.478</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="2">
+        <v>46299.82291666666</v>
+      </c>
+      <c r="B177">
+        <v>20.734</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="2">
+        <v>46299.83333333334</v>
+      </c>
+      <c r="B178">
+        <v>13.087</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="2">
+        <v>46299.84375</v>
+      </c>
+      <c r="B179">
+        <v>11.587</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="2">
+        <v>46299.85416666666</v>
+      </c>
+      <c r="B180">
+        <v>9.887</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="2">
+        <v>46299.86458333334</v>
+      </c>
+      <c r="B181">
+        <v>7.987</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="2">
+        <v>46299.875</v>
+      </c>
+      <c r="B182">
+        <v>8.686999999999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="2">
+        <v>46299.88541666666</v>
+      </c>
+      <c r="B183">
+        <v>7.084</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="2">
+        <v>46299.89583333334</v>
+      </c>
+      <c r="B184">
+        <v>6.28</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="2">
+        <v>46299.90625</v>
+      </c>
+      <c r="B185">
+        <v>5.18</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="2">
+        <v>46299.91666666666</v>
+      </c>
+      <c r="B186">
+        <v>6.08</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="2">
+        <v>46299.92708333334</v>
+      </c>
+      <c r="B187">
+        <v>5.88</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="2">
         <v>46299.9375</v>
       </c>
-      <c r="B92">
+      <c r="B188">
+        <v>4.78</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="2">
+        <v>46299.94791666666</v>
+      </c>
+      <c r="B189">
+        <v>4.18</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2">
+        <v>46299.95833333334</v>
+      </c>
+      <c r="B190">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2">
+        <v>46299.96875</v>
+      </c>
+      <c r="B191">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2">
+        <v>46299.97916666666</v>
+      </c>
+      <c r="B192">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2">
+        <v>46299.98958333334</v>
+      </c>
+      <c r="B193">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B194">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2">
+        <v>46300.01041666666</v>
+      </c>
+      <c r="B195">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2">
+        <v>46300.02083333334</v>
+      </c>
+      <c r="B196">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2">
+        <v>46300.03125</v>
+      </c>
+      <c r="B197">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2">
+        <v>46300.04166666666</v>
+      </c>
+      <c r="B198">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2">
+        <v>46300.05208333334</v>
+      </c>
+      <c r="B199">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2">
+        <v>46300.0625</v>
+      </c>
+      <c r="B200">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2">
+        <v>46300.07291666666</v>
+      </c>
+      <c r="B201">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2">
+        <v>46300.08333333334</v>
+      </c>
+      <c r="B202">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2">
+        <v>46300.09375</v>
+      </c>
+      <c r="B203">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2">
+        <v>46300.10416666666</v>
+      </c>
+      <c r="B204">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2">
+        <v>46300.11458333334</v>
+      </c>
+      <c r="B205">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2">
+        <v>46300.125</v>
+      </c>
+      <c r="B206">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2">
+        <v>46300.13541666666</v>
+      </c>
+      <c r="B207">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2">
+        <v>46300.14583333334</v>
+      </c>
+      <c r="B208">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2">
+        <v>46300.15625</v>
+      </c>
+      <c r="B209">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2">
+        <v>46300.16666666666</v>
+      </c>
+      <c r="B210">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2">
+        <v>46300.17708333334</v>
+      </c>
+      <c r="B211">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2">
+        <v>46300.1875</v>
+      </c>
+      <c r="B212">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2">
+        <v>46300.19791666666</v>
+      </c>
+      <c r="B213">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2">
+        <v>46300.20833333334</v>
+      </c>
+      <c r="B214">
+        <v>5.688</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2">
+        <v>46300.21875</v>
+      </c>
+      <c r="B215">
+        <v>6.219</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2">
+        <v>46300.22916666666</v>
+      </c>
+      <c r="B216">
+        <v>7.044</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2">
+        <v>46300.23958333334</v>
+      </c>
+      <c r="B217">
+        <v>9.321</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2">
+        <v>46300.25</v>
+      </c>
+      <c r="B218">
+        <v>70.337</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2">
+        <v>46300.26041666666</v>
+      </c>
+      <c r="B219">
+        <v>75.94799999999999</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2">
+        <v>46300.27083333334</v>
+      </c>
+      <c r="B220">
+        <v>109.456</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2">
+        <v>46300.28125</v>
+      </c>
+      <c r="B221">
+        <v>205.043</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2">
+        <v>46300.29166666666</v>
+      </c>
+      <c r="B222">
+        <v>443.22</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2">
+        <v>46300.30208333334</v>
+      </c>
+      <c r="B223">
+        <v>630.162</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2">
+        <v>46300.3125</v>
+      </c>
+      <c r="B224">
+        <v>868.883</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2">
+      <c r="A225" s="2">
+        <v>46300.32291666666</v>
+      </c>
+      <c r="B225">
+        <v>1095.102</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2">
+      <c r="A226" s="2">
+        <v>46300.33333333334</v>
+      </c>
+      <c r="B226">
+        <v>1576.764</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2">
+      <c r="A227" s="2">
+        <v>46300.34375</v>
+      </c>
+      <c r="B227">
+        <v>1821.818</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2">
+      <c r="A228" s="2">
+        <v>46300.35416666666</v>
+      </c>
+      <c r="B228">
+        <v>2129.922</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2">
+      <c r="A229" s="2">
+        <v>46300.36458333334</v>
+      </c>
+      <c r="B229">
+        <v>2359.078</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2">
+      <c r="A230" s="2">
+        <v>46300.375</v>
+      </c>
+      <c r="B230">
+        <v>2808.149</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2">
+      <c r="A231" s="2">
+        <v>46300.38541666666</v>
+      </c>
+      <c r="B231">
+        <v>3002.086</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2">
+      <c r="A232" s="2">
+        <v>46300.39583333334</v>
+      </c>
+      <c r="B232">
+        <v>3147.549</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2">
+      <c r="A233" s="2">
+        <v>46300.40625</v>
+      </c>
+      <c r="B233">
+        <v>3287.528</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2">
+      <c r="A234" s="2">
+        <v>46300.41666666666</v>
+      </c>
+      <c r="B234">
+        <v>3491.577</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2">
+      <c r="A235" s="2">
+        <v>46300.42708333334</v>
+      </c>
+      <c r="B235">
+        <v>3556.852</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2">
+      <c r="A236" s="2">
+        <v>46300.4375</v>
+      </c>
+      <c r="B236">
+        <v>3596.975</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2">
+      <c r="A237" s="2">
+        <v>46300.44791666666</v>
+      </c>
+      <c r="B237">
+        <v>3646.434</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2">
+      <c r="A238" s="2">
+        <v>46300.45833333334</v>
+      </c>
+      <c r="B238">
+        <v>3683.278</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2">
+      <c r="A239" s="2">
+        <v>46300.46875</v>
+      </c>
+      <c r="B239">
+        <v>3700.468</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2">
+      <c r="A240" s="2">
+        <v>46300.47916666666</v>
+      </c>
+      <c r="B240">
+        <v>3711.903</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2">
+      <c r="A241" s="2">
+        <v>46300.48958333334</v>
+      </c>
+      <c r="B241">
+        <v>3722.611</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2">
+      <c r="A242" s="2">
+        <v>46300.5</v>
+      </c>
+      <c r="B242">
+        <v>3716.808</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2">
+      <c r="A243" s="2">
+        <v>46300.51041666666</v>
+      </c>
+      <c r="B243">
+        <v>3718.804</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2">
+      <c r="A244" s="2">
+        <v>46300.52083333334</v>
+      </c>
+      <c r="B244">
+        <v>3697.112</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2">
+      <c r="A245" s="2">
+        <v>46300.53125</v>
+      </c>
+      <c r="B245">
+        <v>3699.713</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2">
+      <c r="A246" s="2">
+        <v>46300.54166666666</v>
+      </c>
+      <c r="B246">
+        <v>3626.544</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2">
+      <c r="A247" s="2">
+        <v>46300.55208333334</v>
+      </c>
+      <c r="B247">
+        <v>3588.98</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2">
+      <c r="A248" s="2">
+        <v>46300.5625</v>
+      </c>
+      <c r="B248">
+        <v>3517.663</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2">
+      <c r="A249" s="2">
+        <v>46300.57291666666</v>
+      </c>
+      <c r="B249">
+        <v>3436.465</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2">
+      <c r="A250" s="2">
+        <v>46300.58333333334</v>
+      </c>
+      <c r="B250">
+        <v>3282.264</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2">
+      <c r="A251" s="2">
+        <v>46300.59375</v>
+      </c>
+      <c r="B251">
+        <v>3172.71</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2">
+      <c r="A252" s="2">
+        <v>46300.60416666666</v>
+      </c>
+      <c r="B252">
+        <v>3017.812</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2">
+      <c r="A253" s="2">
+        <v>46300.61458333334</v>
+      </c>
+      <c r="B253">
+        <v>2855.603</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2">
+      <c r="A254" s="2">
+        <v>46300.625</v>
+      </c>
+      <c r="B254">
+        <v>2544.374</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2">
+      <c r="A255" s="2">
+        <v>46300.63541666666</v>
+      </c>
+      <c r="B255">
+        <v>2330.172</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2">
+      <c r="A256" s="2">
+        <v>46300.64583333334</v>
+      </c>
+      <c r="B256">
+        <v>2066.325</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2">
+      <c r="A257" s="2">
+        <v>46300.65625</v>
+      </c>
+      <c r="B257">
+        <v>1817.147</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2">
+      <c r="A258" s="2">
+        <v>46300.66666666666</v>
+      </c>
+      <c r="B258">
+        <v>1472.074</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2">
+      <c r="A259" s="2">
+        <v>46300.67708333334</v>
+      </c>
+      <c r="B259">
+        <v>1216.172</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2">
+      <c r="A260" s="2">
+        <v>46300.6875</v>
+      </c>
+      <c r="B260">
+        <v>955.5940000000001</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2">
+      <c r="A261" s="2">
+        <v>46300.69791666666</v>
+      </c>
+      <c r="B261">
+        <v>730.602</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2">
+      <c r="A262" s="2">
+        <v>46300.70833333334</v>
+      </c>
+      <c r="B262">
+        <v>391.085</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2">
+      <c r="A263" s="2">
+        <v>46300.71875</v>
+      </c>
+      <c r="B263">
+        <v>253.619</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2">
+      <c r="A264" s="2">
+        <v>46300.72916666666</v>
+      </c>
+      <c r="B264">
+        <v>144.224</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2">
+      <c r="A265" s="2">
+        <v>46300.73958333334</v>
+      </c>
+      <c r="B265">
+        <v>80.27</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2">
+      <c r="A266" s="2">
+        <v>46300.75</v>
+      </c>
+      <c r="B266">
+        <v>87.818</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2">
+      <c r="A267" s="2">
+        <v>46300.76041666666</v>
+      </c>
+      <c r="B267">
+        <v>83.938</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2">
+      <c r="A268" s="2">
+        <v>46300.77083333334</v>
+      </c>
+      <c r="B268">
+        <v>82.89700000000001</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2">
+      <c r="A269" s="2">
+        <v>46300.78125</v>
+      </c>
+      <c r="B269">
+        <v>84.43300000000001</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2">
+      <c r="A270" s="2">
+        <v>46300.79166666666</v>
+      </c>
+      <c r="B270">
+        <v>84.76000000000001</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2">
+      <c r="A271" s="2">
+        <v>46300.80208333334</v>
+      </c>
+      <c r="B271">
+        <v>84.66</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2">
+      <c r="A272" s="2">
+        <v>46300.8125</v>
+      </c>
+      <c r="B272">
+        <v>82.863</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2">
+      <c r="A273" s="2">
+        <v>46300.82291666666</v>
+      </c>
+      <c r="B273">
+        <v>81.319</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2">
+      <c r="A274" s="2">
+        <v>46300.83333333334</v>
+      </c>
+      <c r="B274">
+        <v>25.683</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2">
+      <c r="A275" s="2">
+        <v>46300.84375</v>
+      </c>
+      <c r="B275">
+        <v>21.083</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2">
+      <c r="A276" s="2">
+        <v>46300.85416666666</v>
+      </c>
+      <c r="B276">
+        <v>19.683</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2">
+      <c r="A277" s="2">
+        <v>46300.86458333334</v>
+      </c>
+      <c r="B277">
+        <v>22.783</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2">
+      <c r="A278" s="2">
+        <v>46300.875</v>
+      </c>
+      <c r="B278">
+        <v>15.383</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2">
+      <c r="A279" s="2">
+        <v>46300.88541666666</v>
+      </c>
+      <c r="B279">
+        <v>14.38</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2">
+      <c r="A280" s="2">
+        <v>46300.89583333334</v>
+      </c>
+      <c r="B280">
+        <v>19.68</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2">
+      <c r="A281" s="2">
+        <v>46300.90625</v>
+      </c>
+      <c r="B281">
+        <v>15.18</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2">
+      <c r="A282" s="2">
+        <v>46300.91666666666</v>
+      </c>
+      <c r="B282">
+        <v>14.58</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2">
+      <c r="A283" s="2">
+        <v>46300.92708333334</v>
+      </c>
+      <c r="B283">
+        <v>18.48</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2">
+      <c r="A284" s="2">
+        <v>46300.9375</v>
+      </c>
+      <c r="B284">
+        <v>18.48</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2">
+      <c r="A285" s="2">
+        <v>46300.94791666666</v>
+      </c>
+      <c r="B285">
+        <v>14.58</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2">
+      <c r="A286" s="2">
+        <v>46300.95833333334</v>
+      </c>
+      <c r="B286">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2">
+      <c r="A287" s="2">
+        <v>46300.96875</v>
+      </c>
+      <c r="B287">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2">
+      <c r="A288" s="2">
+        <v>46300.97916666666</v>
+      </c>
+      <c r="B288">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2">
+      <c r="A289" s="2">
+        <v>46300.98958333334</v>
+      </c>
+      <c r="B289">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2">
+      <c r="A290" s="2">
+        <v>46301</v>
+      </c>
+      <c r="B290">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2">
+      <c r="A291" s="2">
+        <v>46301.01041666666</v>
+      </c>
+      <c r="B291">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2">
+      <c r="A292" s="2">
+        <v>46301.02083333334</v>
+      </c>
+      <c r="B292">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2">
+      <c r="A293" s="2">
+        <v>46301.03125</v>
+      </c>
+      <c r="B293">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2">
+      <c r="A294" s="2">
+        <v>46301.04166666666</v>
+      </c>
+      <c r="B294">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2">
+      <c r="A295" s="2">
+        <v>46301.05208333334</v>
+      </c>
+      <c r="B295">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2">
+      <c r="A296" s="2">
+        <v>46301.0625</v>
+      </c>
+      <c r="B296">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2">
+      <c r="A297" s="2">
+        <v>46301.07291666666</v>
+      </c>
+      <c r="B297">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2">
+      <c r="A298" s="2">
+        <v>46301.08333333334</v>
+      </c>
+      <c r="B298">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2">
+      <c r="A299" s="2">
+        <v>46301.09375</v>
+      </c>
+      <c r="B299">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2">
+      <c r="A300" s="2">
+        <v>46301.10416666666</v>
+      </c>
+      <c r="B300">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2">
+      <c r="A301" s="2">
+        <v>46301.11458333334</v>
+      </c>
+      <c r="B301">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2">
+      <c r="A302" s="2">
+        <v>46301.125</v>
+      </c>
+      <c r="B302">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2">
+      <c r="A303" s="2">
+        <v>46301.13541666666</v>
+      </c>
+      <c r="B303">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2">
+      <c r="A304" s="2">
+        <v>46301.14583333334</v>
+      </c>
+      <c r="B304">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2">
+      <c r="A305" s="2">
+        <v>46301.15625</v>
+      </c>
+      <c r="B305">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2">
+      <c r="A306" s="2">
+        <v>46301.16666666666</v>
+      </c>
+      <c r="B306">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2">
+      <c r="A307" s="2">
+        <v>46301.17708333334</v>
+      </c>
+      <c r="B307">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2">
+      <c r="A308" s="2">
+        <v>46301.1875</v>
+      </c>
+      <c r="B308">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2">
+      <c r="A309" s="2">
+        <v>46301.19791666666</v>
+      </c>
+      <c r="B309">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2">
+      <c r="A310" s="2">
+        <v>46301.20833333334</v>
+      </c>
+      <c r="B310">
+        <v>4.624</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2">
+      <c r="A311" s="2">
+        <v>46301.21875</v>
+      </c>
+      <c r="B311">
+        <v>5.093</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2">
+      <c r="A312" s="2">
+        <v>46301.22916666666</v>
+      </c>
+      <c r="B312">
+        <v>5.891</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2">
+      <c r="A313" s="2">
+        <v>46301.23958333334</v>
+      </c>
+      <c r="B313">
+        <v>7.157</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2">
+      <c r="A314" s="2">
+        <v>46301.25</v>
+      </c>
+      <c r="B314">
+        <v>18.752</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2">
+      <c r="A315" s="2">
+        <v>46301.26041666666</v>
+      </c>
+      <c r="B315">
+        <v>21.908</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2">
+      <c r="A316" s="2">
+        <v>46301.27083333334</v>
+      </c>
+      <c r="B316">
+        <v>48.13</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2">
+      <c r="A317" s="2">
+        <v>46301.28125</v>
+      </c>
+      <c r="B317">
+        <v>122.106</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2">
+      <c r="A318" s="2">
+        <v>46301.29166666666</v>
+      </c>
+      <c r="B318">
+        <v>388.159</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2">
+      <c r="A319" s="2">
+        <v>46301.30208333334</v>
+      </c>
+      <c r="B319">
+        <v>558.537</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2">
+      <c r="A320" s="2">
+        <v>46301.3125</v>
+      </c>
+      <c r="B320">
+        <v>777.186</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2">
+      <c r="A321" s="2">
+        <v>46301.32291666666</v>
+      </c>
+      <c r="B321">
+        <v>990.5069999999999</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2">
+      <c r="A322" s="2">
+        <v>46301.33333333334</v>
+      </c>
+      <c r="B322">
+        <v>1378.698</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2">
+      <c r="A323" s="2">
+        <v>46301.34375</v>
+      </c>
+      <c r="B323">
+        <v>1626.804</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2">
+      <c r="A324" s="2">
+        <v>46301.35416666666</v>
+      </c>
+      <c r="B324">
+        <v>1903.422</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2">
+      <c r="A325" s="2">
+        <v>46301.36458333334</v>
+      </c>
+      <c r="B325">
+        <v>2112.801</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2">
+      <c r="A326" s="2">
+        <v>46301.375</v>
+      </c>
+      <c r="B326">
+        <v>2528.509</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2">
+      <c r="A327" s="2">
+        <v>46301.38541666666</v>
+      </c>
+      <c r="B327">
+        <v>2723.344</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2">
+      <c r="A328" s="2">
+        <v>46301.39583333334</v>
+      </c>
+      <c r="B328">
+        <v>2893.649</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2">
+      <c r="A329" s="2">
+        <v>46301.40625</v>
+      </c>
+      <c r="B329">
+        <v>3034.096</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2">
+      <c r="A330" s="2">
+        <v>46301.41666666666</v>
+      </c>
+      <c r="B330">
+        <v>3246.238</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2">
+      <c r="A331" s="2">
+        <v>46301.42708333334</v>
+      </c>
+      <c r="B331">
+        <v>3382.759</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2">
+      <c r="A332" s="2">
+        <v>46301.4375</v>
+      </c>
+      <c r="B332">
+        <v>3364.861</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2">
+      <c r="A333" s="2">
+        <v>46301.44791666666</v>
+      </c>
+      <c r="B333">
+        <v>3424.585</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2">
+      <c r="A334" s="2">
+        <v>46301.45833333334</v>
+      </c>
+      <c r="B334">
+        <v>3486.743</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2">
+      <c r="A335" s="2">
+        <v>46301.46875</v>
+      </c>
+      <c r="B335">
+        <v>3522.212</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2">
+      <c r="A336" s="2">
+        <v>46301.47916666666</v>
+      </c>
+      <c r="B336">
+        <v>3551.865</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2">
+      <c r="A337" s="2">
+        <v>46301.48958333334</v>
+      </c>
+      <c r="B337">
+        <v>3563.275</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2">
+      <c r="A338" s="2">
+        <v>46301.5</v>
+      </c>
+      <c r="B338">
+        <v>3565.904</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2">
+      <c r="A339" s="2">
+        <v>46301.51041666666</v>
+      </c>
+      <c r="B339">
+        <v>3573.573</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2">
+      <c r="A340" s="2">
+        <v>46301.52083333334</v>
+      </c>
+      <c r="B340">
+        <v>3553.887</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2">
+      <c r="A341" s="2">
+        <v>46301.53125</v>
+      </c>
+      <c r="B341">
+        <v>3494.556</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2">
+      <c r="A342" s="2">
+        <v>46301.54166666666</v>
+      </c>
+      <c r="B342">
+        <v>3430.246</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2">
+      <c r="A343" s="2">
+        <v>46301.55208333334</v>
+      </c>
+      <c r="B343">
+        <v>3387.734</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2">
+      <c r="A344" s="2">
+        <v>46301.5625</v>
+      </c>
+      <c r="B344">
+        <v>3336.574</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2">
+      <c r="A345" s="2">
+        <v>46301.57291666666</v>
+      </c>
+      <c r="B345">
+        <v>3270.589</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2">
+      <c r="A346" s="2">
+        <v>46301.58333333334</v>
+      </c>
+      <c r="B346">
+        <v>3145.063</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2">
+      <c r="A347" s="2">
+        <v>46301.59375</v>
+      </c>
+      <c r="B347">
+        <v>3048.558</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2">
+      <c r="A348" s="2">
+        <v>46301.60416666666</v>
+      </c>
+      <c r="B348">
+        <v>2933.53</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2">
+      <c r="A349" s="2">
+        <v>46301.61458333334</v>
+      </c>
+      <c r="B349">
+        <v>2787.888</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2">
+      <c r="A350" s="2">
+        <v>46301.625</v>
+      </c>
+      <c r="B350">
+        <v>2485.777</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2">
+      <c r="A351" s="2">
+        <v>46301.63541666666</v>
+      </c>
+      <c r="B351">
+        <v>2275.508</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2">
+      <c r="A352" s="2">
+        <v>46301.64583333334</v>
+      </c>
+      <c r="B352">
+        <v>2026.972</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2">
+      <c r="A353" s="2">
+        <v>46301.65625</v>
+      </c>
+      <c r="B353">
+        <v>1802.388</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2">
+      <c r="A354" s="2">
+        <v>46301.66666666666</v>
+      </c>
+      <c r="B354">
+        <v>1418.782</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2">
+      <c r="A355" s="2">
+        <v>46301.67708333334</v>
+      </c>
+      <c r="B355">
+        <v>1159.825</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2">
+      <c r="A356" s="2">
+        <v>46301.6875</v>
+      </c>
+      <c r="B356">
+        <v>908.866</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2">
+      <c r="A357" s="2">
+        <v>46301.69791666666</v>
+      </c>
+      <c r="B357">
+        <v>680.451</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2">
+      <c r="A358" s="2">
+        <v>46301.70833333334</v>
+      </c>
+      <c r="B358">
+        <v>358.868</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2">
+      <c r="A359" s="2">
+        <v>46301.71875</v>
+      </c>
+      <c r="B359">
+        <v>230.517</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2">
+      <c r="A360" s="2">
+        <v>46301.72916666666</v>
+      </c>
+      <c r="B360">
+        <v>119.57</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2">
+      <c r="A361" s="2">
+        <v>46301.73958333334</v>
+      </c>
+      <c r="B361">
+        <v>72.40300000000001</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2">
+      <c r="A362" s="2">
+        <v>46301.75</v>
+      </c>
+      <c r="B362">
+        <v>87.947</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2">
+      <c r="A363" s="2">
+        <v>46301.76041666666</v>
+      </c>
+      <c r="B363">
+        <v>94.232</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2">
+      <c r="A364" s="2">
+        <v>46301.77083333334</v>
+      </c>
+      <c r="B364">
+        <v>96.188</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2">
+      <c r="A365" s="2">
+        <v>46301.78125</v>
+      </c>
+      <c r="B365">
+        <v>95.67400000000001</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2">
+      <c r="A366" s="2">
+        <v>46301.79166666666</v>
+      </c>
+      <c r="B366">
+        <v>90.76000000000001</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2">
+      <c r="A367" s="2">
+        <v>46301.80208333334</v>
+      </c>
+      <c r="B367">
+        <v>89.685</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2">
+      <c r="A368" s="2">
+        <v>46301.8125</v>
+      </c>
+      <c r="B368">
+        <v>88.66</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2">
+      <c r="A369" s="2">
+        <v>46301.82291666666</v>
+      </c>
+      <c r="B369">
+        <v>83.66</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2">
+      <c r="A370" s="2">
+        <v>46301.83333333334</v>
+      </c>
+      <c r="B370">
+        <v>27.38</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2">
+      <c r="A371" s="2">
+        <v>46301.84375</v>
+      </c>
+      <c r="B371">
+        <v>26.58</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2">
+      <c r="A372" s="2">
+        <v>46301.85416666666</v>
+      </c>
+      <c r="B372">
+        <v>12.18</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2">
+      <c r="A373" s="2">
+        <v>46301.86458333334</v>
+      </c>
+      <c r="B373">
+        <v>25.18</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2">
+      <c r="A374" s="2">
+        <v>46301.875</v>
+      </c>
+      <c r="B374">
+        <v>9.68</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2">
+      <c r="A375" s="2">
+        <v>46301.88541666666</v>
+      </c>
+      <c r="B375">
+        <v>23.68</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2">
+      <c r="A376" s="2">
+        <v>46301.89583333334</v>
+      </c>
+      <c r="B376">
+        <v>23.18</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2">
+      <c r="A377" s="2">
+        <v>46301.90625</v>
+      </c>
+      <c r="B377">
+        <v>18.88</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2">
+      <c r="A378" s="2">
+        <v>46301.91666666666</v>
+      </c>
+      <c r="B378">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2">
+      <c r="A379" s="2">
+        <v>46301.92708333334</v>
+      </c>
+      <c r="B379">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2">
+      <c r="A380" s="2">
+        <v>46301.9375</v>
+      </c>
+      <c r="B380">
+        <v>11.08</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2">
+      <c r="A381" s="2">
+        <v>46301.94791666666</v>
+      </c>
+      <c r="B381">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2">
+      <c r="A382" s="2">
+        <v>46301.95833333334</v>
+      </c>
+      <c r="B382">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2">
+      <c r="A383" s="2">
+        <v>46301.96875</v>
+      </c>
+      <c r="B383">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2">
+      <c r="A384" s="2">
+        <v>46301.97916666666</v>
+      </c>
+      <c r="B384">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2">
+      <c r="A385" s="2">
+        <v>46301.98958333334</v>
+      </c>
+      <c r="B385">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2">
+      <c r="A386" s="2">
+        <v>46302</v>
+      </c>
+      <c r="B386">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2">
+      <c r="A387" s="2">
+        <v>46302.01041666666</v>
+      </c>
+      <c r="B387">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2">
+      <c r="A388" s="2">
+        <v>46302.02083333334</v>
+      </c>
+      <c r="B388">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2">
+      <c r="A389" s="2">
+        <v>46302.03125</v>
+      </c>
+      <c r="B389">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2">
+      <c r="A390" s="2">
+        <v>46302.04166666666</v>
+      </c>
+      <c r="B390">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2">
+      <c r="A391" s="2">
+        <v>46302.05208333334</v>
+      </c>
+      <c r="B391">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2">
+      <c r="A392" s="2">
+        <v>46302.0625</v>
+      </c>
+      <c r="B392">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2">
+      <c r="A393" s="2">
+        <v>46302.07291666666</v>
+      </c>
+      <c r="B393">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2">
+      <c r="A394" s="2">
+        <v>46302.08333333334</v>
+      </c>
+      <c r="B394">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2">
+      <c r="A395" s="2">
+        <v>46302.09375</v>
+      </c>
+      <c r="B395">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2">
+      <c r="A396" s="2">
+        <v>46302.10416666666</v>
+      </c>
+      <c r="B396">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2">
+      <c r="A397" s="2">
+        <v>46302.11458333334</v>
+      </c>
+      <c r="B397">
+        <v>1.16</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2">
+      <c r="A398" s="2">
+        <v>46302.125</v>
+      </c>
+      <c r="B398">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2">
+      <c r="A399" s="2">
+        <v>46302.13541666666</v>
+      </c>
+      <c r="B399">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2">
+      <c r="A400" s="2">
+        <v>46302.14583333334</v>
+      </c>
+      <c r="B400">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2">
+      <c r="A401" s="2">
+        <v>46302.15625</v>
+      </c>
+      <c r="B401">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2">
+      <c r="A402" s="2">
+        <v>46302.16666666666</v>
+      </c>
+      <c r="B402">
+        <v>1.081</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2">
+      <c r="A403" s="2">
+        <v>46302.17708333334</v>
+      </c>
+      <c r="B403">
+        <v>1.081</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2">
+      <c r="A404" s="2">
+        <v>46302.1875</v>
+      </c>
+      <c r="B404">
+        <v>1.081</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2">
+      <c r="A405" s="2">
+        <v>46302.19791666666</v>
+      </c>
+      <c r="B405">
+        <v>1.081</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2">
+      <c r="A406" s="2">
+        <v>46302.20833333334</v>
+      </c>
+      <c r="B406">
+        <v>1.126</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2">
+      <c r="A407" s="2">
+        <v>46302.21875</v>
+      </c>
+      <c r="B407">
+        <v>1.186</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2">
+      <c r="A408" s="2">
+        <v>46302.22916666666</v>
+      </c>
+      <c r="B408">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2">
+      <c r="A409" s="2">
+        <v>46302.23958333334</v>
+      </c>
+      <c r="B409">
+        <v>1.398</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2">
+      <c r="A410" s="2">
+        <v>46302.25</v>
+      </c>
+      <c r="B410">
+        <v>6.577</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2">
+      <c r="A411" s="2">
+        <v>46302.26041666666</v>
+      </c>
+      <c r="B411">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2">
+      <c r="A412" s="2">
+        <v>46302.27083333334</v>
+      </c>
+      <c r="B412">
+        <v>25.129</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2">
+      <c r="A413" s="2">
+        <v>46302.28125</v>
+      </c>
+      <c r="B413">
+        <v>90.494</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2">
+      <c r="A414" s="2">
+        <v>46302.29166666666</v>
+      </c>
+      <c r="B414">
+        <v>355.092</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2">
+      <c r="A415" s="2">
+        <v>46302.30208333334</v>
+      </c>
+      <c r="B415">
+        <v>513.593</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2">
+      <c r="A416" s="2">
+        <v>46302.3125</v>
+      </c>
+      <c r="B416">
+        <v>701.203</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2">
+      <c r="A417" s="2">
+        <v>46302.32291666666</v>
+      </c>
+      <c r="B417">
+        <v>897.447</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2">
+      <c r="A418" s="2">
+        <v>46302.33333333334</v>
+      </c>
+      <c r="B418">
+        <v>1315.768</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2">
+      <c r="A419" s="2">
+        <v>46302.34375</v>
+      </c>
+      <c r="B419">
+        <v>1537.795</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2">
+      <c r="A420" s="2">
+        <v>46302.35416666666</v>
+      </c>
+      <c r="B420">
+        <v>1805.559</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2">
+      <c r="A421" s="2">
+        <v>46302.36458333334</v>
+      </c>
+      <c r="B421">
+        <v>2020.392</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2">
+      <c r="A422" s="2">
+        <v>46302.375</v>
+      </c>
+      <c r="B422">
+        <v>2370.704</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2">
+      <c r="A423" s="2">
+        <v>46302.38541666666</v>
+      </c>
+      <c r="B423">
+        <v>2532.931</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2">
+      <c r="A424" s="2">
+        <v>46302.39583333334</v>
+      </c>
+      <c r="B424">
+        <v>2680.769</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2">
+      <c r="A425" s="2">
+        <v>46302.40625</v>
+      </c>
+      <c r="B425">
+        <v>2792.879</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2">
+      <c r="A426" s="2">
+        <v>46302.41666666666</v>
+      </c>
+      <c r="B426">
+        <v>2962.088</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2">
+      <c r="A427" s="2">
+        <v>46302.42708333334</v>
+      </c>
+      <c r="B427">
+        <v>3048.37</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2">
+      <c r="A428" s="2">
+        <v>46302.4375</v>
+      </c>
+      <c r="B428">
+        <v>3084.796</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2">
+      <c r="A429" s="2">
+        <v>46302.44791666666</v>
+      </c>
+      <c r="B429">
+        <v>3143.064</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2">
+      <c r="A430" s="2">
+        <v>46302.45833333334</v>
+      </c>
+      <c r="B430">
+        <v>3194.727</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2">
+      <c r="A431" s="2">
+        <v>46302.46875</v>
+      </c>
+      <c r="B431">
+        <v>3231.85</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2">
+      <c r="A432" s="2">
+        <v>46302.47916666666</v>
+      </c>
+      <c r="B432">
+        <v>3238.587</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2">
+      <c r="A433" s="2">
+        <v>46302.48958333334</v>
+      </c>
+      <c r="B433">
+        <v>3231.765</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2">
+      <c r="A434" s="2">
+        <v>46302.5</v>
+      </c>
+      <c r="B434">
+        <v>3224.09</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2">
+      <c r="A435" s="2">
+        <v>46302.51041666666</v>
+      </c>
+      <c r="B435">
+        <v>3221.94</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2">
+      <c r="A436" s="2">
+        <v>46302.52083333334</v>
+      </c>
+      <c r="B436">
+        <v>3197.811</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2">
+      <c r="A437" s="2">
+        <v>46302.53125</v>
+      </c>
+      <c r="B437">
+        <v>3154.602</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2">
+      <c r="A438" s="2">
+        <v>46302.54166666666</v>
+      </c>
+      <c r="B438">
+        <v>3101.591</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2">
+      <c r="A439" s="2">
+        <v>46302.55208333334</v>
+      </c>
+      <c r="B439">
+        <v>3049.772</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2">
+      <c r="A440" s="2">
+        <v>46302.5625</v>
+      </c>
+      <c r="B440">
+        <v>2978.25</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2">
+      <c r="A441" s="2">
+        <v>46302.57291666666</v>
+      </c>
+      <c r="B441">
+        <v>2889.75</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2">
+      <c r="A442" s="2">
+        <v>46302.58333333334</v>
+      </c>
+      <c r="B442">
+        <v>2746.633</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2">
+      <c r="A443" s="2">
+        <v>46302.59375</v>
+      </c>
+      <c r="B443">
+        <v>2647.392</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2">
+      <c r="A444" s="2">
+        <v>46302.60416666666</v>
+      </c>
+      <c r="B444">
+        <v>2552.551</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2">
+      <c r="A445" s="2">
+        <v>46302.61458333334</v>
+      </c>
+      <c r="B445">
+        <v>2407.756</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2">
+      <c r="A446" s="2">
+        <v>46302.625</v>
+      </c>
+      <c r="B446">
+        <v>2089.921</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2">
+      <c r="A447" s="2">
+        <v>46302.63541666666</v>
+      </c>
+      <c r="B447">
+        <v>1895.083</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2">
+      <c r="A448" s="2">
+        <v>46302.64583333334</v>
+      </c>
+      <c r="B448">
+        <v>1679.348</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2">
+      <c r="A449" s="2">
+        <v>46302.65625</v>
+      </c>
+      <c r="B449">
+        <v>1469.681</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2">
+      <c r="A450" s="2">
+        <v>46302.66666666666</v>
+      </c>
+      <c r="B450">
+        <v>1132.102</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2">
+      <c r="A451" s="2">
+        <v>46302.67708333334</v>
+      </c>
+      <c r="B451">
+        <v>920.672</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2">
+      <c r="A452" s="2">
+        <v>46302.6875</v>
+      </c>
+      <c r="B452">
+        <v>717.648</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2">
+      <c r="A453" s="2">
+        <v>46302.69791666666</v>
+      </c>
+      <c r="B453">
+        <v>548.357</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2">
+      <c r="A454" s="2">
+        <v>46302.70833333334</v>
+      </c>
+      <c r="B454">
+        <v>287.262</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2">
+      <c r="A455" s="2">
+        <v>46302.71875</v>
+      </c>
+      <c r="B455">
+        <v>171.651</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2">
+      <c r="A456" s="2">
+        <v>46302.72916666666</v>
+      </c>
+      <c r="B456">
+        <v>83.946</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2">
+      <c r="A457" s="2">
+        <v>46302.73958333334</v>
+      </c>
+      <c r="B457">
+        <v>44.35</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2">
+      <c r="A458" s="2">
+        <v>46302.75</v>
+      </c>
+      <c r="B458">
+        <v>67.901</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2">
+      <c r="A459" s="2">
+        <v>46302.76041666666</v>
+      </c>
+      <c r="B459">
+        <v>72.84999999999999</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2">
+      <c r="A460" s="2">
+        <v>46302.77083333334</v>
+      </c>
+      <c r="B460">
+        <v>72.58799999999999</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2">
+      <c r="A461" s="2">
+        <v>46302.78125</v>
+      </c>
+      <c r="B461">
+        <v>71.248</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2">
+      <c r="A462" s="2">
+        <v>46302.79166666666</v>
+      </c>
+      <c r="B462">
+        <v>66.86</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2">
+      <c r="A463" s="2">
+        <v>46302.80208333334</v>
+      </c>
+      <c r="B463">
+        <v>66.45099999999999</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2">
+      <c r="A464" s="2">
+        <v>46302.8125</v>
+      </c>
+      <c r="B464">
+        <v>64.393</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2">
+      <c r="A465" s="2">
+        <v>46302.82291666666</v>
+      </c>
+      <c r="B465">
+        <v>73.16</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2">
+      <c r="A466" s="2">
+        <v>46302.83333333334</v>
+      </c>
+      <c r="B466">
+        <v>7.981</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2">
+      <c r="A467" s="2">
+        <v>46302.84375</v>
+      </c>
+      <c r="B467">
+        <v>18.481</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2">
+      <c r="A468" s="2">
+        <v>46302.85416666666</v>
+      </c>
+      <c r="B468">
+        <v>4.281</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2">
+      <c r="A469" s="2">
+        <v>46302.86458333334</v>
+      </c>
+      <c r="B469">
+        <v>1.881</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2">
+      <c r="A470" s="2">
+        <v>46302.875</v>
+      </c>
+      <c r="B470">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2">
+      <c r="A471" s="2">
+        <v>46302.88541666666</v>
+      </c>
+      <c r="B471">
         <v>1.08</v>
       </c>
     </row>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B189"/>
+  <dimension ref="A1:B183"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,1506 +394,1458 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="B2">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46302.01041666666</v>
+        <v>46303.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46302.02083333334</v>
+        <v>46303.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46302.03125</v>
+        <v>46303.03125</v>
       </c>
       <c r="B5">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46302.04166666666</v>
+        <v>46303.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46302.05208333334</v>
+        <v>46303.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46302.0625</v>
+        <v>46303.0625</v>
       </c>
       <c r="B8">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46302.07291666666</v>
+        <v>46303.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46302.08333333334</v>
+        <v>46303.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46302.09375</v>
+        <v>46303.09375</v>
       </c>
       <c r="B11">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46302.10416666666</v>
+        <v>46303.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46302.11458333334</v>
+        <v>46303.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.16</v>
+        <v>1.448</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46302.125</v>
+        <v>46303.125</v>
       </c>
       <c r="B14">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46302.13541666666</v>
+        <v>46303.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46302.14583333334</v>
+        <v>46303.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46302.15625</v>
+        <v>46303.15625</v>
       </c>
       <c r="B17">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46302.16666666666</v>
+        <v>46303.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.081</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46302.17708333334</v>
+        <v>46303.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.081</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46302.1875</v>
+        <v>46303.1875</v>
       </c>
       <c r="B20">
-        <v>1.081</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46302.19791666666</v>
+        <v>46303.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.081</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46302.20833333334</v>
+        <v>46303.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.126</v>
+        <v>1.404</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46302.21875</v>
+        <v>46303.21875</v>
       </c>
       <c r="B23">
-        <v>1.186</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46302.22916666666</v>
+        <v>46303.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.25</v>
+        <v>1.516</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46302.23958333334</v>
+        <v>46303.23958333334</v>
       </c>
       <c r="B25">
-        <v>1.398</v>
+        <v>2.392</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46302.25</v>
+        <v>46303.25</v>
       </c>
       <c r="B26">
-        <v>6.577</v>
+        <v>8.105</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46302.26041666666</v>
+        <v>46303.26041666666</v>
       </c>
       <c r="B27">
-        <v>7.65</v>
+        <v>8.808</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46302.27083333334</v>
+        <v>46303.27083333334</v>
       </c>
       <c r="B28">
-        <v>25.129</v>
+        <v>24.065</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46302.28125</v>
+        <v>46303.28125</v>
       </c>
       <c r="B29">
-        <v>90.494</v>
+        <v>83.989</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46302.29166666666</v>
+        <v>46303.29166666666</v>
       </c>
       <c r="B30">
-        <v>355.092</v>
+        <v>353.717</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46302.30208333334</v>
+        <v>46303.30208333334</v>
       </c>
       <c r="B31">
-        <v>513.593</v>
+        <v>512.051</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46302.3125</v>
+        <v>46303.3125</v>
       </c>
       <c r="B32">
-        <v>701.203</v>
+        <v>713.5839999999999</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46302.32291666666</v>
+        <v>46303.32291666666</v>
       </c>
       <c r="B33">
-        <v>897.447</v>
+        <v>946.412</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46302.33333333334</v>
+        <v>46303.33333333334</v>
       </c>
       <c r="B34">
-        <v>1315.768</v>
+        <v>1393.733</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46302.34375</v>
+        <v>46303.34375</v>
       </c>
       <c r="B35">
-        <v>1537.795</v>
+        <v>1638.932</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46302.35416666666</v>
+        <v>46303.35416666666</v>
       </c>
       <c r="B36">
-        <v>1805.559</v>
+        <v>1932.419</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46302.36458333334</v>
+        <v>46303.36458333334</v>
       </c>
       <c r="B37">
-        <v>2020.392</v>
+        <v>2158.212</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46302.375</v>
+        <v>46303.375</v>
       </c>
       <c r="B38">
-        <v>2370.704</v>
+        <v>2534.821</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46302.38541666666</v>
+        <v>46303.38541666666</v>
       </c>
       <c r="B39">
-        <v>2532.931</v>
+        <v>2691.343</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46302.39583333334</v>
+        <v>46303.39583333334</v>
       </c>
       <c r="B40">
-        <v>2680.769</v>
+        <v>2846.543</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46302.40625</v>
+        <v>46303.40625</v>
       </c>
       <c r="B41">
-        <v>2792.879</v>
+        <v>2980.398</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46302.41666666666</v>
+        <v>46303.41666666666</v>
       </c>
       <c r="B42">
-        <v>2962.088</v>
+        <v>3162.815</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46302.42708333334</v>
+        <v>46303.42708333334</v>
       </c>
       <c r="B43">
-        <v>3048.37</v>
+        <v>3256.443</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46302.4375</v>
+        <v>46303.4375</v>
       </c>
       <c r="B44">
-        <v>3084.796</v>
+        <v>3323.02</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46302.44791666666</v>
+        <v>46303.44791666666</v>
       </c>
       <c r="B45">
-        <v>3143.064</v>
+        <v>3385.007</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46302.45833333334</v>
+        <v>46303.45833333334</v>
       </c>
       <c r="B46">
-        <v>3194.727</v>
+        <v>3421.434</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46302.46875</v>
+        <v>46303.46875</v>
       </c>
       <c r="B47">
-        <v>3231.85</v>
+        <v>3425.481</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46302.47916666666</v>
+        <v>46303.47916666666</v>
       </c>
       <c r="B48">
-        <v>3238.587</v>
+        <v>3449.048</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46302.48958333334</v>
+        <v>46303.48958333334</v>
       </c>
       <c r="B49">
-        <v>3231.765</v>
+        <v>3458.695</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46302.5</v>
+        <v>46303.5</v>
       </c>
       <c r="B50">
-        <v>3224.09</v>
+        <v>3453.312</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46302.51041666666</v>
+        <v>46303.51041666666</v>
       </c>
       <c r="B51">
-        <v>3221.94</v>
+        <v>3447.407</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46302.52083333334</v>
+        <v>46303.52083333334</v>
       </c>
       <c r="B52">
-        <v>3197.811</v>
+        <v>3432.25</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46302.53125</v>
+        <v>46303.53125</v>
       </c>
       <c r="B53">
-        <v>3154.602</v>
+        <v>3411.417</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46302.54166666666</v>
+        <v>46303.54166666666</v>
       </c>
       <c r="B54">
-        <v>3101.591</v>
+        <v>3367.026</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46302.55208333334</v>
+        <v>46303.55208333334</v>
       </c>
       <c r="B55">
-        <v>3049.772</v>
+        <v>3320.276</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46302.5625</v>
+        <v>46303.5625</v>
       </c>
       <c r="B56">
-        <v>2978.25</v>
+        <v>3264.118</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46302.57291666666</v>
+        <v>46303.57291666666</v>
       </c>
       <c r="B57">
-        <v>2889.75</v>
+        <v>3192.026</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46302.58333333334</v>
+        <v>46303.58333333334</v>
       </c>
       <c r="B58">
-        <v>2746.633</v>
+        <v>3042.421</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46302.59375</v>
+        <v>46303.59375</v>
       </c>
       <c r="B59">
-        <v>2647.392</v>
+        <v>2946.881</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46302.60416666666</v>
+        <v>46303.60416666666</v>
       </c>
       <c r="B60">
-        <v>2552.551</v>
+        <v>2819.201</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46302.61458333334</v>
+        <v>46303.61458333334</v>
       </c>
       <c r="B61">
-        <v>2407.756</v>
+        <v>2676.905</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46302.625</v>
+        <v>46303.625</v>
       </c>
       <c r="B62">
-        <v>2089.921</v>
+        <v>2349.818</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46302.63541666666</v>
+        <v>46303.63541666666</v>
       </c>
       <c r="B63">
-        <v>1895.083</v>
+        <v>2173.086</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46302.64583333334</v>
+        <v>46303.64583333334</v>
       </c>
       <c r="B64">
-        <v>1679.348</v>
+        <v>1936.963</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46302.65625</v>
+        <v>46303.65625</v>
       </c>
       <c r="B65">
-        <v>1469.681</v>
+        <v>1717.447</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46302.66666666666</v>
+        <v>46303.66666666666</v>
       </c>
       <c r="B66">
-        <v>1132.102</v>
+        <v>1310.342</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46302.67708333334</v>
+        <v>46303.67708333334</v>
       </c>
       <c r="B67">
-        <v>920.672</v>
+        <v>1063.868</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46302.6875</v>
+        <v>46303.6875</v>
       </c>
       <c r="B68">
-        <v>717.648</v>
+        <v>784.668</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46302.69791666666</v>
+        <v>46303.69791666666</v>
       </c>
       <c r="B69">
-        <v>548.357</v>
+        <v>579.869</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46302.70833333334</v>
+        <v>46303.70833333334</v>
       </c>
       <c r="B70">
-        <v>287.262</v>
+        <v>292.141</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46302.71875</v>
+        <v>46303.71875</v>
       </c>
       <c r="B71">
-        <v>171.651</v>
+        <v>168.447</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46302.72916666666</v>
+        <v>46303.72916666666</v>
       </c>
       <c r="B72">
-        <v>83.946</v>
+        <v>80.754</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46302.73958333334</v>
+        <v>46303.73958333334</v>
       </c>
       <c r="B73">
-        <v>44.35</v>
+        <v>44.781</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46302.75</v>
+        <v>46303.75</v>
       </c>
       <c r="B74">
-        <v>67.901</v>
+        <v>57.467</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46302.76041666666</v>
+        <v>46303.76041666666</v>
       </c>
       <c r="B75">
-        <v>72.84999999999999</v>
+        <v>61.771</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46302.77083333334</v>
+        <v>46303.77083333334</v>
       </c>
       <c r="B76">
-        <v>72.58799999999999</v>
+        <v>61.335</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46302.78125</v>
+        <v>46303.78125</v>
       </c>
       <c r="B77">
-        <v>71.248</v>
+        <v>61.285</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46302.79166666666</v>
+        <v>46303.79166666666</v>
       </c>
       <c r="B78">
-        <v>66.86</v>
+        <v>60.023</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46302.80208333334</v>
+        <v>46303.80208333334</v>
       </c>
       <c r="B79">
-        <v>66.45099999999999</v>
+        <v>56.898</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46302.8125</v>
+        <v>46303.8125</v>
       </c>
       <c r="B80">
-        <v>64.393</v>
+        <v>49.623</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46302.82291666666</v>
+        <v>46303.82291666666</v>
       </c>
       <c r="B81">
-        <v>73.16</v>
+        <v>48.215</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46302.83333333334</v>
+        <v>46303.83333333334</v>
       </c>
       <c r="B82">
-        <v>7.981</v>
+        <v>41.668</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46302.84375</v>
+        <v>46303.84375</v>
       </c>
       <c r="B83">
-        <v>18.481</v>
+        <v>40.468</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46302.85416666666</v>
+        <v>46303.85416666666</v>
       </c>
       <c r="B84">
-        <v>4.281</v>
+        <v>39.968</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46302.86458333334</v>
+        <v>46303.86458333334</v>
       </c>
       <c r="B85">
-        <v>1.881</v>
+        <v>37.668</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46302.875</v>
+        <v>46303.875</v>
       </c>
       <c r="B86">
-        <v>1.28</v>
+        <v>6.268</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46302.88541666666</v>
+        <v>46303.88541666666</v>
       </c>
       <c r="B87">
-        <v>1.08</v>
+        <v>9.968</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46302.89583333334</v>
+        <v>46303.89583333334</v>
       </c>
       <c r="B88">
-        <v>1.08</v>
+        <v>10.368</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46302.90625</v>
+        <v>46303.90625</v>
       </c>
       <c r="B89">
-        <v>1.08</v>
+        <v>9.868</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46302.91666666666</v>
+        <v>46303.91666666666</v>
       </c>
       <c r="B90">
-        <v>1.08</v>
+        <v>6.268</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="2">
-        <v>46302.92708333334</v>
+        <v>46303.92708333334</v>
       </c>
       <c r="B91">
-        <v>1.08</v>
+        <v>6.468</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="2">
-        <v>46302.9375</v>
+        <v>46303.9375</v>
       </c>
       <c r="B92">
-        <v>1.08</v>
+        <v>5.668</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="2">
-        <v>46302.94791666666</v>
+        <v>46303.94791666666</v>
       </c>
       <c r="B93">
-        <v>1.08</v>
+        <v>5.868</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="2">
-        <v>46302.95833333334</v>
+        <v>46303.95833333334</v>
       </c>
       <c r="B94">
-        <v>1.68</v>
+        <v>1.468</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="2">
-        <v>46302.96875</v>
+        <v>46303.96875</v>
       </c>
       <c r="B95">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="2">
-        <v>46302.97916666666</v>
+        <v>46303.97916666666</v>
       </c>
       <c r="B96">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="2">
-        <v>46302.98958333334</v>
+        <v>46303.98958333334</v>
       </c>
       <c r="B97">
-        <v>1.08</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="2">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B98">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="2">
-        <v>46303.01041666666</v>
+        <v>46304.01041666666</v>
       </c>
       <c r="B99">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="2">
-        <v>46303.02083333334</v>
+        <v>46304.02083333334</v>
       </c>
       <c r="B100">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="2">
-        <v>46303.03125</v>
+        <v>46304.03125</v>
       </c>
       <c r="B101">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="2">
-        <v>46303.04166666666</v>
+        <v>46304.04166666666</v>
       </c>
       <c r="B102">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="2">
-        <v>46303.05208333334</v>
+        <v>46304.05208333334</v>
       </c>
       <c r="B103">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="2">
-        <v>46303.0625</v>
+        <v>46304.0625</v>
       </c>
       <c r="B104">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="2">
-        <v>46303.07291666666</v>
+        <v>46304.07291666666</v>
       </c>
       <c r="B105">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="2">
-        <v>46303.08333333334</v>
+        <v>46304.08333333334</v>
       </c>
       <c r="B106">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="2">
-        <v>46303.09375</v>
+        <v>46304.09375</v>
       </c>
       <c r="B107">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="2">
-        <v>46303.10416666666</v>
+        <v>46304.10416666666</v>
       </c>
       <c r="B108">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="2">
-        <v>46303.11458333334</v>
+        <v>46304.11458333334</v>
       </c>
       <c r="B109">
-        <v>1.448</v>
+        <v>1.432</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="2">
-        <v>46303.125</v>
+        <v>46304.125</v>
       </c>
       <c r="B110">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="2">
-        <v>46303.13541666666</v>
+        <v>46304.13541666666</v>
       </c>
       <c r="B111">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="2">
-        <v>46303.14583333334</v>
+        <v>46304.14583333334</v>
       </c>
       <c r="B112">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="2">
-        <v>46303.15625</v>
+        <v>46304.15625</v>
       </c>
       <c r="B113">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="2">
-        <v>46303.16666666666</v>
+        <v>46304.16666666666</v>
       </c>
       <c r="B114">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="2">
-        <v>46303.17708333334</v>
+        <v>46304.17708333334</v>
       </c>
       <c r="B115">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="2">
-        <v>46303.1875</v>
+        <v>46304.1875</v>
       </c>
       <c r="B116">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="2">
-        <v>46303.19791666666</v>
+        <v>46304.19791666666</v>
       </c>
       <c r="B117">
-        <v>1.368</v>
+        <v>1.352</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="2">
-        <v>46303.20833333334</v>
+        <v>46304.20833333334</v>
       </c>
       <c r="B118">
-        <v>1.404</v>
+        <v>5.424</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="2">
-        <v>46303.21875</v>
+        <v>46304.21875</v>
       </c>
       <c r="B119">
-        <v>1.46</v>
+        <v>7.745</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="2">
-        <v>46303.22916666666</v>
+        <v>46304.22916666666</v>
       </c>
       <c r="B120">
-        <v>1.516</v>
+        <v>12.747</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="2">
-        <v>46303.23958333334</v>
+        <v>46304.23958333334</v>
       </c>
       <c r="B121">
-        <v>2.392</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="2">
-        <v>46303.25</v>
+        <v>46304.25</v>
       </c>
       <c r="B122">
-        <v>8.105</v>
+        <v>16.988</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="2">
-        <v>46303.26041666666</v>
+        <v>46304.26041666666</v>
       </c>
       <c r="B123">
-        <v>8.808</v>
+        <v>18.363</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" s="2">
-        <v>46303.27083333334</v>
+        <v>46304.27083333334</v>
       </c>
       <c r="B124">
-        <v>24.065</v>
+        <v>26.633</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" s="2">
-        <v>46303.28125</v>
+        <v>46304.28125</v>
       </c>
       <c r="B125">
-        <v>83.989</v>
+        <v>79.69199999999999</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" s="2">
-        <v>46303.29166666666</v>
+        <v>46304.29166666666</v>
       </c>
       <c r="B126">
-        <v>353.717</v>
+        <v>292.474</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" s="2">
-        <v>46303.30208333334</v>
+        <v>46304.30208333334</v>
       </c>
       <c r="B127">
-        <v>512.051</v>
+        <v>411.968</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" s="2">
-        <v>46303.3125</v>
+        <v>46304.3125</v>
       </c>
       <c r="B128">
-        <v>713.5839999999999</v>
+        <v>561.978</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" s="2">
-        <v>46303.32291666666</v>
+        <v>46304.32291666666</v>
       </c>
       <c r="B129">
-        <v>946.412</v>
+        <v>715.95</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" s="2">
-        <v>46303.33333333334</v>
+        <v>46304.33333333334</v>
       </c>
       <c r="B130">
-        <v>1393.733</v>
+        <v>1081.646</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" s="2">
-        <v>46303.34375</v>
+        <v>46304.34375</v>
       </c>
       <c r="B131">
-        <v>1638.932</v>
+        <v>1260.477</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" s="2">
-        <v>46303.35416666666</v>
+        <v>46304.35416666666</v>
       </c>
       <c r="B132">
-        <v>1932.419</v>
+        <v>1446.872</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" s="2">
-        <v>46303.36458333334</v>
+        <v>46304.36458333334</v>
       </c>
       <c r="B133">
-        <v>2158.212</v>
+        <v>1605.797</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" s="2">
-        <v>46303.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B134">
-        <v>2534.821</v>
+        <v>1877.772</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" s="2">
-        <v>46303.38541666666</v>
+        <v>46304.38541666666</v>
       </c>
       <c r="B135">
-        <v>2691.343</v>
+        <v>2015.456</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" s="2">
-        <v>46303.39583333334</v>
+        <v>46304.39583333334</v>
       </c>
       <c r="B136">
-        <v>2846.543</v>
+        <v>2144.366</v>
       </c>
     </row>
     <row r="137" spans="1:2">
       <c r="A137" s="2">
-        <v>46303.40625</v>
+        <v>46304.40625</v>
       </c>
       <c r="B137">
-        <v>2980.398</v>
+        <v>2248.442</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" s="2">
-        <v>46303.41666666666</v>
+        <v>46304.41666666666</v>
       </c>
       <c r="B138">
-        <v>3162.815</v>
+        <v>2406.253</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" s="2">
-        <v>46303.42708333334</v>
+        <v>46304.42708333334</v>
       </c>
       <c r="B139">
-        <v>3256.443</v>
+        <v>2483.122</v>
       </c>
     </row>
     <row r="140" spans="1:2">
       <c r="A140" s="2">
-        <v>46303.4375</v>
+        <v>46304.4375</v>
       </c>
       <c r="B140">
-        <v>3323.02</v>
+        <v>2540.829</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" s="2">
-        <v>46303.44791666666</v>
+        <v>46304.44791666666</v>
       </c>
       <c r="B141">
-        <v>3385.007</v>
+        <v>2588.211</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" s="2">
-        <v>46303.45833333334</v>
+        <v>46304.45833333334</v>
       </c>
       <c r="B142">
-        <v>3421.434</v>
+        <v>2639.579</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" s="2">
-        <v>46303.46875</v>
+        <v>46304.46875</v>
       </c>
       <c r="B143">
-        <v>3425.481</v>
+        <v>2668.686</v>
       </c>
     </row>
     <row r="144" spans="1:2">
       <c r="A144" s="2">
-        <v>46303.47916666666</v>
+        <v>46304.47916666666</v>
       </c>
       <c r="B144">
-        <v>3449.048</v>
+        <v>2684.824</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" s="2">
-        <v>46303.48958333334</v>
+        <v>46304.48958333334</v>
       </c>
       <c r="B145">
-        <v>3458.695</v>
+        <v>2699.849</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" s="2">
-        <v>46303.5</v>
+        <v>46304.5</v>
       </c>
       <c r="B146">
-        <v>3453.312</v>
+        <v>2699.154</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" s="2">
-        <v>46303.51041666666</v>
+        <v>46304.51041666666</v>
       </c>
       <c r="B147">
-        <v>3447.407</v>
+        <v>2695.11</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" s="2">
-        <v>46303.52083333334</v>
+        <v>46304.52083333334</v>
       </c>
       <c r="B148">
-        <v>3432.25</v>
+        <v>2683.931</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" s="2">
-        <v>46303.53125</v>
+        <v>46304.53125</v>
       </c>
       <c r="B149">
-        <v>3411.417</v>
+        <v>2659.795</v>
       </c>
     </row>
     <row r="150" spans="1:2">
       <c r="A150" s="2">
-        <v>46303.54166666666</v>
+        <v>46304.54166666666</v>
       </c>
       <c r="B150">
-        <v>3367.026</v>
+        <v>2615.994</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" s="2">
-        <v>46303.55208333334</v>
+        <v>46304.55208333334</v>
       </c>
       <c r="B151">
-        <v>3320.276</v>
+        <v>2578.677</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" s="2">
-        <v>46303.5625</v>
+        <v>46304.5625</v>
       </c>
       <c r="B152">
-        <v>3264.118</v>
+        <v>2534.749</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" s="2">
-        <v>46303.57291666666</v>
+        <v>46304.57291666666</v>
       </c>
       <c r="B153">
-        <v>3192.026</v>
+        <v>2476.706</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" s="2">
-        <v>46303.58333333334</v>
+        <v>46304.58333333334</v>
       </c>
       <c r="B154">
-        <v>3042.421</v>
+        <v>2333.684</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" s="2">
-        <v>46303.59375</v>
+        <v>46304.59375</v>
       </c>
       <c r="B155">
-        <v>2946.881</v>
+        <v>2233.524</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" s="2">
-        <v>46303.60416666666</v>
+        <v>46304.60416666666</v>
       </c>
       <c r="B156">
-        <v>2819.201</v>
+        <v>2102.376</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" s="2">
-        <v>46303.61458333334</v>
+        <v>46304.61458333334</v>
       </c>
       <c r="B157">
-        <v>2676.905</v>
+        <v>1972.053</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" s="2">
-        <v>46303.625</v>
+        <v>46304.625</v>
       </c>
       <c r="B158">
-        <v>2349.818</v>
+        <v>1680.023</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" s="2">
-        <v>46303.63541666666</v>
+        <v>46304.63541666666</v>
       </c>
       <c r="B159">
-        <v>2173.086</v>
+        <v>1518.555</v>
       </c>
     </row>
     <row r="160" spans="1:2">
       <c r="A160" s="2">
-        <v>46303.64583333334</v>
+        <v>46304.64583333334</v>
       </c>
       <c r="B160">
-        <v>1936.963</v>
+        <v>1351.391</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" s="2">
-        <v>46303.65625</v>
+        <v>46304.65625</v>
       </c>
       <c r="B161">
-        <v>1717.447</v>
+        <v>1193.892</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" s="2">
-        <v>46303.66666666666</v>
+        <v>46304.66666666666</v>
       </c>
       <c r="B162">
-        <v>1310.342</v>
+        <v>877.867</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" s="2">
-        <v>46303.67708333334</v>
+        <v>46304.67708333334</v>
       </c>
       <c r="B163">
-        <v>1063.868</v>
+        <v>712.401</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" s="2">
-        <v>46303.6875</v>
+        <v>46304.6875</v>
       </c>
       <c r="B164">
-        <v>784.668</v>
+        <v>543.579</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" s="2">
-        <v>46303.69791666666</v>
+        <v>46304.69791666666</v>
       </c>
       <c r="B165">
-        <v>579.869</v>
+        <v>407.269</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" s="2">
-        <v>46303.70833333334</v>
+        <v>46304.70833333334</v>
       </c>
       <c r="B166">
-        <v>292.141</v>
+        <v>194.551</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" s="2">
-        <v>46303.71875</v>
+        <v>46304.71875</v>
       </c>
       <c r="B167">
-        <v>168.447</v>
+        <v>111.596</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" s="2">
-        <v>46303.72916666666</v>
+        <v>46304.72916666666</v>
       </c>
       <c r="B168">
-        <v>80.754</v>
+        <v>55.187</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" s="2">
-        <v>46303.73958333334</v>
+        <v>46304.73958333334</v>
       </c>
       <c r="B169">
-        <v>44.781</v>
+        <v>36.275</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" s="2">
-        <v>46303.75</v>
+        <v>46304.75</v>
       </c>
       <c r="B170">
-        <v>57.467</v>
+        <v>44.085</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" s="2">
-        <v>46303.76041666666</v>
+        <v>46304.76041666666</v>
       </c>
       <c r="B171">
-        <v>61.771</v>
+        <v>49.415</v>
       </c>
     </row>
     <row r="172" spans="1:2">
       <c r="A172" s="2">
-        <v>46303.77083333334</v>
+        <v>46304.77083333334</v>
       </c>
       <c r="B172">
-        <v>61.335</v>
+        <v>55.086</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" s="2">
-        <v>46303.78125</v>
+        <v>46304.78125</v>
       </c>
       <c r="B173">
-        <v>61.285</v>
+        <v>55.178</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" s="2">
-        <v>46303.79166666666</v>
+        <v>46304.79166666666</v>
       </c>
       <c r="B174">
-        <v>60.023</v>
+        <v>55.032</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" s="2">
-        <v>46303.80208333334</v>
+        <v>46304.80208333334</v>
       </c>
       <c r="B175">
-        <v>56.898</v>
+        <v>54.932</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" s="2">
-        <v>46303.8125</v>
+        <v>46304.8125</v>
       </c>
       <c r="B176">
-        <v>49.623</v>
+        <v>49.632</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" s="2">
-        <v>46303.82291666666</v>
+        <v>46304.82291666666</v>
       </c>
       <c r="B177">
-        <v>48.215</v>
+        <v>48.932</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" s="2">
-        <v>46303.83333333334</v>
+        <v>46304.83333333334</v>
       </c>
       <c r="B178">
-        <v>41.668</v>
+        <v>40.652</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" s="2">
-        <v>46303.84375</v>
+        <v>46304.84375</v>
       </c>
       <c r="B179">
-        <v>40.468</v>
+        <v>38.052</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" s="2">
-        <v>46303.85416666666</v>
+        <v>46304.85416666666</v>
       </c>
       <c r="B180">
-        <v>39.968</v>
+        <v>38.052</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" s="2">
-        <v>46303.86458333334</v>
+        <v>46304.86458333334</v>
       </c>
       <c r="B181">
-        <v>37.668</v>
+        <v>41.352</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" s="2">
-        <v>46303.875</v>
+        <v>46304.875</v>
       </c>
       <c r="B182">
-        <v>6.268</v>
+        <v>2.152</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" s="2">
-        <v>46303.88541666666</v>
+        <v>46304.88541666666</v>
       </c>
       <c r="B183">
-        <v>9.968</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2">
-      <c r="A184" s="2">
-        <v>46303.89583333334</v>
-      </c>
-      <c r="B184">
-        <v>10.368</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2">
-      <c r="A185" s="2">
-        <v>46303.90625</v>
-      </c>
-      <c r="B185">
-        <v>9.868</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2">
-      <c r="A186" s="2">
-        <v>46303.91666666666</v>
-      </c>
-      <c r="B186">
-        <v>6.268</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2">
-      <c r="A187" s="2">
-        <v>46303.92708333334</v>
-      </c>
-      <c r="B187">
-        <v>6.468</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2">
-      <c r="A188" s="2">
-        <v>46303.9375</v>
-      </c>
-      <c r="B188">
-        <v>5.668</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2">
-      <c r="A189" s="2">
-        <v>46303.94791666666</v>
-      </c>
-      <c r="B189">
-        <v>5.868</v>
+        <v>1.352</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,714 +394,714 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="B2">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46307.01041666666</v>
+        <v>46308.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.752</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46307.02083333334</v>
+        <v>46308.02083333334</v>
       </c>
       <c r="B4">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46307.03125</v>
+        <v>46308.03125</v>
       </c>
       <c r="B5">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46307.04166666666</v>
+        <v>46308.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46307.05208333334</v>
+        <v>46308.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46307.0625</v>
+        <v>46308.0625</v>
       </c>
       <c r="B8">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46307.07291666666</v>
+        <v>46308.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46307.08333333334</v>
+        <v>46308.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46307.09375</v>
+        <v>46308.09375</v>
       </c>
       <c r="B11">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46307.10416666666</v>
+        <v>46308.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46307.11458333334</v>
+        <v>46308.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.032</v>
+        <v>1.332</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46307.125</v>
+        <v>46308.125</v>
       </c>
       <c r="B14">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46307.13541666666</v>
+        <v>46308.13541666666</v>
       </c>
       <c r="B15">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46307.14583333334</v>
+        <v>46308.14583333334</v>
       </c>
       <c r="B16">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46307.15625</v>
+        <v>46308.15625</v>
       </c>
       <c r="B17">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46307.16666666666</v>
+        <v>46308.16666666666</v>
       </c>
       <c r="B18">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46307.17708333334</v>
+        <v>46308.17708333334</v>
       </c>
       <c r="B19">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46307.1875</v>
+        <v>46308.1875</v>
       </c>
       <c r="B20">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46307.19791666666</v>
+        <v>46308.19791666666</v>
       </c>
       <c r="B21">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46307.20833333334</v>
+        <v>46308.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.501</v>
+        <v>1.289</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46307.21875</v>
+        <v>46308.21875</v>
       </c>
       <c r="B23">
-        <v>1.349</v>
+        <v>1.325</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46307.22916666666</v>
+        <v>46308.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.945</v>
+        <v>1.914</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46307.23958333334</v>
+        <v>46308.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.816</v>
+        <v>2.745</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46307.25</v>
+        <v>46308.25</v>
       </c>
       <c r="B26">
-        <v>6.161</v>
+        <v>4.824</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46307.26041666666</v>
+        <v>46308.26041666666</v>
       </c>
       <c r="B27">
-        <v>8.832000000000001</v>
+        <v>6.366</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46307.27083333334</v>
+        <v>46308.27083333334</v>
       </c>
       <c r="B28">
-        <v>26</v>
+        <v>17.871</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46307.28125</v>
+        <v>46308.28125</v>
       </c>
       <c r="B29">
-        <v>32.567</v>
+        <v>25.786</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46307.29166666666</v>
+        <v>46308.29166666666</v>
       </c>
       <c r="B30">
-        <v>108.209</v>
+        <v>79.893</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46307.30208333334</v>
+        <v>46308.30208333334</v>
       </c>
       <c r="B31">
-        <v>140.421</v>
+        <v>114.57</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46307.3125</v>
+        <v>46308.3125</v>
       </c>
       <c r="B32">
-        <v>180.709</v>
+        <v>166.381</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46307.32291666666</v>
+        <v>46308.32291666666</v>
       </c>
       <c r="B33">
-        <v>236.469</v>
+        <v>221.631</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46307.33333333334</v>
+        <v>46308.33333333334</v>
       </c>
       <c r="B34">
-        <v>360.811</v>
+        <v>339.799</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46307.34375</v>
+        <v>46308.34375</v>
       </c>
       <c r="B35">
-        <v>410.067</v>
+        <v>413.717</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46307.35416666666</v>
+        <v>46308.35416666666</v>
       </c>
       <c r="B36">
-        <v>494.079</v>
+        <v>504.761</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46307.36458333334</v>
+        <v>46308.36458333334</v>
       </c>
       <c r="B37">
-        <v>544.504</v>
+        <v>579.575</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46307.375</v>
+        <v>46308.375</v>
       </c>
       <c r="B38">
-        <v>651.726</v>
+        <v>688.427</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46307.38541666666</v>
+        <v>46308.38541666666</v>
       </c>
       <c r="B39">
-        <v>708.309</v>
+        <v>767.3680000000001</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46307.39583333334</v>
+        <v>46308.39583333334</v>
       </c>
       <c r="B40">
-        <v>770.194</v>
+        <v>832.1319999999999</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46307.40625</v>
+        <v>46308.40625</v>
       </c>
       <c r="B41">
-        <v>809.772</v>
+        <v>894.4930000000001</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46307.41666666666</v>
+        <v>46308.41666666666</v>
       </c>
       <c r="B42">
-        <v>881.1180000000001</v>
+        <v>997.547</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46307.42708333334</v>
+        <v>46308.42708333334</v>
       </c>
       <c r="B43">
-        <v>900.997</v>
+        <v>1050.877</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46307.4375</v>
+        <v>46308.4375</v>
       </c>
       <c r="B44">
-        <v>929.372</v>
+        <v>1094.422</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46307.44791666666</v>
+        <v>46308.44791666666</v>
       </c>
       <c r="B45">
-        <v>952.203</v>
+        <v>1134.253</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46307.45833333334</v>
+        <v>46308.45833333334</v>
       </c>
       <c r="B46">
-        <v>995.523</v>
+        <v>1189.527</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46307.46875</v>
+        <v>46308.46875</v>
       </c>
       <c r="B47">
-        <v>1011.613</v>
+        <v>1206.592</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46307.47916666666</v>
+        <v>46308.47916666666</v>
       </c>
       <c r="B48">
-        <v>1022.468</v>
+        <v>1221.036</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46307.48958333334</v>
+        <v>46308.48958333334</v>
       </c>
       <c r="B49">
-        <v>1021.363</v>
+        <v>1226.241</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46307.5</v>
+        <v>46308.5</v>
       </c>
       <c r="B50">
-        <v>1022.097</v>
+        <v>1244.579</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46307.51041666666</v>
+        <v>46308.51041666666</v>
       </c>
       <c r="B51">
-        <v>1015.636</v>
+        <v>1234.617</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46307.52083333334</v>
+        <v>46308.52083333334</v>
       </c>
       <c r="B52">
-        <v>1005.446</v>
+        <v>1221.321</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46307.53125</v>
+        <v>46308.53125</v>
       </c>
       <c r="B53">
-        <v>990.543</v>
+        <v>1205.113</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46307.54166666666</v>
+        <v>46308.54166666666</v>
       </c>
       <c r="B54">
-        <v>951.353</v>
+        <v>1172.049</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46307.55208333334</v>
+        <v>46308.55208333334</v>
       </c>
       <c r="B55">
-        <v>930.3049999999999</v>
+        <v>1142.258</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46307.5625</v>
+        <v>46308.5625</v>
       </c>
       <c r="B56">
-        <v>899.8</v>
+        <v>1108.29</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46307.57291666666</v>
+        <v>46308.57291666666</v>
       </c>
       <c r="B57">
-        <v>862.749</v>
+        <v>1062.624</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46307.58333333334</v>
+        <v>46308.58333333334</v>
       </c>
       <c r="B58">
-        <v>790.364</v>
+        <v>982.692</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46307.59375</v>
+        <v>46308.59375</v>
       </c>
       <c r="B59">
-        <v>736.884</v>
+        <v>939.6420000000001</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46307.60416666666</v>
+        <v>46308.60416666666</v>
       </c>
       <c r="B60">
-        <v>686.338</v>
+        <v>878.764</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46307.61458333334</v>
+        <v>46308.61458333334</v>
       </c>
       <c r="B61">
-        <v>638.347</v>
+        <v>830.458</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46307.625</v>
+        <v>46308.625</v>
       </c>
       <c r="B62">
-        <v>556.192</v>
+        <v>689.139</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46307.63541666666</v>
+        <v>46308.63541666666</v>
       </c>
       <c r="B63">
-        <v>484.935</v>
+        <v>617.178</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46307.64583333334</v>
+        <v>46308.64583333334</v>
       </c>
       <c r="B64">
-        <v>431.821</v>
+        <v>550.561</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46307.65625</v>
+        <v>46308.65625</v>
       </c>
       <c r="B65">
-        <v>397.364</v>
+        <v>473.79</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46307.66666666666</v>
+        <v>46308.66666666666</v>
       </c>
       <c r="B66">
-        <v>271.685</v>
+        <v>350.573</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46307.67708333334</v>
+        <v>46308.67708333334</v>
       </c>
       <c r="B67">
-        <v>226.003</v>
+        <v>287.091</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46307.6875</v>
+        <v>46308.6875</v>
       </c>
       <c r="B68">
-        <v>181.263</v>
+        <v>221.64</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46307.69791666666</v>
+        <v>46308.69791666666</v>
       </c>
       <c r="B69">
-        <v>146.463</v>
+        <v>166.727</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46307.70833333334</v>
+        <v>46308.70833333334</v>
       </c>
       <c r="B70">
-        <v>67.40300000000001</v>
+        <v>87.72</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46307.71875</v>
+        <v>46308.71875</v>
       </c>
       <c r="B71">
-        <v>46.452</v>
+        <v>59.464</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46307.72916666666</v>
+        <v>46308.72916666666</v>
       </c>
       <c r="B72">
-        <v>39.498</v>
+        <v>39.771</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46307.73958333334</v>
+        <v>46308.73958333334</v>
       </c>
       <c r="B73">
-        <v>65.842</v>
+        <v>34.298</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46307.75</v>
+        <v>46308.75</v>
       </c>
       <c r="B74">
-        <v>44.603</v>
+        <v>46.348</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46307.76041666666</v>
+        <v>46308.76041666666</v>
       </c>
       <c r="B75">
-        <v>44.473</v>
+        <v>56.29</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46307.77083333334</v>
+        <v>46308.77083333334</v>
       </c>
       <c r="B76">
-        <v>54.469</v>
+        <v>56.574</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46307.78125</v>
+        <v>46308.78125</v>
       </c>
       <c r="B77">
-        <v>56.569</v>
+        <v>55.174</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46307.79166666666</v>
+        <v>46308.79166666666</v>
       </c>
       <c r="B78">
-        <v>53.132</v>
+        <v>54.032</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46307.80208333334</v>
+        <v>46308.80208333334</v>
       </c>
       <c r="B79">
-        <v>49.232</v>
+        <v>51.132</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46307.8125</v>
+        <v>46308.8125</v>
       </c>
       <c r="B80">
-        <v>48.732</v>
+        <v>49.732</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46307.82291666666</v>
+        <v>46308.82291666666</v>
       </c>
       <c r="B81">
-        <v>47.832</v>
+        <v>50.632</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46307.83333333334</v>
+        <v>46308.83333333334</v>
       </c>
       <c r="B82">
-        <v>45.552</v>
+        <v>19.852</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46307.84375</v>
+        <v>46308.84375</v>
       </c>
       <c r="B83">
-        <v>1.952</v>
+        <v>19.152</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46307.85416666666</v>
+        <v>46308.85416666666</v>
       </c>
       <c r="B84">
-        <v>0.952</v>
+        <v>21.352</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46307.86458333334</v>
+        <v>46308.86458333334</v>
       </c>
       <c r="B85">
-        <v>2.552</v>
+        <v>21.152</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46307.875</v>
+        <v>46308.875</v>
       </c>
       <c r="B86">
-        <v>0.952</v>
+        <v>9.651999999999999</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46307.88541666666</v>
+        <v>46308.88541666666</v>
       </c>
       <c r="B87">
-        <v>2.152</v>
+        <v>21.052</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46307.89583333334</v>
+        <v>46308.89583333334</v>
       </c>
       <c r="B88">
-        <v>2.952</v>
+        <v>3.252</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46307.90625</v>
+        <v>46308.90625</v>
       </c>
       <c r="B89">
-        <v>4.552</v>
+        <v>4.052</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46307.91666666666</v>
+        <v>46308.91666666666</v>
       </c>
       <c r="B90">
-        <v>0.952</v>
+        <v>1.252</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,714 +394,714 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="B2">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46308.01041666666</v>
+        <v>46309.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46308.02083333334</v>
+        <v>46309.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46308.03125</v>
+        <v>46309.03125</v>
       </c>
       <c r="B5">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46308.04166666666</v>
+        <v>46309.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.332</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46308.05208333334</v>
+        <v>46309.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.332</v>
+        <v>1.668</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46308.0625</v>
+        <v>46309.0625</v>
       </c>
       <c r="B8">
-        <v>1.332</v>
+        <v>1.668</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46308.07291666666</v>
+        <v>46309.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.332</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46308.08333333334</v>
+        <v>46309.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.332</v>
+        <v>1.568</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46308.09375</v>
+        <v>46309.09375</v>
       </c>
       <c r="B11">
-        <v>1.332</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46308.10416666666</v>
+        <v>46309.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.332</v>
+        <v>2.768</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46308.11458333334</v>
+        <v>46309.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.332</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46308.125</v>
+        <v>46309.125</v>
       </c>
       <c r="B14">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46308.13541666666</v>
+        <v>46309.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.252</v>
+        <v>1.388</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46308.14583333334</v>
+        <v>46309.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46308.15625</v>
+        <v>46309.15625</v>
       </c>
       <c r="B17">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46308.16666666666</v>
+        <v>46309.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46308.17708333334</v>
+        <v>46309.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46308.1875</v>
+        <v>46309.1875</v>
       </c>
       <c r="B20">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46308.19791666666</v>
+        <v>46309.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46308.20833333334</v>
+        <v>46309.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.289</v>
+        <v>1.533</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46308.21875</v>
+        <v>46309.21875</v>
       </c>
       <c r="B23">
-        <v>1.325</v>
+        <v>1.269</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46308.22916666666</v>
+        <v>46309.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.914</v>
+        <v>1.983</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46308.23958333334</v>
+        <v>46309.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.745</v>
+        <v>3.766</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46308.25</v>
+        <v>46309.25</v>
       </c>
       <c r="B26">
-        <v>4.824</v>
+        <v>9.045</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46308.26041666666</v>
+        <v>46309.26041666666</v>
       </c>
       <c r="B27">
-        <v>6.366</v>
+        <v>12.64</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46308.27083333334</v>
+        <v>46309.27083333334</v>
       </c>
       <c r="B28">
-        <v>17.871</v>
+        <v>18.433</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46308.28125</v>
+        <v>46309.28125</v>
       </c>
       <c r="B29">
-        <v>25.786</v>
+        <v>35.339</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46308.29166666666</v>
+        <v>46309.29166666666</v>
       </c>
       <c r="B30">
-        <v>79.893</v>
+        <v>158.95</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46308.30208333334</v>
+        <v>46309.30208333334</v>
       </c>
       <c r="B31">
-        <v>114.57</v>
+        <v>250.122</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46308.3125</v>
+        <v>46309.3125</v>
       </c>
       <c r="B32">
-        <v>166.381</v>
+        <v>351.868</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46308.32291666666</v>
+        <v>46309.32291666666</v>
       </c>
       <c r="B33">
-        <v>221.631</v>
+        <v>460.851</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46308.33333333334</v>
+        <v>46309.33333333334</v>
       </c>
       <c r="B34">
-        <v>339.799</v>
+        <v>729.88</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46308.34375</v>
+        <v>46309.34375</v>
       </c>
       <c r="B35">
-        <v>413.717</v>
+        <v>883.856</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46308.35416666666</v>
+        <v>46309.35416666666</v>
       </c>
       <c r="B36">
-        <v>504.761</v>
+        <v>1044.98</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46308.36458333334</v>
+        <v>46309.36458333334</v>
       </c>
       <c r="B37">
-        <v>579.575</v>
+        <v>1190.297</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46308.375</v>
+        <v>46309.375</v>
       </c>
       <c r="B38">
-        <v>688.427</v>
+        <v>1466.624</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46308.38541666666</v>
+        <v>46309.38541666666</v>
       </c>
       <c r="B39">
-        <v>767.3680000000001</v>
+        <v>1619.946</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46308.39583333334</v>
+        <v>46309.39583333334</v>
       </c>
       <c r="B40">
-        <v>832.1319999999999</v>
+        <v>1745.661</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46308.40625</v>
+        <v>46309.40625</v>
       </c>
       <c r="B41">
-        <v>894.4930000000001</v>
+        <v>1863.256</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46308.41666666666</v>
+        <v>46309.41666666666</v>
       </c>
       <c r="B42">
-        <v>997.547</v>
+        <v>2076.265</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46308.42708333334</v>
+        <v>46309.42708333334</v>
       </c>
       <c r="B43">
-        <v>1050.877</v>
+        <v>2159.4</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46308.4375</v>
+        <v>46309.4375</v>
       </c>
       <c r="B44">
-        <v>1094.422</v>
+        <v>2230.061</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46308.44791666666</v>
+        <v>46309.44791666666</v>
       </c>
       <c r="B45">
-        <v>1134.253</v>
+        <v>2299.546</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46308.45833333334</v>
+        <v>46309.45833333334</v>
       </c>
       <c r="B46">
-        <v>1189.527</v>
+        <v>2400.656</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46308.46875</v>
+        <v>46309.46875</v>
       </c>
       <c r="B47">
-        <v>1206.592</v>
+        <v>2440.426</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46308.47916666666</v>
+        <v>46309.47916666666</v>
       </c>
       <c r="B48">
-        <v>1221.036</v>
+        <v>2471.592</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46308.48958333334</v>
+        <v>46309.48958333334</v>
       </c>
       <c r="B49">
-        <v>1226.241</v>
+        <v>2486.946</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46308.5</v>
+        <v>46309.5</v>
       </c>
       <c r="B50">
-        <v>1244.579</v>
+        <v>2519.963</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46308.51041666666</v>
+        <v>46309.51041666666</v>
       </c>
       <c r="B51">
-        <v>1234.617</v>
+        <v>2520.073</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46308.52083333334</v>
+        <v>46309.52083333334</v>
       </c>
       <c r="B52">
-        <v>1221.321</v>
+        <v>2517.328</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46308.53125</v>
+        <v>46309.53125</v>
       </c>
       <c r="B53">
-        <v>1205.113</v>
+        <v>2502.531</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46308.54166666666</v>
+        <v>46309.54166666666</v>
       </c>
       <c r="B54">
-        <v>1172.049</v>
+        <v>2477.756</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46308.55208333334</v>
+        <v>46309.55208333334</v>
       </c>
       <c r="B55">
-        <v>1142.258</v>
+        <v>2442.452</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46308.5625</v>
+        <v>46309.5625</v>
       </c>
       <c r="B56">
-        <v>1108.29</v>
+        <v>2415.764</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46308.57291666666</v>
+        <v>46309.57291666666</v>
       </c>
       <c r="B57">
-        <v>1062.624</v>
+        <v>2362.7</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46308.58333333334</v>
+        <v>46309.58333333334</v>
       </c>
       <c r="B58">
-        <v>982.692</v>
+        <v>2245.56</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46308.59375</v>
+        <v>46309.59375</v>
       </c>
       <c r="B59">
-        <v>939.6420000000001</v>
+        <v>2158.203</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46308.60416666666</v>
+        <v>46309.60416666666</v>
       </c>
       <c r="B60">
-        <v>878.764</v>
+        <v>2062.563</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46308.61458333334</v>
+        <v>46309.61458333334</v>
       </c>
       <c r="B61">
-        <v>830.458</v>
+        <v>1948.063</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46308.625</v>
+        <v>46309.625</v>
       </c>
       <c r="B62">
-        <v>689.139</v>
+        <v>1683.591</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46308.63541666666</v>
+        <v>46309.63541666666</v>
       </c>
       <c r="B63">
-        <v>617.178</v>
+        <v>1523.397</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46308.64583333334</v>
+        <v>46309.64583333334</v>
       </c>
       <c r="B64">
-        <v>550.561</v>
+        <v>1346.441</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46308.65625</v>
+        <v>46309.65625</v>
       </c>
       <c r="B65">
-        <v>473.79</v>
+        <v>1175.368</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46308.66666666666</v>
+        <v>46309.66666666666</v>
       </c>
       <c r="B66">
-        <v>350.573</v>
+        <v>864.7329999999999</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46308.67708333334</v>
+        <v>46309.67708333334</v>
       </c>
       <c r="B67">
-        <v>287.091</v>
+        <v>692.068</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46308.6875</v>
+        <v>46309.6875</v>
       </c>
       <c r="B68">
-        <v>221.64</v>
+        <v>510.233</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46308.69791666666</v>
+        <v>46309.69791666666</v>
       </c>
       <c r="B69">
-        <v>166.727</v>
+        <v>363.688</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46308.70833333334</v>
+        <v>46309.70833333334</v>
       </c>
       <c r="B70">
-        <v>87.72</v>
+        <v>210.057</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46308.71875</v>
+        <v>46309.71875</v>
       </c>
       <c r="B71">
-        <v>59.464</v>
+        <v>124.612</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46308.72916666666</v>
+        <v>46309.72916666666</v>
       </c>
       <c r="B72">
-        <v>39.771</v>
+        <v>85.84</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46308.73958333334</v>
+        <v>46309.73958333334</v>
       </c>
       <c r="B73">
-        <v>34.298</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46308.75</v>
+        <v>46309.75</v>
       </c>
       <c r="B74">
-        <v>46.348</v>
+        <v>49.344</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46308.76041666666</v>
+        <v>46309.76041666666</v>
       </c>
       <c r="B75">
-        <v>56.29</v>
+        <v>55.366</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46308.77083333334</v>
+        <v>46309.77083333334</v>
       </c>
       <c r="B76">
-        <v>56.574</v>
+        <v>66.65000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46308.78125</v>
+        <v>46309.78125</v>
       </c>
       <c r="B77">
-        <v>55.174</v>
+        <v>68.53400000000001</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46308.79166666666</v>
+        <v>46309.79166666666</v>
       </c>
       <c r="B78">
-        <v>54.032</v>
+        <v>52.568</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46308.80208333334</v>
+        <v>46309.80208333334</v>
       </c>
       <c r="B79">
-        <v>51.132</v>
+        <v>68.16800000000001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46308.8125</v>
+        <v>46309.8125</v>
       </c>
       <c r="B80">
-        <v>49.732</v>
+        <v>63.368</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46308.82291666666</v>
+        <v>46309.82291666666</v>
       </c>
       <c r="B81">
-        <v>50.632</v>
+        <v>61.068</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46308.83333333334</v>
+        <v>46309.83333333334</v>
       </c>
       <c r="B82">
-        <v>19.852</v>
+        <v>51.688</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46308.84375</v>
+        <v>46309.84375</v>
       </c>
       <c r="B83">
-        <v>19.152</v>
+        <v>16.688</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46308.85416666666</v>
+        <v>46309.85416666666</v>
       </c>
       <c r="B84">
-        <v>21.352</v>
+        <v>3.588</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46308.86458333334</v>
+        <v>46309.86458333334</v>
       </c>
       <c r="B85">
-        <v>21.152</v>
+        <v>3.988</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46308.875</v>
+        <v>46309.875</v>
       </c>
       <c r="B86">
-        <v>9.651999999999999</v>
+        <v>14.288</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46308.88541666666</v>
+        <v>46309.88541666666</v>
       </c>
       <c r="B87">
-        <v>21.052</v>
+        <v>4.788</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46308.89583333334</v>
+        <v>46309.89583333334</v>
       </c>
       <c r="B88">
-        <v>3.252</v>
+        <v>3.588</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46308.90625</v>
+        <v>46309.90625</v>
       </c>
       <c r="B89">
-        <v>4.052</v>
+        <v>4.788</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46308.91666666666</v>
+        <v>46309.91666666666</v>
       </c>
       <c r="B90">
-        <v>1.252</v>
+        <v>1.188</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -394,714 +394,714 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46309</v>
+        <v>46311</v>
       </c>
       <c r="B2">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46309.01041666666</v>
+        <v>46311.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46309.02083333334</v>
+        <v>46311.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46309.03125</v>
+        <v>46311.03125</v>
       </c>
       <c r="B5">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46309.04166666666</v>
+        <v>46311.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.268</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46309.05208333334</v>
+        <v>46311.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.668</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46309.0625</v>
+        <v>46311.0625</v>
       </c>
       <c r="B8">
-        <v>1.668</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46309.07291666666</v>
+        <v>46311.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.268</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46309.08333333334</v>
+        <v>46311.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.568</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46309.09375</v>
+        <v>46311.09375</v>
       </c>
       <c r="B11">
-        <v>1.268</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46309.10416666666</v>
+        <v>46311.10416666666</v>
       </c>
       <c r="B12">
-        <v>2.768</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46309.11458333334</v>
+        <v>46311.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.268</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46309.125</v>
+        <v>46311.125</v>
       </c>
       <c r="B14">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46309.13541666666</v>
+        <v>46311.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.388</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46309.14583333334</v>
+        <v>46311.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46309.15625</v>
+        <v>46311.15625</v>
       </c>
       <c r="B17">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46309.16666666666</v>
+        <v>46311.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46309.17708333334</v>
+        <v>46311.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46309.1875</v>
+        <v>46311.1875</v>
       </c>
       <c r="B20">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46309.19791666666</v>
+        <v>46311.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46309.20833333334</v>
+        <v>46311.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.533</v>
+        <v>1.022</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46309.21875</v>
+        <v>46311.21875</v>
       </c>
       <c r="B23">
-        <v>1.269</v>
+        <v>7.554</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46309.22916666666</v>
+        <v>46311.22916666666</v>
       </c>
       <c r="B24">
-        <v>1.983</v>
+        <v>8.124000000000001</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46309.23958333334</v>
+        <v>46311.23958333334</v>
       </c>
       <c r="B25">
-        <v>3.766</v>
+        <v>2.453</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46309.25</v>
+        <v>46311.25</v>
       </c>
       <c r="B26">
-        <v>9.045</v>
+        <v>8.285</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46309.26041666666</v>
+        <v>46311.26041666666</v>
       </c>
       <c r="B27">
-        <v>12.64</v>
+        <v>10.025</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46309.27083333334</v>
+        <v>46311.27083333334</v>
       </c>
       <c r="B28">
-        <v>18.433</v>
+        <v>12.802</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46309.28125</v>
+        <v>46311.28125</v>
       </c>
       <c r="B29">
-        <v>35.339</v>
+        <v>31.093</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46309.29166666666</v>
+        <v>46311.29166666666</v>
       </c>
       <c r="B30">
-        <v>158.95</v>
+        <v>137.296</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46309.30208333334</v>
+        <v>46311.30208333334</v>
       </c>
       <c r="B31">
-        <v>250.122</v>
+        <v>203.891</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46309.3125</v>
+        <v>46311.3125</v>
       </c>
       <c r="B32">
-        <v>351.868</v>
+        <v>295.87</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46309.32291666666</v>
+        <v>46311.32291666666</v>
       </c>
       <c r="B33">
-        <v>460.851</v>
+        <v>397.35</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46309.33333333334</v>
+        <v>46311.33333333334</v>
       </c>
       <c r="B34">
-        <v>729.88</v>
+        <v>644.127</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46309.34375</v>
+        <v>46311.34375</v>
       </c>
       <c r="B35">
-        <v>883.856</v>
+        <v>760.763</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46309.35416666666</v>
+        <v>46311.35416666666</v>
       </c>
       <c r="B36">
-        <v>1044.98</v>
+        <v>920.083</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46309.36458333334</v>
+        <v>46311.36458333334</v>
       </c>
       <c r="B37">
-        <v>1190.297</v>
+        <v>1042.677</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46309.375</v>
+        <v>46311.375</v>
       </c>
       <c r="B38">
-        <v>1466.624</v>
+        <v>1257.786</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46309.38541666666</v>
+        <v>46311.38541666666</v>
       </c>
       <c r="B39">
-        <v>1619.946</v>
+        <v>1378.822</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46309.39583333334</v>
+        <v>46311.39583333334</v>
       </c>
       <c r="B40">
-        <v>1745.661</v>
+        <v>1520.97</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46309.40625</v>
+        <v>46311.40625</v>
       </c>
       <c r="B41">
-        <v>1863.256</v>
+        <v>1636.746</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46309.41666666666</v>
+        <v>46311.41666666666</v>
       </c>
       <c r="B42">
-        <v>2076.265</v>
+        <v>1799.183</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46309.42708333334</v>
+        <v>46311.42708333334</v>
       </c>
       <c r="B43">
-        <v>2159.4</v>
+        <v>1899.548</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46309.4375</v>
+        <v>46311.4375</v>
       </c>
       <c r="B44">
-        <v>2230.061</v>
+        <v>2003.66</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46309.44791666666</v>
+        <v>46311.44791666666</v>
       </c>
       <c r="B45">
-        <v>2299.546</v>
+        <v>2086.015</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46309.45833333334</v>
+        <v>46311.45833333334</v>
       </c>
       <c r="B46">
-        <v>2400.656</v>
+        <v>2192.551</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46309.46875</v>
+        <v>46311.46875</v>
       </c>
       <c r="B47">
-        <v>2440.426</v>
+        <v>2235.983</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46309.47916666666</v>
+        <v>46311.47916666666</v>
       </c>
       <c r="B48">
-        <v>2471.592</v>
+        <v>2265.774</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46309.48958333334</v>
+        <v>46311.48958333334</v>
       </c>
       <c r="B49">
-        <v>2486.946</v>
+        <v>2283.944</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46309.5</v>
+        <v>46311.5</v>
       </c>
       <c r="B50">
-        <v>2519.963</v>
+        <v>2255.933</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46309.51041666666</v>
+        <v>46311.51041666666</v>
       </c>
       <c r="B51">
-        <v>2520.073</v>
+        <v>2235.344</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46309.52083333334</v>
+        <v>46311.52083333334</v>
       </c>
       <c r="B52">
-        <v>2517.328</v>
+        <v>2205.196</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46309.53125</v>
+        <v>46311.53125</v>
       </c>
       <c r="B53">
-        <v>2502.531</v>
+        <v>2162.365</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46309.54166666666</v>
+        <v>46311.54166666666</v>
       </c>
       <c r="B54">
-        <v>2477.756</v>
+        <v>2072.878</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46309.55208333334</v>
+        <v>46311.55208333334</v>
       </c>
       <c r="B55">
-        <v>2442.452</v>
+        <v>2007.238</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46309.5625</v>
+        <v>46311.5625</v>
       </c>
       <c r="B56">
-        <v>2415.764</v>
+        <v>1944.759</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46309.57291666666</v>
+        <v>46311.57291666666</v>
       </c>
       <c r="B57">
-        <v>2362.7</v>
+        <v>1869.705</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46309.58333333334</v>
+        <v>46311.58333333334</v>
       </c>
       <c r="B58">
-        <v>2245.56</v>
+        <v>1722.182</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46309.59375</v>
+        <v>46311.59375</v>
       </c>
       <c r="B59">
-        <v>2158.203</v>
+        <v>1629.759</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46309.60416666666</v>
+        <v>46311.60416666666</v>
       </c>
       <c r="B60">
-        <v>2062.563</v>
+        <v>1529.686</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46309.61458333334</v>
+        <v>46311.61458333334</v>
       </c>
       <c r="B61">
-        <v>1948.063</v>
+        <v>1429.378</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46309.625</v>
+        <v>46311.625</v>
       </c>
       <c r="B62">
-        <v>1683.591</v>
+        <v>1214.323</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46309.63541666666</v>
+        <v>46311.63541666666</v>
       </c>
       <c r="B63">
-        <v>1523.397</v>
+        <v>1112.456</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46309.64583333334</v>
+        <v>46311.64583333334</v>
       </c>
       <c r="B64">
-        <v>1346.441</v>
+        <v>990.564</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46309.65625</v>
+        <v>46311.65625</v>
       </c>
       <c r="B65">
-        <v>1175.368</v>
+        <v>867.644</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46309.66666666666</v>
+        <v>46311.66666666666</v>
       </c>
       <c r="B66">
-        <v>864.7329999999999</v>
+        <v>622.653</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46309.67708333334</v>
+        <v>46311.67708333334</v>
       </c>
       <c r="B67">
-        <v>692.068</v>
+        <v>502.217</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46309.6875</v>
+        <v>46311.6875</v>
       </c>
       <c r="B68">
-        <v>510.233</v>
+        <v>365.38</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46309.69791666666</v>
+        <v>46311.69791666666</v>
       </c>
       <c r="B69">
-        <v>363.688</v>
+        <v>256.264</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46309.70833333334</v>
+        <v>46311.70833333334</v>
       </c>
       <c r="B70">
-        <v>210.057</v>
+        <v>118.902</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46309.71875</v>
+        <v>46311.71875</v>
       </c>
       <c r="B71">
-        <v>124.612</v>
+        <v>58.81</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46309.72916666666</v>
+        <v>46311.72916666666</v>
       </c>
       <c r="B72">
-        <v>85.84</v>
+        <v>40.696</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46309.73958333334</v>
+        <v>46311.73958333334</v>
       </c>
       <c r="B73">
-        <v>72.8</v>
+        <v>33.985</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46309.75</v>
+        <v>46311.75</v>
       </c>
       <c r="B74">
-        <v>49.344</v>
+        <v>55.406</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46309.76041666666</v>
+        <v>46311.76041666666</v>
       </c>
       <c r="B75">
-        <v>55.366</v>
+        <v>61.149</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46309.77083333334</v>
+        <v>46311.77083333334</v>
       </c>
       <c r="B76">
-        <v>66.65000000000001</v>
+        <v>59.221</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46309.78125</v>
+        <v>46311.78125</v>
       </c>
       <c r="B77">
-        <v>68.53400000000001</v>
+        <v>60.005</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46309.79166666666</v>
+        <v>46311.79166666666</v>
       </c>
       <c r="B78">
-        <v>52.568</v>
+        <v>57.56</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46309.80208333334</v>
+        <v>46311.80208333334</v>
       </c>
       <c r="B79">
-        <v>68.16800000000001</v>
+        <v>57.26</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46309.8125</v>
+        <v>46311.8125</v>
       </c>
       <c r="B80">
-        <v>63.368</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46309.82291666666</v>
+        <v>46311.82291666666</v>
       </c>
       <c r="B81">
-        <v>61.068</v>
+        <v>54.46</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46309.83333333334</v>
+        <v>46311.83333333334</v>
       </c>
       <c r="B82">
-        <v>51.688</v>
+        <v>44.38</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46309.84375</v>
+        <v>46311.84375</v>
       </c>
       <c r="B83">
-        <v>16.688</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46309.85416666666</v>
+        <v>46311.85416666666</v>
       </c>
       <c r="B84">
-        <v>3.588</v>
+        <v>41.08</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46309.86458333334</v>
+        <v>46311.86458333334</v>
       </c>
       <c r="B85">
-        <v>3.988</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46309.875</v>
+        <v>46311.875</v>
       </c>
       <c r="B86">
-        <v>14.288</v>
+        <v>23.48</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46309.88541666666</v>
+        <v>46311.88541666666</v>
       </c>
       <c r="B87">
-        <v>4.788</v>
+        <v>21.48</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46309.89583333334</v>
+        <v>46311.89583333334</v>
       </c>
       <c r="B88">
-        <v>3.588</v>
+        <v>19.18</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="2">
-        <v>46309.90625</v>
+        <v>46311.90625</v>
       </c>
       <c r="B89">
-        <v>4.788</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="2">
-        <v>46309.91666666666</v>
+        <v>46311.91666666666</v>
       </c>
       <c r="B90">
-        <v>1.188</v>
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B90"/>
+  <dimension ref="A1:B88"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,714 +394,698 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46311</v>
+        <v>46316</v>
       </c>
       <c r="B2">
-        <v>1.08</v>
+        <v>7.688</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46311.01041666666</v>
+        <v>46316.01041666666</v>
       </c>
       <c r="B3">
-        <v>1.08</v>
+        <v>7.688</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46311.02083333334</v>
+        <v>46316.02083333334</v>
       </c>
       <c r="B4">
-        <v>1.08</v>
+        <v>7.688</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46311.03125</v>
+        <v>46316.03125</v>
       </c>
       <c r="B5">
-        <v>1.08</v>
+        <v>7.688</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46311.04166666666</v>
+        <v>46316.04166666666</v>
       </c>
       <c r="B6">
-        <v>1.46</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46311.05208333334</v>
+        <v>46316.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.66</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46311.0625</v>
+        <v>46316.0625</v>
       </c>
       <c r="B8">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46311.07291666666</v>
+        <v>46316.07291666666</v>
       </c>
       <c r="B9">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46311.08333333334</v>
+        <v>46316.08333333334</v>
       </c>
       <c r="B10">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46311.09375</v>
+        <v>46316.09375</v>
       </c>
       <c r="B11">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46311.10416666666</v>
+        <v>46316.10416666666</v>
       </c>
       <c r="B12">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46311.11458333334</v>
+        <v>46316.11458333334</v>
       </c>
       <c r="B13">
-        <v>1.16</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46311.125</v>
+        <v>46316.125</v>
       </c>
       <c r="B14">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46311.13541666666</v>
+        <v>46316.13541666666</v>
       </c>
       <c r="B15">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46311.14583333334</v>
+        <v>46316.14583333334</v>
       </c>
       <c r="B16">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46311.15625</v>
+        <v>46316.15625</v>
       </c>
       <c r="B17">
-        <v>1.08</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46311.16666666666</v>
+        <v>46316.16666666666</v>
       </c>
       <c r="B18">
-        <v>1.08</v>
+        <v>25.188</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46311.17708333334</v>
+        <v>46316.17708333334</v>
       </c>
       <c r="B19">
-        <v>1.08</v>
+        <v>25.288</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46311.1875</v>
+        <v>46316.1875</v>
       </c>
       <c r="B20">
-        <v>1.08</v>
+        <v>25.488</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46311.19791666666</v>
+        <v>46316.19791666666</v>
       </c>
       <c r="B21">
-        <v>1.08</v>
+        <v>25.688</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46311.20833333334</v>
+        <v>46316.20833333334</v>
       </c>
       <c r="B22">
-        <v>1.022</v>
+        <v>20.752</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46311.21875</v>
+        <v>46316.21875</v>
       </c>
       <c r="B23">
-        <v>7.554</v>
+        <v>21.192</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46311.22916666666</v>
+        <v>46316.22916666666</v>
       </c>
       <c r="B24">
-        <v>8.124000000000001</v>
+        <v>21.348</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46311.23958333334</v>
+        <v>46316.23958333334</v>
       </c>
       <c r="B25">
-        <v>2.453</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46311.25</v>
+        <v>46316.25</v>
       </c>
       <c r="B26">
-        <v>8.285</v>
+        <v>15.374</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46311.26041666666</v>
+        <v>46316.26041666666</v>
       </c>
       <c r="B27">
-        <v>10.025</v>
+        <v>15.819</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46311.27083333334</v>
+        <v>46316.27083333334</v>
       </c>
       <c r="B28">
-        <v>12.802</v>
+        <v>16.612</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46311.28125</v>
+        <v>46316.28125</v>
       </c>
       <c r="B29">
-        <v>31.093</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46311.29166666666</v>
+        <v>46316.29166666666</v>
       </c>
       <c r="B30">
-        <v>137.296</v>
+        <v>134.456</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46311.30208333334</v>
+        <v>46316.30208333334</v>
       </c>
       <c r="B31">
-        <v>203.891</v>
+        <v>199.37</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46311.3125</v>
+        <v>46316.3125</v>
       </c>
       <c r="B32">
-        <v>295.87</v>
+        <v>321.724</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46311.32291666666</v>
+        <v>46316.32291666666</v>
       </c>
       <c r="B33">
-        <v>397.35</v>
+        <v>449.13</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46311.33333333334</v>
+        <v>46316.33333333334</v>
       </c>
       <c r="B34">
-        <v>644.127</v>
+        <v>788.684</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46311.34375</v>
+        <v>46316.34375</v>
       </c>
       <c r="B35">
-        <v>760.763</v>
+        <v>970.168</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46311.35416666666</v>
+        <v>46316.35416666666</v>
       </c>
       <c r="B36">
-        <v>920.083</v>
+        <v>1162.631</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46311.36458333334</v>
+        <v>46316.36458333334</v>
       </c>
       <c r="B37">
-        <v>1042.677</v>
+        <v>1329.529</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46311.375</v>
+        <v>46316.375</v>
       </c>
       <c r="B38">
-        <v>1257.786</v>
+        <v>1668.261</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46311.38541666666</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="B39">
-        <v>1378.822</v>
+        <v>1817.922</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46311.39583333334</v>
+        <v>46316.39583333334</v>
       </c>
       <c r="B40">
-        <v>1520.97</v>
+        <v>1992.754</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46311.40625</v>
+        <v>46316.40625</v>
       </c>
       <c r="B41">
-        <v>1636.746</v>
+        <v>2130.33</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46311.41666666666</v>
+        <v>46316.41666666666</v>
       </c>
       <c r="B42">
-        <v>1799.183</v>
+        <v>2370.992</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46311.42708333334</v>
+        <v>46316.42708333334</v>
       </c>
       <c r="B43">
-        <v>1899.548</v>
+        <v>2488.317</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46311.4375</v>
+        <v>46316.4375</v>
       </c>
       <c r="B44">
-        <v>2003.66</v>
+        <v>2577.48</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46311.44791666666</v>
+        <v>46316.44791666666</v>
       </c>
       <c r="B45">
-        <v>2086.015</v>
+        <v>2658.241</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46311.45833333334</v>
+        <v>46316.45833333334</v>
       </c>
       <c r="B46">
-        <v>2192.551</v>
+        <v>2786.73</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46311.46875</v>
+        <v>46316.46875</v>
       </c>
       <c r="B47">
-        <v>2235.983</v>
+        <v>2837.678</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46311.47916666666</v>
+        <v>46316.47916666666</v>
       </c>
       <c r="B48">
-        <v>2265.774</v>
+        <v>2893.517</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46311.48958333334</v>
+        <v>46316.48958333334</v>
       </c>
       <c r="B49">
-        <v>2283.944</v>
+        <v>2921.718</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46311.5</v>
+        <v>46316.5</v>
       </c>
       <c r="B50">
-        <v>2255.933</v>
+        <v>2945.099</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46311.51041666666</v>
+        <v>46316.51041666666</v>
       </c>
       <c r="B51">
-        <v>2235.344</v>
+        <v>2955.308</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46311.52083333334</v>
+        <v>46316.52083333334</v>
       </c>
       <c r="B52">
-        <v>2205.196</v>
+        <v>2954.072</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46311.53125</v>
+        <v>46316.53125</v>
       </c>
       <c r="B53">
-        <v>2162.365</v>
+        <v>2948.462</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46311.54166666666</v>
+        <v>46316.54166666666</v>
       </c>
       <c r="B54">
-        <v>2072.878</v>
+        <v>2899.119</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46311.55208333334</v>
+        <v>46316.55208333334</v>
       </c>
       <c r="B55">
-        <v>2007.238</v>
+        <v>2865.234</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46311.5625</v>
+        <v>46316.5625</v>
       </c>
       <c r="B56">
-        <v>1944.759</v>
+        <v>2795.538</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46311.57291666666</v>
+        <v>46316.57291666666</v>
       </c>
       <c r="B57">
-        <v>1869.705</v>
+        <v>2730.767</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46311.58333333334</v>
+        <v>46316.58333333334</v>
       </c>
       <c r="B58">
-        <v>1722.182</v>
+        <v>2553.966</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46311.59375</v>
+        <v>46316.59375</v>
       </c>
       <c r="B59">
-        <v>1629.759</v>
+        <v>2439.794</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46311.60416666666</v>
+        <v>46316.60416666666</v>
       </c>
       <c r="B60">
-        <v>1529.686</v>
+        <v>2302.919</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46311.61458333334</v>
+        <v>46316.61458333334</v>
       </c>
       <c r="B61">
-        <v>1429.378</v>
+        <v>2164.674</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46311.625</v>
+        <v>46316.625</v>
       </c>
       <c r="B62">
-        <v>1214.323</v>
+        <v>1810.539</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46311.63541666666</v>
+        <v>46316.63541666666</v>
       </c>
       <c r="B63">
-        <v>1112.456</v>
+        <v>1627.316</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46311.64583333334</v>
+        <v>46316.64583333334</v>
       </c>
       <c r="B64">
-        <v>990.564</v>
+        <v>1410.572</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46311.65625</v>
+        <v>46316.65625</v>
       </c>
       <c r="B65">
-        <v>867.644</v>
+        <v>1210.464</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46311.66666666666</v>
+        <v>46316.66666666666</v>
       </c>
       <c r="B66">
-        <v>622.653</v>
+        <v>827.659</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46311.67708333334</v>
+        <v>46316.67708333334</v>
       </c>
       <c r="B67">
-        <v>502.217</v>
+        <v>637.504</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46311.6875</v>
+        <v>46316.6875</v>
       </c>
       <c r="B68">
-        <v>365.38</v>
+        <v>443.47</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46311.69791666666</v>
+        <v>46316.69791666666</v>
       </c>
       <c r="B69">
-        <v>256.264</v>
+        <v>295.783</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46311.70833333334</v>
+        <v>46316.70833333334</v>
       </c>
       <c r="B70">
-        <v>118.902</v>
+        <v>145.038</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46311.71875</v>
+        <v>46316.71875</v>
       </c>
       <c r="B71">
-        <v>58.81</v>
+        <v>88.496</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46311.72916666666</v>
+        <v>46316.72916666666</v>
       </c>
       <c r="B72">
-        <v>40.696</v>
+        <v>73.637</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46311.73958333334</v>
+        <v>46316.73958333334</v>
       </c>
       <c r="B73">
-        <v>33.985</v>
+        <v>71.193</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46311.75</v>
+        <v>46316.75</v>
       </c>
       <c r="B74">
-        <v>55.406</v>
+        <v>65.02500000000001</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46311.76041666666</v>
+        <v>46316.76041666666</v>
       </c>
       <c r="B75">
-        <v>61.149</v>
+        <v>62.165</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46311.77083333334</v>
+        <v>46316.77083333334</v>
       </c>
       <c r="B76">
-        <v>59.221</v>
+        <v>63.345</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46311.78125</v>
+        <v>46316.78125</v>
       </c>
       <c r="B77">
-        <v>60.005</v>
+        <v>60.121</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46311.79166666666</v>
+        <v>46316.79166666666</v>
       </c>
       <c r="B78">
-        <v>57.56</v>
+        <v>53.962</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46311.80208333334</v>
+        <v>46316.80208333334</v>
       </c>
       <c r="B79">
-        <v>57.26</v>
+        <v>53.168</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46311.8125</v>
+        <v>46316.8125</v>
       </c>
       <c r="B80">
-        <v>53.96</v>
+        <v>53.068</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46311.82291666666</v>
+        <v>46316.82291666666</v>
       </c>
       <c r="B81">
-        <v>54.46</v>
+        <v>53.168</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46311.83333333334</v>
+        <v>46316.83333333334</v>
       </c>
       <c r="B82">
-        <v>44.38</v>
+        <v>9.188000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46311.84375</v>
+        <v>46316.84375</v>
       </c>
       <c r="B83">
-        <v>41.18</v>
+        <v>13.588</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46311.85416666666</v>
+        <v>46316.85416666666</v>
       </c>
       <c r="B84">
-        <v>41.08</v>
+        <v>12.088</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46311.86458333334</v>
+        <v>46316.86458333334</v>
       </c>
       <c r="B85">
-        <v>1.88</v>
+        <v>12.488</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46311.875</v>
+        <v>46316.875</v>
       </c>
       <c r="B86">
-        <v>23.48</v>
+        <v>14.888</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46311.88541666666</v>
+        <v>46316.88541666666</v>
       </c>
       <c r="B87">
-        <v>21.48</v>
+        <v>14.088</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46311.89583333334</v>
+        <v>46316.89583333334</v>
       </c>
       <c r="B88">
-        <v>19.18</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" s="2">
-        <v>46311.90625</v>
-      </c>
-      <c r="B89">
-        <v>2.68</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" s="2">
-        <v>46311.91666666666</v>
-      </c>
-      <c r="B90">
-        <v>1.08</v>
+        <v>7.688</v>
       </c>
     </row>
   </sheetData>

--- a/data_fetching/Entsoe/Notified_Production_Solar.xlsx
+++ b/data_fetching/Entsoe/Notified_Production_Solar.xlsx
@@ -381,7 +381,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B88"/>
+  <dimension ref="A1:B97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -394,39 +394,39 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="2">
-        <v>46316</v>
+        <v>46320</v>
       </c>
       <c r="B2">
-        <v>7.688</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2">
-        <v>46316.01041666666</v>
+        <v>46320.01041666666</v>
       </c>
       <c r="B3">
-        <v>7.688</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2">
-        <v>46316.02083333334</v>
+        <v>46320.02083333334</v>
       </c>
       <c r="B4">
-        <v>7.688</v>
+        <v>1.188</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2">
-        <v>46316.03125</v>
+        <v>46320.03125</v>
       </c>
       <c r="B5">
-        <v>7.688</v>
+        <v>1.288</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2">
-        <v>46316.04166666666</v>
+        <v>46320.04166666666</v>
       </c>
       <c r="B6">
         <v>1.268</v>
@@ -434,15 +434,15 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2">
-        <v>46316.05208333334</v>
+        <v>46320.05208333334</v>
       </c>
       <c r="B7">
-        <v>1.268</v>
+        <v>1.368</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2">
-        <v>46316.0625</v>
+        <v>46320.0625</v>
       </c>
       <c r="B8">
         <v>1.268</v>
@@ -450,7 +450,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2">
-        <v>46316.07291666666</v>
+        <v>46320.07291666666</v>
       </c>
       <c r="B9">
         <v>1.268</v>
@@ -458,7 +458,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2">
-        <v>46316.08333333334</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B10">
         <v>1.268</v>
@@ -466,7 +466,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2">
-        <v>46316.09375</v>
+        <v>46320.09375</v>
       </c>
       <c r="B11">
         <v>1.268</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2">
-        <v>46316.10416666666</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B12">
         <v>1.268</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2">
-        <v>46316.11458333334</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B13">
         <v>1.268</v>
@@ -490,601 +490,673 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2">
-        <v>46316.125</v>
+        <v>46320.08333333334</v>
       </c>
       <c r="B14">
-        <v>1.188</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2">
-        <v>46316.13541666666</v>
+        <v>46320.09375</v>
       </c>
       <c r="B15">
-        <v>1.188</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2">
-        <v>46316.14583333334</v>
+        <v>46320.10416666666</v>
       </c>
       <c r="B16">
-        <v>1.188</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2">
-        <v>46316.15625</v>
+        <v>46320.11458333334</v>
       </c>
       <c r="B17">
-        <v>1.188</v>
+        <v>1.268</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="2">
-        <v>46316.16666666666</v>
+        <v>46320.125</v>
       </c>
       <c r="B18">
-        <v>25.188</v>
+        <v>1.287</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="2">
-        <v>46316.17708333334</v>
+        <v>46320.13541666666</v>
       </c>
       <c r="B19">
-        <v>25.288</v>
+        <v>1.323</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="2">
-        <v>46316.1875</v>
+        <v>46320.14583333334</v>
       </c>
       <c r="B20">
-        <v>25.488</v>
+        <v>1.377</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="2">
-        <v>46316.19791666666</v>
+        <v>46320.15625</v>
       </c>
       <c r="B21">
-        <v>25.688</v>
+        <v>1.445</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="2">
-        <v>46316.20833333334</v>
+        <v>46320.16666666666</v>
       </c>
       <c r="B22">
-        <v>20.752</v>
+        <v>1.797</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="2">
-        <v>46316.21875</v>
+        <v>46320.17708333334</v>
       </c>
       <c r="B23">
-        <v>21.192</v>
+        <v>1.885</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="2">
-        <v>46316.22916666666</v>
+        <v>46320.1875</v>
       </c>
       <c r="B24">
-        <v>21.348</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="2">
-        <v>46316.23958333334</v>
+        <v>46320.19791666666</v>
       </c>
       <c r="B25">
-        <v>21.86</v>
+        <v>3.157</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="2">
-        <v>46316.25</v>
+        <v>46320.20833333334</v>
       </c>
       <c r="B26">
-        <v>15.374</v>
+        <v>11.806</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="2">
-        <v>46316.26041666666</v>
+        <v>46320.21875</v>
       </c>
       <c r="B27">
-        <v>15.819</v>
+        <v>14.574</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="2">
-        <v>46316.27083333334</v>
+        <v>46320.22916666666</v>
       </c>
       <c r="B28">
-        <v>16.612</v>
+        <v>21.692</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="2">
-        <v>46316.28125</v>
+        <v>46320.23958333334</v>
       </c>
       <c r="B29">
-        <v>32.8</v>
+        <v>29.414</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="2">
-        <v>46316.29166666666</v>
+        <v>46320.25</v>
       </c>
       <c r="B30">
-        <v>134.456</v>
+        <v>74.223</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="2">
-        <v>46316.30208333334</v>
+        <v>46320.26041666666</v>
       </c>
       <c r="B31">
-        <v>199.37</v>
+        <v>114.032</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="2">
-        <v>46316.3125</v>
+        <v>46320.27083333334</v>
       </c>
       <c r="B32">
-        <v>321.724</v>
+        <v>199.836</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="2">
-        <v>46316.32291666666</v>
+        <v>46320.28125</v>
       </c>
       <c r="B33">
-        <v>449.13</v>
+        <v>297.479</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="2">
-        <v>46316.33333333334</v>
+        <v>46320.29166666666</v>
       </c>
       <c r="B34">
-        <v>788.684</v>
+        <v>499.411</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="2">
-        <v>46316.34375</v>
+        <v>46320.30208333334</v>
       </c>
       <c r="B35">
-        <v>970.168</v>
+        <v>635.172</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="2">
-        <v>46316.35416666666</v>
+        <v>46320.3125</v>
       </c>
       <c r="B36">
-        <v>1162.631</v>
+        <v>793.854</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="2">
-        <v>46316.36458333334</v>
+        <v>46320.32291666666</v>
       </c>
       <c r="B37">
-        <v>1329.529</v>
+        <v>946.849</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="2">
-        <v>46316.375</v>
+        <v>46320.33333333334</v>
       </c>
       <c r="B38">
-        <v>1668.261</v>
+        <v>1239.558</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2">
-        <v>46316.38541666666</v>
+        <v>46320.34375</v>
       </c>
       <c r="B39">
-        <v>1817.922</v>
+        <v>1385.831</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="2">
-        <v>46316.39583333334</v>
+        <v>46320.35416666666</v>
       </c>
       <c r="B40">
-        <v>1992.754</v>
+        <v>1509.984</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="2">
-        <v>46316.40625</v>
+        <v>46320.36458333334</v>
       </c>
       <c r="B41">
-        <v>2130.33</v>
+        <v>1648.906</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="2">
-        <v>46316.41666666666</v>
+        <v>46320.375</v>
       </c>
       <c r="B42">
-        <v>2370.992</v>
+        <v>1885.642</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="2">
-        <v>46316.42708333334</v>
+        <v>46320.38541666666</v>
       </c>
       <c r="B43">
-        <v>2488.317</v>
+        <v>1998.614</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="2">
-        <v>46316.4375</v>
+        <v>46320.39583333334</v>
       </c>
       <c r="B44">
-        <v>2577.48</v>
+        <v>2087.851</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="2">
-        <v>46316.44791666666</v>
+        <v>46320.40625</v>
       </c>
       <c r="B45">
-        <v>2658.241</v>
+        <v>2156.544</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="2">
-        <v>46316.45833333334</v>
+        <v>46320.41666666666</v>
       </c>
       <c r="B46">
-        <v>2786.73</v>
+        <v>2307.926</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="2">
-        <v>46316.46875</v>
+        <v>46320.42708333334</v>
       </c>
       <c r="B47">
-        <v>2837.678</v>
+        <v>2356.506</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="2">
-        <v>46316.47916666666</v>
+        <v>46320.4375</v>
       </c>
       <c r="B48">
-        <v>2893.517</v>
+        <v>2391.671</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="2">
-        <v>46316.48958333334</v>
+        <v>46320.44791666666</v>
       </c>
       <c r="B49">
-        <v>2921.718</v>
+        <v>2412.879</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2">
-        <v>46316.5</v>
+        <v>46320.45833333334</v>
       </c>
       <c r="B50">
-        <v>2945.099</v>
+        <v>2456.568</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="2">
-        <v>46316.51041666666</v>
+        <v>46320.46875</v>
       </c>
       <c r="B51">
-        <v>2955.308</v>
+        <v>2454.316</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="2">
-        <v>46316.52083333334</v>
+        <v>46320.47916666666</v>
       </c>
       <c r="B52">
-        <v>2954.072</v>
+        <v>2442.91</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="2">
-        <v>46316.53125</v>
+        <v>46320.48958333334</v>
       </c>
       <c r="B53">
-        <v>2948.462</v>
+        <v>2420.129</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="2">
-        <v>46316.54166666666</v>
+        <v>46320.5</v>
       </c>
       <c r="B54">
-        <v>2899.119</v>
+        <v>2394.444</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="2">
-        <v>46316.55208333334</v>
+        <v>46320.51041666666</v>
       </c>
       <c r="B55">
-        <v>2865.234</v>
+        <v>2353.831</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="2">
-        <v>46316.5625</v>
+        <v>46320.52083333334</v>
       </c>
       <c r="B56">
-        <v>2795.538</v>
+        <v>2306.063</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="2">
-        <v>46316.57291666666</v>
+        <v>46320.53125</v>
       </c>
       <c r="B57">
-        <v>2730.767</v>
+        <v>2237.795</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="2">
-        <v>46316.58333333334</v>
+        <v>46320.54166666666</v>
       </c>
       <c r="B58">
-        <v>2553.966</v>
+        <v>2116.049</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="2">
-        <v>46316.59375</v>
+        <v>46320.55208333334</v>
       </c>
       <c r="B59">
-        <v>2439.794</v>
+        <v>2011.47</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="2">
-        <v>46316.60416666666</v>
+        <v>46320.5625</v>
       </c>
       <c r="B60">
-        <v>2302.919</v>
+        <v>1886.886</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="2">
-        <v>46316.61458333334</v>
+        <v>46320.57291666666</v>
       </c>
       <c r="B61">
-        <v>2164.674</v>
+        <v>1754.4</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="2">
-        <v>46316.625</v>
+        <v>46320.58333333334</v>
       </c>
       <c r="B62">
-        <v>1810.539</v>
+        <v>1508.313</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="2">
-        <v>46316.63541666666</v>
+        <v>46320.59375</v>
       </c>
       <c r="B63">
-        <v>1627.316</v>
+        <v>1327.8</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="2">
-        <v>46316.64583333334</v>
+        <v>46320.60416666666</v>
       </c>
       <c r="B64">
-        <v>1410.572</v>
+        <v>1132.241</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="2">
-        <v>46316.65625</v>
+        <v>46320.61458333334</v>
       </c>
       <c r="B65">
-        <v>1210.464</v>
+        <v>961.468</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="2">
-        <v>46316.66666666666</v>
+        <v>46320.625</v>
       </c>
       <c r="B66">
-        <v>827.659</v>
+        <v>678.6660000000001</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="2">
-        <v>46316.67708333334</v>
+        <v>46320.63541666666</v>
       </c>
       <c r="B67">
-        <v>637.504</v>
+        <v>501.608</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="2">
-        <v>46316.6875</v>
+        <v>46320.64583333334</v>
       </c>
       <c r="B68">
-        <v>443.47</v>
+        <v>341.035</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="2">
-        <v>46316.69791666666</v>
+        <v>46320.65625</v>
       </c>
       <c r="B69">
-        <v>295.783</v>
+        <v>222.483</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="2">
-        <v>46316.70833333334</v>
+        <v>46320.66666666666</v>
       </c>
       <c r="B70">
-        <v>145.038</v>
+        <v>102.375</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="2">
-        <v>46316.71875</v>
+        <v>46320.67708333334</v>
       </c>
       <c r="B71">
-        <v>88.496</v>
+        <v>52.653</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="2">
-        <v>46316.72916666666</v>
+        <v>46320.6875</v>
       </c>
       <c r="B72">
-        <v>73.637</v>
+        <v>38.909</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="2">
-        <v>46316.73958333334</v>
+        <v>46320.69791666666</v>
       </c>
       <c r="B73">
-        <v>71.193</v>
+        <v>32.947</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="2">
-        <v>46316.75</v>
+        <v>46320.70833333334</v>
       </c>
       <c r="B74">
-        <v>65.02500000000001</v>
+        <v>38.208</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="2">
-        <v>46316.76041666666</v>
+        <v>46320.71875</v>
       </c>
       <c r="B75">
-        <v>62.165</v>
+        <v>40.79</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="2">
-        <v>46316.77083333334</v>
+        <v>46320.72916666666</v>
       </c>
       <c r="B76">
-        <v>63.345</v>
+        <v>37.957</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="2">
-        <v>46316.78125</v>
+        <v>46320.73958333334</v>
       </c>
       <c r="B77">
-        <v>60.121</v>
+        <v>38.537</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="2">
-        <v>46316.79166666666</v>
+        <v>46320.75</v>
       </c>
       <c r="B78">
-        <v>53.962</v>
+        <v>37.968</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="2">
-        <v>46316.80208333334</v>
+        <v>46320.76041666666</v>
       </c>
       <c r="B79">
-        <v>53.168</v>
+        <v>38.368</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="2">
-        <v>46316.8125</v>
+        <v>46320.77083333334</v>
       </c>
       <c r="B80">
-        <v>53.068</v>
+        <v>33.368</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="2">
-        <v>46316.82291666666</v>
+        <v>46320.78125</v>
       </c>
       <c r="B81">
-        <v>53.168</v>
+        <v>30.768</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="2">
-        <v>46316.83333333334</v>
+        <v>46320.79166666666</v>
       </c>
       <c r="B82">
-        <v>9.188000000000001</v>
+        <v>26.368</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="2">
-        <v>46316.84375</v>
+        <v>46320.80208333334</v>
       </c>
       <c r="B83">
-        <v>13.588</v>
+        <v>26.468</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="2">
-        <v>46316.85416666666</v>
+        <v>46320.8125</v>
       </c>
       <c r="B84">
-        <v>12.088</v>
+        <v>27.768</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="2">
-        <v>46316.86458333334</v>
+        <v>46320.82291666666</v>
       </c>
       <c r="B85">
-        <v>12.488</v>
+        <v>26.668</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="2">
-        <v>46316.875</v>
+        <v>46320.83333333334</v>
       </c>
       <c r="B86">
-        <v>14.888</v>
+        <v>10.588</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="2">
-        <v>46316.88541666666</v>
+        <v>46320.84375</v>
       </c>
       <c r="B87">
-        <v>14.088</v>
+        <v>9.788</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="2">
-        <v>46316.89583333334</v>
+        <v>46320.85416666666</v>
       </c>
       <c r="B88">
+        <v>11.988</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="2">
+        <v>46320.86458333334</v>
+      </c>
+      <c r="B89">
+        <v>8.988</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="2">
+        <v>46320.875</v>
+      </c>
+      <c r="B90">
+        <v>9.188000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="2">
+        <v>46320.88541666666</v>
+      </c>
+      <c r="B91">
+        <v>9.788</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="2">
+        <v>46320.89583333334</v>
+      </c>
+      <c r="B92">
+        <v>9.188000000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="2">
+        <v>46320.90625</v>
+      </c>
+      <c r="B93">
+        <v>9.688000000000001</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="2">
+        <v>46320.91666666666</v>
+      </c>
+      <c r="B94">
+        <v>11.188</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="2">
+        <v>46320.92708333334</v>
+      </c>
+      <c r="B95">
+        <v>9.587999999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="2">
+        <v>46320.9375</v>
+      </c>
+      <c r="B96">
+        <v>8.388</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="2">
+        <v>46320.94791666666</v>
+      </c>
+      <c r="B97">
         <v>7.688</v>
       </c>
     </row>
